--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1462,7 +1462,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/EncounterInicioLE)
 </t>
   </si>
   <si>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$116</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4067" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4213" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -570,6 +570,26 @@
   </si>
   <si>
     <t>Doc Acreditacion Cuidador</t>
+  </si>
+  <si>
+    <t>EspecialidadMedicaDestinoCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/EspecialidadMedicaDestinoCodigo}
+</t>
+  </si>
+  <si>
+    <t>Especialidad Médica Destino Código</t>
+  </si>
+  <si>
+    <t>SubEspecialidadMedicaDestinoCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/SubEspecialidadMedicaDestinoCodigo}
+</t>
+  </si>
+  <si>
+    <t>SubEspecialidad Médica Destino Código</t>
   </si>
   <si>
     <t>ServiceRequest.modifierExtension</t>
@@ -1947,24 +1967,39 @@
     <t>paciente</t>
   </si>
   <si>
-    <t>QuestionnaireResponse</t>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PacienteLE)
+</t>
+  </si>
+  <si>
+    <t>Anamnesis</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/QuestionnaireResponseInicioLE)
 </t>
   </si>
   <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/CondicionInicio1LE)
+    <t>DiagnosticoSospecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ConditionInicioDiagnosticoSospechaLE)
 </t>
   </si>
   <si>
-    <t>AllergyIntolerance</t>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ConditionInicioSospechaGesLE)
+</t>
+  </si>
+  <si>
+    <t>TipoAlergia</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/AllergyIntoleranceInicioLE)
+</t>
+  </si>
+  <si>
+    <t>IndiceComorbilidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ConditionInicioIndiceComorbilidadLE)
 </t>
   </si>
   <si>
@@ -2382,11 +2417,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN112"/>
+  <dimension ref="A1:AN116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.68359375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.9296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -4821,45 +4856,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>178</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
         <v>78</v>
       </c>
@@ -4907,7 +4940,7 @@
         <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>76</v>
@@ -4916,7 +4949,7 @@
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>136</v>
@@ -4928,7 +4961,7 @@
         <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4937,20 +4970,22 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="B23" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="C23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>184</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>86</v>
@@ -4959,20 +4994,18 @@
         <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>78</v>
@@ -5009,19 +5042,19 @@
         <v>78</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AC23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -5030,66 +5063,66 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I24" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5137,7 +5170,7 @@
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5149,27 +5182,27 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -5177,30 +5210,32 @@
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M25" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>78</v>
@@ -5237,83 +5272,85 @@
         <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AC25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE25" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="AF25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL25" t="s" s="2">
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AM25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
-      <c r="A26" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
@@ -5351,19 +5388,19 @@
         <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
@@ -5375,27 +5412,27 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5412,26 +5449,22 @@
         <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5455,13 +5488,13 @@
         <v>78</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>78</v>
@@ -5479,7 +5512,7 @@
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
@@ -5491,16 +5524,16 @@
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5509,45 +5542,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5571,52 +5602,52 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5627,7 +5658,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5644,22 +5675,26 @@
         <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5683,13 +5718,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5707,7 +5742,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5719,16 +5754,16 @@
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5737,43 +5772,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5797,52 +5834,52 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5851,9 +5888,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5861,35 +5898,31 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5937,28 +5970,28 @@
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5969,18 +6002,18 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>78</v>
@@ -5992,15 +6025,17 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M32" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>78</v>
@@ -6037,31 +6072,31 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>78</v>
@@ -6070,7 +6105,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6079,43 +6114,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6151,19 +6188,19 @@
         <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
@@ -6175,16 +6212,16 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6193,9 +6230,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -6203,35 +6240,31 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>78</v>
       </c>
@@ -6279,7 +6312,7 @@
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
@@ -6291,16 +6324,16 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6311,18 +6344,18 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>78</v>
@@ -6331,19 +6364,19 @@
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>253</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -6381,40 +6414,40 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6425,7 +6458,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6448,17 +6481,19 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M36" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="N36" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>78</v>
@@ -6468,7 +6503,7 @@
         <v>78</v>
       </c>
       <c r="R36" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>78</v>
@@ -6507,7 +6542,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6525,10 +6560,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6537,9 +6572,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6553,7 +6588,7 @@
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6562,18 +6597,18 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M37" s="2"/>
-      <c r="N37" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6621,7 +6656,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6639,10 +6674,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6651,9 +6686,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6661,13 +6696,13 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
@@ -6676,19 +6711,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6698,7 +6731,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6737,7 +6770,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6755,10 +6788,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6767,9 +6800,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6783,7 +6816,7 @@
         <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6792,19 +6825,17 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6853,7 +6884,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6871,10 +6902,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6885,7 +6916,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6908,19 +6939,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>99</v>
+        <v>278</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6933,7 +6964,7 @@
         <v>78</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>293</v>
+        <v>78</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>78</v>
@@ -6969,7 +7000,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6987,10 +7018,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6999,9 +7030,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -7009,13 +7040,13 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -7024,18 +7055,20 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7047,7 +7080,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>301</v>
+        <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7083,7 +7116,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7101,10 +7134,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7115,7 +7148,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7138,16 +7171,20 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>306</v>
+        <v>99</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7159,7 +7196,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7195,7 +7232,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7213,10 +7250,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7225,9 +7262,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7235,13 +7272,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7250,16 +7287,16 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -7273,7 +7310,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7309,7 +7346,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7327,10 +7364,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7341,7 +7378,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7352,7 +7389,7 @@
         <v>76</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>78</v>
@@ -7364,17 +7401,15 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7423,13 +7458,13 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>78</v>
@@ -7438,13 +7473,13 @@
         <v>97</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>325</v>
+        <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7455,7 +7490,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7466,7 +7501,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7478,16 +7513,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>99</v>
+        <v>319</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7537,13 +7572,13 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>78</v>
@@ -7552,13 +7587,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7569,11 +7604,11 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7592,15 +7627,17 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M46" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
         <v>78</v>
@@ -7649,7 +7686,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7664,13 +7701,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7681,11 +7718,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7704,15 +7741,17 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>343</v>
+        <v>99</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M47" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7761,7 +7800,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7776,13 +7815,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7793,18 +7832,18 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>78</v>
@@ -7816,20 +7855,16 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>185</v>
+        <v>341</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>78</v>
       </c>
@@ -7877,13 +7912,13 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>78</v>
@@ -7892,13 +7927,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7907,42 +7942,40 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>105</v>
+        <v>349</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>78</v>
@@ -7967,13 +8000,13 @@
         <v>78</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
         <v>78</v>
@@ -7991,13 +8024,13 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -8006,58 +8039,60 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>367</v>
+        <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>368</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8081,13 +8116,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8105,10 +8140,10 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -8120,16 +8155,16 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>128</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>377</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -8137,7 +8172,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8145,7 +8180,7 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>85</v>
@@ -8154,26 +8189,24 @@
         <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>219</v>
+        <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8197,13 +8230,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>383</v>
+        <v>219</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8221,13 +8254,13 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>78</v>
@@ -8236,24 +8269,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8261,30 +8294,32 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>199</v>
+        <v>376</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M52" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
         <v>78</v>
@@ -8309,13 +8344,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>78</v>
+        <v>380</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8333,10 +8368,10 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>201</v>
+        <v>375</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -8345,61 +8380,63 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>202</v>
+        <v>382</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>204</v>
+        <v>385</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>205</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8423,31 +8460,31 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA53" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD53" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>207</v>
+        <v>384</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
@@ -8459,27 +8496,27 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>202</v>
+        <v>393</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8487,35 +8524,31 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8563,28 +8596,28 @@
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8595,18 +8628,18 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>78</v>
@@ -8618,15 +8651,17 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M55" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>78</v>
@@ -8663,31 +8698,31 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
@@ -8696,7 +8731,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8705,43 +8740,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8777,19 +8814,19 @@
         <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
@@ -8801,16 +8838,16 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8819,9 +8856,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8829,35 +8866,31 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8905,7 +8938,7 @@
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
@@ -8917,16 +8950,16 @@
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8937,18 +8970,18 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>78</v>
@@ -8957,19 +8990,19 @@
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>253</v>
+        <v>186</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
@@ -9007,40 +9040,40 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9051,7 +9084,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9074,17 +9107,19 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M59" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="N59" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>78</v>
@@ -9109,11 +9144,13 @@
         <v>78</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="X59" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y59" t="s" s="2">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="Z59" t="s" s="2">
         <v>78</v>
@@ -9131,7 +9168,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9149,10 +9186,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9161,9 +9198,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9177,7 +9214,7 @@
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9186,18 +9223,18 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M60" s="2"/>
-      <c r="N60" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9245,7 +9282,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9263,10 +9300,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9275,9 +9312,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9285,13 +9322,13 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -9300,19 +9337,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9337,13 +9372,11 @@
         <v>78</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="X61" s="2"/>
       <c r="Y61" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9361,7 +9394,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9379,10 +9412,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9391,9 +9424,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9407,7 +9440,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9416,19 +9449,17 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M62" s="2"/>
       <c r="N62" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9477,7 +9508,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9495,10 +9526,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9507,9 +9538,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9523,7 +9554,7 @@
         <v>85</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9532,22 +9563,24 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>105</v>
+        <v>278</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>401</v>
+        <v>279</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P63" t="s" s="2">
-        <v>403</v>
-      </c>
+      <c r="P63" s="2"/>
       <c r="Q63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9567,13 +9600,13 @@
         <v>78</v>
       </c>
       <c r="W63" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>405</v>
+        <v>78</v>
       </c>
       <c r="Z63" t="s" s="2">
         <v>78</v>
@@ -9591,7 +9624,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>400</v>
+        <v>283</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9606,24 +9639,24 @@
         <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>407</v>
+        <v>284</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>408</v>
+        <v>285</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9637,35 +9670,33 @@
         <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>411</v>
+        <v>287</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>288</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
+        <v>289</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>414</v>
+        <v>290</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P64" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9709,7 +9740,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>410</v>
+        <v>291</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9724,13 +9755,13 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>416</v>
+        <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>417</v>
+        <v>293</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9739,9 +9770,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9755,29 +9786,31 @@
         <v>85</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9797,13 +9830,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9821,7 +9854,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>201</v>
+        <v>406</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9833,27 +9866,27 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>415</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9864,32 +9897,38 @@
         <v>76</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>130</v>
+        <v>278</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>131</v>
+        <v>417</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="Q66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9921,38 +9960,40 @@
         <v>78</v>
       </c>
       <c r="AA66" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB66" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD66" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>207</v>
+        <v>416</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9961,13 +10002,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9979,7 +10018,7 @@
         <v>85</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9988,13 +10027,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>423</v>
+        <v>204</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -10051,13 +10090,13 @@
         <v>76</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -10077,7 +10116,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -10088,7 +10127,7 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>78</v>
@@ -10100,13 +10139,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>272</v>
+        <v>130</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>425</v>
+        <v>131</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10145,55 +10184,55 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB68" s="2"/>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE68" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AF68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
+      <c r="B69" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -10203,26 +10242,24 @@
         <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>219</v>
+        <v>429</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>430</v>
+        <v>407</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
         <v>78</v>
@@ -10247,13 +10284,13 @@
         <v>78</v>
       </c>
       <c r="W69" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>78</v>
@@ -10271,50 +10308,50 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>428</v>
+        <v>213</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>78</v>
@@ -10323,20 +10360,18 @@
         <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>78</v>
@@ -10361,13 +10396,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>446</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10385,43 +10420,43 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>447</v>
+        <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10440,18 +10475,18 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M71" s="2"/>
-      <c r="N71" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10475,13 +10510,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10499,7 +10534,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10514,38 +10549,38 @@
         <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10554,15 +10589,17 @@
         <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>456</v>
+        <v>225</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M72" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>78</v>
@@ -10587,13 +10624,13 @@
         <v>78</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>78</v>
@@ -10611,43 +10648,43 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>463</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>465</v>
+        <v>78</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10666,16 +10703,18 @@
         <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
+      <c r="N73" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10723,7 +10762,7 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>76</v>
@@ -10738,38 +10777,38 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>472</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>473</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10778,13 +10817,13 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10835,10 +10874,10 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -10850,28 +10889,28 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>483</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>78</v>
+        <v>471</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10890,13 +10929,13 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -10923,13 +10962,13 @@
         <v>78</v>
       </c>
       <c r="W75" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>488</v>
+        <v>78</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>489</v>
+        <v>78</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>78</v>
@@ -10947,7 +10986,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10962,28 +11001,28 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10993,7 +11032,7 @@
         <v>85</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -11002,13 +11041,13 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -11059,7 +11098,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11074,28 +11113,28 @@
         <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>501</v>
+        <v>489</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11114,17 +11153,15 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="M77" s="2"/>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>78</v>
@@ -11149,13 +11186,13 @@
         <v>78</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>78</v>
+        <v>495</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>78</v>
@@ -11173,7 +11210,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11188,28 +11225,28 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>509</v>
+        <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>511</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>512</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11219,7 +11256,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11228,17 +11265,15 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>219</v>
+        <v>500</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
@@ -11263,13 +11298,13 @@
         <v>78</v>
       </c>
       <c r="W78" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>518</v>
+        <v>78</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>78</v>
@@ -11287,7 +11322,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -11302,35 +11337,35 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>78</v>
+        <v>507</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>78</v>
@@ -11342,16 +11377,16 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -11401,13 +11436,13 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>78</v>
@@ -11416,28 +11451,28 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>78</v>
+        <v>518</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>78</v>
+        <v>520</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11447,7 +11482,7 @@
         <v>85</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -11456,15 +11491,17 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M80" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
         <v>78</v>
@@ -11489,13 +11526,13 @@
         <v>78</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>78</v>
@@ -11513,13 +11550,13 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>78</v>
@@ -11528,16 +11565,16 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11545,18 +11582,18 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>78</v>
@@ -11565,18 +11602,20 @@
         <v>78</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>198</v>
+        <v>532</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>199</v>
+        <v>533</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M81" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
         <v>78</v>
@@ -11625,72 +11664,70 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>201</v>
+        <v>530</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>202</v>
+        <v>538</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>204</v>
+        <v>540</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>78</v>
@@ -11715,31 +11752,31 @@
         <v>78</v>
       </c>
       <c r="W82" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>78</v>
+        <v>542</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>78</v>
+        <v>543</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA82" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD82" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>207</v>
+        <v>539</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11751,7 +11788,7 @@
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>78</v>
@@ -11760,18 +11797,18 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>202</v>
+        <v>544</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11779,35 +11816,31 @@
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11831,11 +11864,13 @@
         <v>78</v>
       </c>
       <c r="W83" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="X83" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y83" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
@@ -11853,28 +11888,28 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>238</v>
+        <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11885,18 +11920,18 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>78</v>
@@ -11908,15 +11943,17 @@
         <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M84" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
         <v>78</v>
@@ -11953,31 +11990,31 @@
         <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>78</v>
@@ -11986,7 +12023,7 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11995,43 +12032,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12055,31 +12094,29 @@
         <v>78</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="X85" s="2"/>
       <c r="Y85" t="s" s="2">
-        <v>78</v>
+        <v>548</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA85" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD85" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
@@ -12091,16 +12128,16 @@
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>202</v>
+        <v>245</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12109,9 +12146,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
@@ -12119,35 +12156,31 @@
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M86" s="2"/>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
       </c>
@@ -12195,7 +12228,7 @@
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12207,16 +12240,16 @@
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -12227,18 +12260,18 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>78</v>
@@ -12247,19 +12280,19 @@
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>253</v>
+        <v>186</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
@@ -12297,40 +12330,40 @@
         <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12341,7 +12374,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12364,17 +12397,19 @@
         <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="M88" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="N88" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>78</v>
@@ -12423,7 +12458,7 @@
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12441,10 +12476,10 @@
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12453,9 +12488,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12469,7 +12504,7 @@
         <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12478,18 +12513,18 @@
         <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="M89" s="2"/>
-      <c r="N89" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12537,7 +12572,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12555,10 +12590,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12567,9 +12602,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12577,13 +12612,13 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
@@ -12592,19 +12627,17 @@
         <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="M90" s="2"/>
       <c r="N90" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
@@ -12653,7 +12686,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12671,10 +12704,10 @@
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12683,9 +12716,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12699,7 +12732,7 @@
         <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -12708,19 +12741,17 @@
         <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M91" s="2"/>
       <c r="N91" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12769,7 +12800,7 @@
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12787,10 +12818,10 @@
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12799,9 +12830,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12815,7 +12846,7 @@
         <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12824,16 +12855,20 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>552</v>
+        <v>278</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>534</v>
+        <v>279</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12881,13 +12916,13 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>551</v>
+        <v>283</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>78</v>
@@ -12899,13 +12934,13 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>554</v>
+        <v>285</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>523</v>
+        <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -12913,7 +12948,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12933,19 +12968,23 @@
         <v>78</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12993,7 +13032,7 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
@@ -13005,16 +13044,16 @@
         <v>78</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -13023,42 +13062,40 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>130</v>
+        <v>558</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>204</v>
+        <v>540</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>180</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
         <v>78</v>
@@ -13095,19 +13132,19 @@
         <v>78</v>
       </c>
       <c r="AA94" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>206</v>
+        <v>78</v>
       </c>
       <c r="AC94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD94" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>207</v>
+        <v>557</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
@@ -13119,7 +13156,7 @@
         <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>78</v>
@@ -13128,18 +13165,18 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>202</v>
+        <v>560</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13147,32 +13184,30 @@
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>558</v>
+        <v>205</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M95" s="2"/>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
         <v>78</v>
@@ -13221,7 +13256,7 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>561</v>
+        <v>207</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13230,10 +13265,10 @@
         <v>85</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>562</v>
+        <v>78</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>78</v>
@@ -13242,7 +13277,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13253,18 +13288,18 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>78</v>
@@ -13273,19 +13308,19 @@
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>564</v>
+        <v>210</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>565</v>
+        <v>211</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>566</v>
+        <v>186</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
@@ -13311,43 +13346,43 @@
         <v>78</v>
       </c>
       <c r="W96" t="s" s="2">
-        <v>224</v>
+        <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>567</v>
+        <v>78</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="Z96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA96" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>569</v>
+        <v>213</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>78</v>
@@ -13356,7 +13391,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13365,9 +13400,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13375,13 +13410,13 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -13390,16 +13425,16 @@
         <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13449,7 +13484,7 @@
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13458,7 +13493,7 @@
         <v>85</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>97</v>
@@ -13470,7 +13505,7 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13481,7 +13516,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13504,16 +13539,16 @@
         <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13539,13 +13574,13 @@
         <v>78</v>
       </c>
       <c r="W98" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>78</v>
+        <v>573</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>78</v>
@@ -13563,7 +13598,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13593,9 +13628,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
@@ -13609,7 +13644,7 @@
         <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13618,16 +13653,16 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13653,13 +13688,13 @@
         <v>78</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>584</v>
+        <v>78</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>78</v>
@@ -13683,7 +13718,7 @@
         <v>76</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>78</v>
@@ -13692,16 +13727,16 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>586</v>
+        <v>78</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>588</v>
+        <v>199</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>589</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13709,7 +13744,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13720,7 +13755,7 @@
         <v>76</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>78</v>
@@ -13732,16 +13767,16 @@
         <v>86</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>591</v>
+        <v>204</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13791,13 +13826,13 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>78</v>
@@ -13806,24 +13841,24 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>596</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>597</v>
+        <v>128</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>589</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
@@ -13834,27 +13869,29 @@
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>599</v>
+        <v>225</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="M101" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
         <v>78</v>
@@ -13879,13 +13916,13 @@
         <v>78</v>
       </c>
       <c r="W101" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="Z101" t="s" s="2">
         <v>78</v>
@@ -13903,7 +13940,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13918,16 +13955,16 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13935,11 +13972,11 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13949,25 +13986,25 @@
         <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I102" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J102" t="s" s="2">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -14005,19 +14042,19 @@
         <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>611</v>
+        <v>78</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="AC102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14032,40 +14069,38 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="B103" s="2"/>
       <c r="C103" t="s" s="2">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14074,17 +14109,15 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
         <v>78</v>
@@ -14133,7 +14166,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14148,13 +14181,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14163,22 +14196,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>618</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="B104" s="2"/>
       <c r="C104" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>86</v>
@@ -14190,16 +14221,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14237,19 +14268,19 @@
         <v>78</v>
       </c>
       <c r="AA104" t="s" s="2">
-        <v>78</v>
+        <v>617</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>78</v>
+        <v>618</v>
       </c>
       <c r="AC104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD104" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14264,13 +14295,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14281,13 +14312,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14306,16 +14337,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14365,7 +14396,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14380,13 +14411,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14397,13 +14428,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14422,16 +14453,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14481,7 +14512,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14496,13 +14527,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14513,13 +14544,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14538,16 +14569,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14597,7 +14628,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14612,13 +14643,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14627,41 +14658,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B108" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="C108" t="s" s="2">
-        <v>78</v>
+        <v>612</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14711,7 +14744,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14726,13 +14759,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14741,45 +14774,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B109" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="C109" t="s" s="2">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>219</v>
+        <v>630</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>635</v>
+        <v>615</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
         <v>78</v>
       </c>
@@ -14803,13 +14836,13 @@
         <v>78</v>
       </c>
       <c r="W109" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>638</v>
+        <v>78</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>639</v>
+        <v>78</v>
       </c>
       <c r="Z109" t="s" s="2">
         <v>78</v>
@@ -14827,7 +14860,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14842,38 +14875,40 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>641</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B110" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="C110" t="s" s="2">
-        <v>78</v>
+        <v>612</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>78</v>
@@ -14882,15 +14917,17 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>47</v>
+        <v>614</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="M110" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
         <v>78</v>
@@ -14939,7 +14976,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>642</v>
+        <v>611</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14954,28 +14991,30 @@
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>645</v>
+        <v>619</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>448</v>
+        <v>620</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>646</v>
+        <v>621</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>647</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="C111" t="s" s="2">
-        <v>78</v>
+        <v>612</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14985,24 +15024,26 @@
         <v>85</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>198</v>
+        <v>634</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>649</v>
+        <v>614</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M111" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
         <v>78</v>
@@ -15051,13 +15092,13 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>78</v>
@@ -15066,13 +15107,13 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>448</v>
+        <v>620</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>651</v>
+        <v>621</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -15083,7 +15124,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
@@ -15103,19 +15144,19 @@
         <v>78</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
@@ -15165,7 +15206,7 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
@@ -15180,23 +15221,477 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B114" s="2"/>
+      <c r="C114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M114" s="2"/>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="AK112" t="s" s="2">
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B115" s="2"/>
+      <c r="C115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M115" s="2"/>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P115" s="2"/>
+      <c r="Q115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B116" s="2"/>
+      <c r="C116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P116" s="2"/>
+      <c r="Q116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AK116" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AL112" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
+      <c r="AL116" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN112">
+  <autoFilter ref="A1:AN116">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15206,7 +15701,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI111">
+  <conditionalFormatting sqref="A2:AI115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1967,7 +1967,7 @@
     <t>paciente</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PacienteLE)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$115</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4213" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -520,16 +520,6 @@
   </si>
   <si>
     <t>ExtBool PresentaDiscapacidad</t>
-  </si>
-  <si>
-    <t>PersonaMayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolPersonaMayor}
-</t>
-  </si>
-  <si>
-    <t>ExtBool PersonaMayor</t>
   </si>
   <si>
     <t>OrigenInterconsulta</t>
@@ -2417,7 +2407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN116"/>
+  <dimension ref="A1:AN115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -4433,7 +4423,7 @@
         <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -4547,7 +4537,7 @@
         <v>169</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -4970,43 +4960,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B23" t="s" s="2">
         <v>179</v>
       </c>
+      <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>181</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="O23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5054,7 +5046,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -5063,7 +5055,7 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>136</v>
@@ -5075,7 +5067,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -5086,43 +5078,41 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J24" t="s" s="2">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5158,19 +5148,19 @@
         <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AC24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5182,29 +5172,31 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="C25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5213,7 +5205,7 @@
         <v>85</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>86</v>
@@ -5225,16 +5217,16 @@
         <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -5272,19 +5264,19 @@
         <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5299,59 +5291,55 @@
         <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN25" t="s" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>78</v>
@@ -5400,50 +5388,50 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>78</v>
@@ -5455,15 +5443,17 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M27" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
@@ -5500,31 +5490,31 @@
         <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>78</v>
@@ -5533,7 +5523,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5544,41 +5534,43 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="O28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5602,52 +5594,52 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5656,9 +5648,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5666,34 +5658,34 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5718,13 +5710,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5742,7 +5734,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5760,10 +5752,10 @@
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5772,9 +5764,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5782,35 +5774,31 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5834,13 +5822,13 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
@@ -5858,7 +5846,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5870,16 +5858,16 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5890,18 +5878,18 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>78</v>
@@ -5913,15 +5901,17 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M31" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>78</v>
@@ -5958,31 +5948,31 @@
         <v>78</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
@@ -5991,7 +5981,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -6000,43 +5990,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O32" t="s" s="2">
         <v>78</v>
       </c>
@@ -6072,19 +6064,19 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6096,16 +6088,16 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6114,9 +6106,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6124,35 +6116,31 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6200,28 +6188,28 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6232,18 +6220,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>78</v>
@@ -6255,15 +6243,17 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M34" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>78</v>
@@ -6300,31 +6290,31 @@
         <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
@@ -6333,7 +6323,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6342,43 +6332,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6414,40 +6406,40 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6456,9 +6448,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6466,13 +6458,13 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -6481,20 +6473,18 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6542,7 +6532,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6560,10 +6550,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6572,9 +6562,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6582,13 +6572,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6597,18 +6587,18 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6617,7 +6607,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6656,7 +6646,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6674,10 +6664,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6688,7 +6678,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6696,7 +6686,7 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
@@ -6711,17 +6701,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6731,7 +6721,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6770,7 +6760,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6788,10 +6778,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6800,9 +6790,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6816,7 +6806,7 @@
         <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6825,17 +6815,19 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M39" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="N39" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6884,7 +6876,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6902,10 +6894,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6916,7 +6908,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6939,19 +6931,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -7000,7 +6992,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -7018,10 +7010,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -7032,7 +7024,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -7055,19 +7047,19 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -7080,7 +7072,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7116,7 +7108,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7134,10 +7126,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7146,9 +7138,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7156,13 +7148,13 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7171,20 +7163,18 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7196,7 +7186,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7232,7 +7222,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7250,10 +7240,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7262,9 +7252,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7272,13 +7262,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7287,17 +7277,15 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
         <v>78</v>
@@ -7310,7 +7298,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7346,7 +7334,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7364,10 +7352,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7378,7 +7366,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7401,15 +7389,17 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M44" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7458,7 +7448,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7476,10 +7466,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7490,7 +7480,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7501,7 +7491,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7513,16 +7503,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7578,7 +7568,7 @@
         <v>76</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>78</v>
@@ -7587,13 +7577,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>78</v>
+        <v>328</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7604,7 +7594,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7627,16 +7617,16 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>327</v>
+        <v>99</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7686,7 +7676,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7701,13 +7691,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7718,11 +7708,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7741,17 +7731,15 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>99</v>
+        <v>338</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7800,7 +7788,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7815,13 +7803,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7832,11 +7820,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7855,13 +7843,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7912,7 +7900,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7927,13 +7915,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7944,18 +7932,18 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>78</v>
@@ -7967,16 +7955,20 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>349</v>
+        <v>188</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O49" t="s" s="2">
         <v>78</v>
       </c>
@@ -8024,13 +8016,13 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -8039,13 +8031,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -8054,45 +8046,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>356</v>
+        <v>78</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8116,13 +8106,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8140,10 +8130,10 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -8155,24 +8145,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8198,13 +8188,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8230,13 +8220,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8254,7 +8244,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8269,24 +8259,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>128</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8294,7 +8284,7 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>85</v>
@@ -8303,24 +8293,26 @@
         <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8344,13 +8336,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>219</v>
+        <v>386</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8368,13 +8360,13 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>78</v>
@@ -8383,24 +8375,24 @@
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>381</v>
+        <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>128</v>
+        <v>389</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8414,29 +8406,25 @@
         <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>385</v>
+        <v>202</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8460,13 +8448,13 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -8484,31 +8472,31 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>384</v>
+        <v>204</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>393</v>
+        <v>205</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8516,18 +8504,18 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>78</v>
@@ -8539,15 +8527,17 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M54" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>78</v>
@@ -8584,31 +8574,31 @@
         <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
@@ -8617,7 +8607,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8626,43 +8616,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8698,19 +8690,19 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8722,16 +8714,16 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8740,9 +8732,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8750,35 +8742,31 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8826,28 +8814,28 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8858,18 +8846,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>78</v>
@@ -8881,15 +8869,17 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M57" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>78</v>
@@ -8926,31 +8916,31 @@
         <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
@@ -8959,7 +8949,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8968,43 +8958,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9040,40 +9032,40 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9082,9 +9074,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9092,13 +9084,13 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -9107,20 +9099,18 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9168,7 +9158,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9186,10 +9176,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9198,9 +9188,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9208,13 +9198,13 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9223,18 +9213,18 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="M60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9258,13 +9248,11 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="X60" s="2"/>
       <c r="Y60" t="s" s="2">
-        <v>78</v>
+        <v>399</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9282,7 +9270,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9300,10 +9288,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9314,7 +9302,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9322,7 +9310,7 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
@@ -9337,17 +9325,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9372,11 +9360,13 @@
         <v>78</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X61" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y61" t="s" s="2">
-        <v>402</v>
+        <v>78</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9394,7 +9384,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9412,10 +9402,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9424,9 +9414,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9440,7 +9430,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9449,17 +9439,19 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M62" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="N62" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9508,7 +9500,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9526,10 +9518,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9540,7 +9532,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9563,19 +9555,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9624,7 +9616,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9642,10 +9634,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9654,9 +9646,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9670,7 +9662,7 @@
         <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9679,24 +9671,22 @@
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>287</v>
+        <v>404</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="Q64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9716,13 +9706,13 @@
         <v>78</v>
       </c>
       <c r="W64" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
@@ -9740,7 +9730,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>291</v>
+        <v>403</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9755,16 +9745,16 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>292</v>
+        <v>410</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>293</v>
+        <v>411</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9772,7 +9762,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9789,27 +9779,31 @@
         <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>105</v>
+        <v>275</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
@@ -9830,13 +9824,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9854,7 +9848,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9869,24 +9863,24 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>413</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9900,35 +9894,29 @@
         <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P66" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9972,7 +9960,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>416</v>
+        <v>204</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9984,16 +9972,16 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -10015,7 +10003,7 @@
         <v>76</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>78</v>
@@ -10027,13 +10015,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>425</v>
+        <v>131</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -10072,31 +10060,29 @@
         <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB67" s="2"/>
       <c r="AC67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -10114,11 +10100,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="C68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10127,10 +10115,10 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10139,13 +10127,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>130</v>
+        <v>426</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>131</v>
+        <v>404</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>132</v>
+        <v>404</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10184,17 +10172,19 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB68" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10203,7 +10193,7 @@
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>136</v>
@@ -10224,13 +10214,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="B69" t="s" s="2">
-        <v>428</v>
-      </c>
+      <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10242,7 +10230,7 @@
         <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10251,13 +10239,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10308,19 +10296,19 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>213</v>
+        <v>430</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>78</v>
@@ -10340,11 +10328,11 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10360,18 +10348,20 @@
         <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M70" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>78</v>
@@ -10396,13 +10386,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>436</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10420,7 +10410,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10432,38 +10422,38 @@
         <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>78</v>
@@ -10475,16 +10465,16 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10510,13 +10500,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10534,50 +10524,50 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>445</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>447</v>
+        <v>78</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>78</v>
@@ -10589,18 +10579,18 @@
         <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>225</v>
+        <v>453</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="M72" s="2"/>
+      <c r="N72" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10624,40 +10614,40 @@
         <v>78</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>451</v>
+        <v>78</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>97</v>
@@ -10666,21 +10656,21 @@
         <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10688,13 +10678,13 @@
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10703,18 +10693,16 @@
         <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M73" s="2"/>
-      <c r="N73" t="s" s="2">
-        <v>459</v>
-      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10762,10 +10750,10 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>85</v>
@@ -10777,38 +10765,38 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>465</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>78</v>
+        <v>466</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10817,13 +10805,13 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10874,10 +10862,10 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>85</v>
@@ -10889,28 +10877,28 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10929,13 +10917,13 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -10986,7 +10974,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -11001,28 +10989,28 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>481</v>
+        <v>78</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -11041,13 +11029,13 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -11074,13 +11062,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11098,7 +11086,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11113,28 +11101,28 @@
         <v>97</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>488</v>
+        <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>78</v>
+        <v>496</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11144,7 +11132,7 @@
         <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11153,13 +11141,13 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -11186,31 +11174,31 @@
         <v>78</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>494</v>
+        <v>78</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11225,28 +11213,28 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>78</v>
+        <v>501</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11256,7 +11244,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11265,15 +11253,17 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M78" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
@@ -11322,7 +11312,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -11337,28 +11327,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11377,16 +11367,16 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>510</v>
+        <v>222</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -11412,13 +11402,13 @@
         <v>78</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>78</v>
@@ -11436,7 +11426,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11451,35 +11441,35 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>518</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>78</v>
@@ -11491,16 +11481,16 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>225</v>
+        <v>529</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -11526,13 +11516,13 @@
         <v>78</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>78</v>
@@ -11550,13 +11540,13 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>78</v>
@@ -11565,38 +11555,38 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="AK80" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>531</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11605,17 +11595,15 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>532</v>
+        <v>222</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
         <v>78</v>
@@ -11640,13 +11628,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11664,7 +11652,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
@@ -11679,24 +11667,24 @@
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>536</v>
+        <v>78</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>537</v>
+        <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -11710,22 +11698,22 @@
         <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>540</v>
+        <v>202</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>541</v>
+        <v>203</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11752,13 +11740,13 @@
         <v>78</v>
       </c>
       <c r="W82" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>543</v>
+        <v>78</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>78</v>
@@ -11776,19 +11764,19 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>539</v>
+        <v>204</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>78</v>
@@ -11797,10 +11785,10 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>544</v>
+        <v>205</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11808,18 +11796,18 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>78</v>
@@ -11831,15 +11819,17 @@
         <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M83" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
         <v>78</v>
@@ -11876,31 +11866,31 @@
         <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>78</v>
@@ -11909,7 +11899,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11918,43 +11908,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>130</v>
+        <v>235</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="O84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11978,31 +11970,29 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="X84" s="2"/>
       <c r="Y84" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -12014,16 +12004,16 @@
         <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>208</v>
+        <v>242</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -12032,9 +12022,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -12042,35 +12032,31 @@
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12094,11 +12080,13 @@
         <v>78</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X85" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y85" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>78</v>
@@ -12116,28 +12104,28 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12148,18 +12136,18 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>78</v>
@@ -12171,15 +12159,17 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M86" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
@@ -12216,31 +12206,31 @@
         <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD86" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
@@ -12249,7 +12239,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -12258,43 +12248,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="O87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12330,40 +12322,40 @@
         <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12372,9 +12364,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12382,13 +12374,13 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12397,20 +12389,18 @@
         <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>99</v>
+        <v>201</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12458,7 +12448,7 @@
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12476,10 +12466,10 @@
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12488,9 +12478,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12498,13 +12488,13 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12513,18 +12503,18 @@
         <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="M89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12572,7 +12562,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12590,10 +12580,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12604,7 +12594,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12612,7 +12602,7 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>85</v>
@@ -12627,17 +12617,17 @@
         <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
@@ -12686,7 +12676,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12704,10 +12694,10 @@
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12716,9 +12706,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12732,7 +12722,7 @@
         <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -12741,17 +12731,19 @@
         <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="M91" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="N91" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12800,7 +12792,7 @@
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12818,10 +12810,10 @@
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12832,7 +12824,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12855,19 +12847,19 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>278</v>
+        <v>201</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
@@ -12916,7 +12908,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12934,10 +12926,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12946,9 +12938,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12962,7 +12954,7 @@
         <v>85</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12971,20 +12963,16 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>204</v>
+        <v>555</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>287</v>
+        <v>537</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13032,13 +13020,13 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>291</v>
+        <v>554</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>78</v>
@@ -13050,21 +13038,21 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>292</v>
+        <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>293</v>
+        <v>557</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -13078,22 +13066,22 @@
         <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>540</v>
+        <v>202</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>559</v>
+        <v>203</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -13144,19 +13132,19 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>557</v>
+        <v>204</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>78</v>
@@ -13165,10 +13153,10 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>560</v>
+        <v>205</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13176,18 +13164,18 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>78</v>
@@ -13199,15 +13187,17 @@
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M95" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
         <v>78</v>
@@ -13244,31 +13234,31 @@
         <v>78</v>
       </c>
       <c r="AA95" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AC95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>78</v>
@@ -13277,7 +13267,7 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13286,41 +13276,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>210</v>
+        <v>561</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>211</v>
+        <v>562</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>186</v>
+        <v>563</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
@@ -13358,31 +13348,31 @@
         <v>78</v>
       </c>
       <c r="AA96" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>213</v>
+        <v>564</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>78</v>
+        <v>565</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>78</v>
@@ -13391,7 +13381,7 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13400,9 +13390,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13410,13 +13400,13 @@
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -13425,16 +13415,16 @@
         <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13460,13 +13450,13 @@
         <v>78</v>
       </c>
       <c r="W97" t="s" s="2">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>78</v>
+        <v>570</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>78</v>
+        <v>571</v>
       </c>
       <c r="Z97" t="s" s="2">
         <v>78</v>
@@ -13484,7 +13474,7 @@
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13493,7 +13483,7 @@
         <v>85</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>97</v>
@@ -13516,7 +13506,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13539,16 +13529,16 @@
         <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13574,13 +13564,13 @@
         <v>78</v>
       </c>
       <c r="W98" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>573</v>
+        <v>78</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>574</v>
+        <v>78</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>78</v>
@@ -13598,7 +13588,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13619,7 +13609,7 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13630,7 +13620,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
@@ -13653,16 +13643,16 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13712,7 +13702,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13733,7 +13723,7 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13742,9 +13732,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13758,7 +13748,7 @@
         <v>85</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13767,16 +13757,16 @@
         <v>86</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13802,13 +13792,13 @@
         <v>78</v>
       </c>
       <c r="W100" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>78</v>
+        <v>587</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>78</v>
+        <v>588</v>
       </c>
       <c r="Z100" t="s" s="2">
         <v>78</v>
@@ -13826,13 +13816,13 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>78</v>
@@ -13841,24 +13831,24 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>78</v>
+        <v>589</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>128</v>
+        <v>591</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
@@ -13869,10 +13859,10 @@
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13881,16 +13871,16 @@
         <v>86</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>225</v>
+        <v>594</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13916,13 +13906,13 @@
         <v>78</v>
       </c>
       <c r="W101" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>590</v>
+        <v>78</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>591</v>
+        <v>78</v>
       </c>
       <c r="Z101" t="s" s="2">
         <v>78</v>
@@ -13940,7 +13930,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13955,16 +13945,16 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13972,7 +13962,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
@@ -13992,20 +13982,18 @@
         <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
         <v>78</v>
@@ -14054,7 +14042,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14069,16 +14057,16 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -14086,11 +14074,11 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" t="s" s="2">
-        <v>78</v>
+        <v>609</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14100,7 +14088,7 @@
         <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14109,15 +14097,17 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M103" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
         <v>78</v>
@@ -14154,19 +14144,19 @@
         <v>78</v>
       </c>
       <c r="AA103" t="s" s="2">
-        <v>78</v>
+        <v>614</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>78</v>
+        <v>615</v>
       </c>
       <c r="AC103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD103" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14181,35 +14171,37 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="AK103" t="s" s="2">
+      <c r="B104" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B104" s="2"/>
-      <c r="C104" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>86</v>
@@ -14221,16 +14213,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14268,19 +14260,19 @@
         <v>78</v>
       </c>
       <c r="AA104" t="s" s="2">
-        <v>617</v>
+        <v>78</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>618</v>
+        <v>78</v>
       </c>
       <c r="AC104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD104" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14295,13 +14287,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14312,13 +14304,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14337,16 +14329,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14396,7 +14388,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14411,13 +14403,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14428,13 +14420,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14453,16 +14445,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14512,7 +14504,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14527,13 +14519,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14544,13 +14536,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14569,16 +14561,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14628,7 +14620,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14643,13 +14635,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14660,13 +14652,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>628</v>
+        <v>146</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14685,16 +14677,16 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14744,7 +14736,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14759,13 +14751,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14776,13 +14768,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>146</v>
+        <v>628</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14801,16 +14793,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14860,7 +14852,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14875,13 +14867,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14892,13 +14884,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14917,16 +14909,16 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
@@ -14976,7 +14968,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14991,13 +14983,13 @@
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -15006,43 +14998,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>633</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J111" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="K111" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="K111" t="s" s="2">
-        <v>614</v>
-      </c>
       <c r="L111" t="s" s="2">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
@@ -15092,7 +15082,7 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
@@ -15107,13 +15097,13 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>619</v>
+        <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>620</v>
+        <v>637</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -15124,11 +15114,11 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
-        <v>78</v>
+        <v>640</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15147,18 +15137,20 @@
         <v>86</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>636</v>
+        <v>222</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="O112" t="s" s="2">
         <v>78</v>
       </c>
@@ -15182,13 +15174,13 @@
         <v>78</v>
       </c>
       <c r="W112" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>78</v>
+        <v>645</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>78</v>
+        <v>646</v>
       </c>
       <c r="Z112" t="s" s="2">
         <v>78</v>
@@ -15206,7 +15198,7 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
@@ -15224,25 +15216,25 @@
         <v>78</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>78</v>
+        <v>648</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
-        <v>643</v>
+        <v>78</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -15258,23 +15250,19 @@
         <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>225</v>
+        <v>650</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>644</v>
+        <v>47</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>647</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
         <v>78</v>
       </c>
@@ -15298,31 +15286,31 @@
         <v>78</v>
       </c>
       <c r="W113" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>648</v>
+        <v>78</v>
       </c>
       <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>76</v>
@@ -15337,24 +15325,24 @@
         <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>78</v>
+        <v>652</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>640</v>
+        <v>451</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" t="s" s="2">
@@ -15365,7 +15353,7 @@
         <v>76</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>78</v>
@@ -15374,16 +15362,16 @@
         <v>78</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>653</v>
+        <v>201</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>47</v>
+        <v>656</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
@@ -15434,13 +15422,13 @@
         <v>78</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AF114" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>78</v>
@@ -15449,24 +15437,24 @@
         <v>97</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>655</v>
+        <v>78</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>657</v>
+        <v>78</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" t="s" s="2">
@@ -15477,7 +15465,7 @@
         <v>76</v>
       </c>
       <c r="F115" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>78</v>
@@ -15486,18 +15474,20 @@
         <v>78</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>204</v>
+        <v>660</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="M115" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
         <v>78</v>
@@ -15546,13 +15536,13 @@
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>78</v>
@@ -15561,137 +15551,23 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>78</v>
+        <v>664</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>454</v>
+        <v>128</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="B116" s="2"/>
-      <c r="C116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D116" s="2"/>
-      <c r="E116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P116" s="2"/>
-      <c r="Q116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN116" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN116">
+  <autoFilter ref="A1:AN115">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15701,7 +15577,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI115">
+  <conditionalFormatting sqref="A2:AI114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1596,7 +1596,7 @@
 orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE)
 </t>
   </si>
   <si>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$109</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1443,7 +1443,7 @@
     <t>ServiceRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>
@@ -1754,86 +1754,6 @@
     <t>.participation[typeCode=LOC].role[scoper.determinerCode=INSTANCE]</t>
   </si>
   <si>
-    <t>ServiceRequest.locationReference.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>ServiceRequest.locationReference.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
     <t>ServiceRequest.reasonCode</t>
   </si>
   <si>
@@ -1867,7 +1787,7 @@
     <t>ServiceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/ObservationInicioLE)
 </t>
   </si>
   <si>
@@ -1947,7 +1867,7 @@
     <t>.outboundRelationship[typeCode=PERT].target</t>
   </si>
   <si>
-    <t>reserva</t>
+    <t>cita</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/AppointmentInicioLE)
@@ -1955,10 +1875,6 @@
   </si>
   <si>
     <t>paciente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
-</t>
   </si>
   <si>
     <t>Anamnesis</t>
@@ -2407,7 +2323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN115"/>
+  <dimension ref="A1:AN109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -11228,7 +11144,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>505</v>
       </c>
@@ -11244,7 +11160,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -12938,7 +12854,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>554</v>
       </c>
@@ -12951,10 +12867,10 @@
         <v>76</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -13050,7 +12966,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>558</v>
       </c>
@@ -13066,24 +12982,26 @@
         <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>202</v>
+        <v>559</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M94" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
         <v>78</v>
@@ -13108,13 +13026,13 @@
         <v>78</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>78</v>
+        <v>562</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>78</v>
+        <v>563</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>78</v>
@@ -13132,31 +13050,31 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>204</v>
+        <v>558</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>564</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>78</v>
+        <v>565</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>205</v>
+        <v>566</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13164,11 +13082,11 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -13184,19 +13102,19 @@
         <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>130</v>
+        <v>569</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>207</v>
+        <v>570</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>208</v>
+        <v>571</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>183</v>
+        <v>572</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
@@ -13234,19 +13152,19 @@
         <v>78</v>
       </c>
       <c r="AA95" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AC95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>210</v>
+        <v>568</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13258,27 +13176,27 @@
         <v>78</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>78</v>
+        <v>573</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>205</v>
+        <v>575</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13286,32 +13204,30 @@
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>201</v>
+        <v>577</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="M96" s="2"/>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
         <v>78</v>
@@ -13360,28 +13276,28 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>565</v>
+        <v>78</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>78</v>
+        <v>580</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>78</v>
+        <v>581</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>128</v>
+        <v>582</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13392,39 +13308,39 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>99</v>
+        <v>585</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13450,37 +13366,37 @@
         <v>78</v>
       </c>
       <c r="W97" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>570</v>
+        <v>78</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="Z97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>78</v>
+        <v>589</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="AC97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>78</v>
@@ -13489,13 +13405,13 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>128</v>
+        <v>593</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13504,13 +13420,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B98" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="C98" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13520,25 +13438,25 @@
         <v>85</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>188</v>
+        <v>595</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13588,13 +13506,13 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>78</v>
@@ -13603,13 +13521,13 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>196</v>
+        <v>593</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13618,13 +13536,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="B99" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="C99" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13634,25 +13554,25 @@
         <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>201</v>
+        <v>585</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13702,13 +13622,13 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>78</v>
@@ -13717,13 +13637,13 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>128</v>
+        <v>593</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13736,9 +13656,11 @@
       <c r="A100" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="B100" s="2"/>
+      <c r="B100" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="C100" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13754,19 +13676,19 @@
         <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>222</v>
+        <v>598</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13792,13 +13714,13 @@
         <v>78</v>
       </c>
       <c r="W100" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>587</v>
+        <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>588</v>
+        <v>78</v>
       </c>
       <c r="Z100" t="s" s="2">
         <v>78</v>
@@ -13831,56 +13753,58 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B101" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="C101" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13930,7 +13854,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13945,38 +13869,40 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B102" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="C102" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -13985,15 +13911,17 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M102" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
         <v>78</v>
@@ -14042,7 +13970,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14057,13 +13985,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14072,20 +14000,22 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B103" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="C103" t="s" s="2">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>86</v>
@@ -14097,16 +14027,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14144,19 +14074,19 @@
         <v>78</v>
       </c>
       <c r="AA103" t="s" s="2">
-        <v>614</v>
+        <v>78</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>615</v>
+        <v>78</v>
       </c>
       <c r="AC103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD103" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14171,13 +14101,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14188,13 +14118,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14213,16 +14143,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>613</v>
+        <v>588</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14272,7 +14202,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14287,13 +14217,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>616</v>
+        <v>591</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>617</v>
+        <v>592</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>618</v>
+        <v>593</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14302,43 +14232,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>621</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="B105" s="2"/>
       <c r="C105" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I105" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J105" t="s" s="2">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14388,7 +14316,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14403,13 +14331,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>616</v>
+        <v>78</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14418,45 +14346,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="B106" s="2"/>
       <c r="C106" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I106" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J106" t="s" s="2">
-        <v>624</v>
+        <v>222</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14480,13 +14408,13 @@
         <v>78</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>78</v>
+        <v>619</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>78</v>
+        <v>620</v>
       </c>
       <c r="Z106" t="s" s="2">
         <v>78</v>
@@ -14504,7 +14432,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14519,40 +14447,38 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>616</v>
+        <v>78</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>78</v>
+        <v>622</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="B107" s="2"/>
       <c r="C107" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14561,17 +14487,15 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>611</v>
+        <v>47</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
         <v>78</v>
@@ -14620,7 +14544,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14635,30 +14559,28 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>617</v>
+        <v>451</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>78</v>
+        <v>628</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>629</v>
+      </c>
+      <c r="B108" s="2"/>
       <c r="C108" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14668,26 +14590,24 @@
         <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J108" t="s" s="2">
-        <v>627</v>
+        <v>201</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>611</v>
+        <v>630</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
         <v>78</v>
@@ -14736,13 +14656,13 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>78</v>
@@ -14751,13 +14671,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>616</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>617</v>
+        <v>451</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>618</v>
+        <v>632</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14766,25 +14686,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="B109" s="2"/>
       <c r="C109" t="s" s="2">
-        <v>609</v>
+        <v>78</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14793,16 +14711,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>613</v>
+        <v>637</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14852,7 +14770,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>608</v>
+        <v>633</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14867,707 +14785,23 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>616</v>
+        <v>638</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>617</v>
+        <v>128</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="D110" s="2"/>
-      <c r="E110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F110" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P110" s="2"/>
-      <c r="Q110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B111" s="2"/>
-      <c r="C111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D111" s="2"/>
-      <c r="E111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P111" s="2"/>
-      <c r="Q111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B112" s="2"/>
-      <c r="C112" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="D112" s="2"/>
-      <c r="E112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P112" s="2"/>
-      <c r="Q112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D113" s="2"/>
-      <c r="E113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P113" s="2"/>
-      <c r="Q113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B114" s="2"/>
-      <c r="C114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D114" s="2"/>
-      <c r="E114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P114" s="2"/>
-      <c r="Q114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B115" s="2"/>
-      <c r="C115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D115" s="2"/>
-      <c r="E115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P115" s="2"/>
-      <c r="Q115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN115" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN115">
+  <autoFilter ref="A1:AN109">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15577,7 +14811,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI114">
+  <conditionalFormatting sqref="A2:AI108">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="639">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -606,9 +606,6 @@
   </si>
   <si>
     <t>ServiceRequest.identifier</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -5005,7 +5002,7 @@
         <v>85</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>187</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>86</v>
@@ -5017,16 +5014,16 @@
         <v>86</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="K24" t="s" s="2">
+      <c r="L24" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
@@ -5064,10 +5061,10 @@
         <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AB24" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AC24" t="s" s="2">
         <v>78</v>
@@ -5091,19 +5088,19 @@
         <v>97</v>
       </c>
       <c r="AJ24" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AL24" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>198</v>
       </c>
     </row>
     <row r="25">
@@ -5111,7 +5108,7 @@
         <v>186</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>78</v>
@@ -5133,16 +5130,16 @@
         <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="L25" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -5207,24 +5204,24 @@
         <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AK25" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AL25" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>198</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -5247,13 +5244,13 @@
         <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="K26" t="s" s="2">
+      <c r="L26" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -5304,28 +5301,28 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>78</v>
@@ -5336,7 +5333,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5362,10 +5359,10 @@
         <v>130</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>183</v>
@@ -5409,7 +5406,7 @@
         <v>133</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>78</v>
@@ -5418,7 +5415,7 @@
         <v>134</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
@@ -5439,7 +5436,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5450,7 +5447,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -5476,16 +5473,16 @@
         <v>105</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>78</v>
@@ -5510,31 +5507,31 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="X28" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="X28" t="s" s="2">
+      <c r="Y28" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE28" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
@@ -5555,7 +5552,7 @@
         <v>128</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5566,7 +5563,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5589,19 +5586,19 @@
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="K29" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="K29" t="s" s="2">
+      <c r="L29" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5626,31 +5623,31 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="X29" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="X29" t="s" s="2">
+      <c r="Y29" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="Z29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5668,10 +5665,10 @@
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5682,7 +5679,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5705,13 +5702,13 @@
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="K30" t="s" s="2">
+      <c r="L30" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -5762,28 +5759,28 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5794,7 +5791,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5820,10 +5817,10 @@
         <v>130</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>183</v>
@@ -5867,7 +5864,7 @@
         <v>133</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>78</v>
@@ -5876,7 +5873,7 @@
         <v>134</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
@@ -5897,7 +5894,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5908,7 +5905,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5931,19 +5928,19 @@
         <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="K32" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="K32" t="s" s="2">
+      <c r="L32" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O32" t="s" s="2">
         <v>78</v>
@@ -5992,7 +5989,7 @@
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6010,10 +6007,10 @@
         <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6024,7 +6021,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6047,13 +6044,13 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K33" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="K33" t="s" s="2">
+      <c r="L33" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -6104,28 +6101,28 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6136,7 +6133,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -6162,10 +6159,10 @@
         <v>130</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>183</v>
@@ -6209,7 +6206,7 @@
         <v>133</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>78</v>
@@ -6218,7 +6215,7 @@
         <v>134</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
@@ -6239,7 +6236,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6250,7 +6247,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -6276,16 +6273,16 @@
         <v>99</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>78</v>
@@ -6334,7 +6331,7 @@
         <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
@@ -6352,10 +6349,10 @@
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6366,7 +6363,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6389,16 +6386,16 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
@@ -6448,7 +6445,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6466,10 +6463,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6480,7 +6477,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6506,14 +6503,14 @@
         <v>105</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
@@ -6523,7 +6520,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6562,7 +6559,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6580,10 +6577,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6594,7 +6591,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6617,17 +6614,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6676,7 +6673,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6694,10 +6691,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6708,7 +6705,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6731,19 +6728,19 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="K39" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="K39" t="s" s="2">
+      <c r="L39" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6792,7 +6789,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6810,10 +6807,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6824,7 +6821,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6847,19 +6844,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6908,7 +6905,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6926,10 +6923,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6940,7 +6937,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6966,16 +6963,16 @@
         <v>99</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -6988,43 +6985,43 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE41" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7042,10 +7039,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7056,7 +7053,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7079,16 +7076,16 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -7102,43 +7099,43 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE42" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7156,10 +7153,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7170,7 +7167,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7193,13 +7190,13 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="K43" t="s" s="2">
+      <c r="L43" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -7250,7 +7247,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7268,10 +7265,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7282,7 +7279,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7305,16 +7302,16 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="K44" t="s" s="2">
+      <c r="L44" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
@@ -7364,7 +7361,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7382,10 +7379,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7396,7 +7393,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7419,16 +7416,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="K45" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="K45" t="s" s="2">
+      <c r="L45" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7478,7 +7475,7 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
@@ -7493,13 +7490,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AK45" t="s" s="2">
+      <c r="AL45" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7510,7 +7507,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7536,13 +7533,13 @@
         <v>99</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7592,7 +7589,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7607,13 +7604,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7624,11 +7621,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7647,13 +7644,13 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="K47" t="s" s="2">
+      <c r="L47" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7704,7 +7701,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7719,13 +7716,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AK47" t="s" s="2">
+      <c r="AL47" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7736,11 +7733,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7759,13 +7756,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7816,7 +7813,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7831,13 +7828,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AK48" t="s" s="2">
+      <c r="AL48" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7848,11 +7845,11 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7871,19 +7868,19 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>78</v>
@@ -7932,7 +7929,7 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
@@ -7947,13 +7944,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AK49" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AK49" t="s" s="2">
+      <c r="AL49" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7964,7 +7961,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7990,13 +7987,13 @@
         <v>105</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -8022,14 +8019,14 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="Y50" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="Y50" t="s" s="2">
-        <v>366</v>
-      </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8046,7 +8043,7 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>85</v>
@@ -8061,24 +8058,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AK50" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AK50" t="s" s="2">
+      <c r="AL50" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8104,13 +8101,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8136,14 +8133,14 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="Y51" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8160,7 +8157,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8175,16 +8172,16 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8192,7 +8189,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8215,19 +8212,19 @@
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
@@ -8252,14 +8249,14 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="X52" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="X52" t="s" s="2">
+      <c r="Y52" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8276,7 +8273,7 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>76</v>
@@ -8294,13 +8291,13 @@
         <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AM52" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8308,7 +8305,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8331,13 +8328,13 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="K53" t="s" s="2">
+      <c r="L53" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -8388,28 +8385,28 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
@@ -8420,7 +8417,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8446,10 +8443,10 @@
         <v>130</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>183</v>
@@ -8493,7 +8490,7 @@
         <v>133</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>78</v>
@@ -8502,7 +8499,7 @@
         <v>134</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
@@ -8523,7 +8520,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8534,7 +8531,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8557,19 +8554,19 @@
         <v>86</v>
       </c>
       <c r="J55" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="K55" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="K55" t="s" s="2">
+      <c r="L55" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>78</v>
@@ -8618,7 +8615,7 @@
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8636,10 +8633,10 @@
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8650,7 +8647,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8673,13 +8670,13 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K56" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="K56" t="s" s="2">
+      <c r="L56" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -8730,28 +8727,28 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8762,7 +8759,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8788,10 +8785,10 @@
         <v>130</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>183</v>
@@ -8835,7 +8832,7 @@
         <v>133</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC57" t="s" s="2">
         <v>78</v>
@@ -8844,7 +8841,7 @@
         <v>134</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
@@ -8865,7 +8862,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8876,7 +8873,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8902,16 +8899,16 @@
         <v>99</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>78</v>
@@ -8960,7 +8957,7 @@
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
@@ -8978,10 +8975,10 @@
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8992,7 +8989,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9015,16 +9012,16 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
@@ -9074,7 +9071,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9092,10 +9089,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9106,7 +9103,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9132,14 +9129,14 @@
         <v>105</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
@@ -9164,11 +9161,11 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X60" s="2"/>
       <c r="Y60" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9186,7 +9183,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9204,10 +9201,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9218,7 +9215,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9241,17 +9238,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9300,7 +9297,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9318,10 +9315,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9332,7 +9329,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9355,19 +9352,19 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="K62" t="s" s="2">
+      <c r="L62" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9416,7 +9413,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9434,10 +9431,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9448,7 +9445,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9471,19 +9468,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9532,7 +9529,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9550,10 +9547,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9564,7 +9561,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9590,10 +9587,10 @@
         <v>105</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -9601,35 +9598,35 @@
         <v>78</v>
       </c>
       <c r="P64" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Q64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="X64" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="X64" t="s" s="2">
+      <c r="Y64" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Y64" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9646,7 +9643,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9661,16 +9658,16 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AK64" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AK64" t="s" s="2">
+      <c r="AL64" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9678,7 +9675,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9701,26 +9698,26 @@
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P65" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="O65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9764,7 +9761,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9779,13 +9776,13 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9796,7 +9793,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9819,13 +9816,13 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -9876,7 +9873,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9908,7 +9905,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9986,7 +9983,7 @@
         <v>134</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
@@ -10018,10 +10015,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="C68" t="s" s="2">
         <v>78</v>
@@ -10043,13 +10040,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10100,7 +10097,7 @@
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10132,7 +10129,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -10155,13 +10152,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10212,7 +10209,7 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
@@ -10244,11 +10241,11 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10267,16 +10264,16 @@
         <v>86</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
@@ -10302,14 +10299,14 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X70" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Y70" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="Y70" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10326,7 +10323,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10341,28 +10338,28 @@
         <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AK70" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AK70" t="s" s="2">
+      <c r="AL70" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AM70" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10381,16 +10378,16 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10416,14 +10413,14 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Y71" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Y71" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10440,7 +10437,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10449,7 +10446,7 @@
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>97</v>
@@ -10458,21 +10455,21 @@
         <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10495,17 +10492,17 @@
         <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="K72" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="K72" t="s" s="2">
+      <c r="L72" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>78</v>
@@ -10554,7 +10551,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
@@ -10572,10 +10569,10 @@
         <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10586,7 +10583,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10609,13 +10606,13 @@
         <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="K73" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="K73" t="s" s="2">
+      <c r="L73" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -10666,7 +10663,7 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>85</v>
@@ -10681,28 +10678,28 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AK73" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AK73" t="s" s="2">
+      <c r="AL73" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AL73" t="s" s="2">
+      <c r="AM73" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10721,13 +10718,13 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="K74" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="K74" t="s" s="2">
+      <c r="L74" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10778,7 +10775,7 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
@@ -10793,28 +10790,28 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AK74" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AK74" t="s" s="2">
+      <c r="AL74" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AL74" t="s" s="2">
+      <c r="AM74" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>476</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10833,13 +10830,13 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="K75" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="K75" t="s" s="2">
+      <c r="L75" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -10890,7 +10887,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10905,24 +10902,24 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AK75" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AK75" t="s" s="2">
+      <c r="AL75" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>486</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10945,13 +10942,13 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="K76" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="K76" t="s" s="2">
+      <c r="L76" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -10978,14 +10975,14 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X76" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Y76" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="Y76" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11002,7 +10999,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11023,22 +11020,22 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>494</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11057,13 +11054,13 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="K77" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="K77" t="s" s="2">
+      <c r="L77" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -11114,7 +11111,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11129,28 +11126,28 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AK77" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AK77" t="s" s="2">
+      <c r="AL77" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AL77" t="s" s="2">
+      <c r="AM77" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AM77" t="s" s="2">
+      <c r="AN77" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11169,16 +11166,16 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="K78" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="K78" t="s" s="2">
+      <c r="L78" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
@@ -11228,7 +11225,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -11243,28 +11240,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AK78" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AK78" t="s" s="2">
+      <c r="AL78" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AL78" t="s" s="2">
+      <c r="AM78" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>515</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11283,16 +11280,16 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K79" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L79" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L79" t="s" s="2">
+      <c r="M79" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
@@ -11318,14 +11315,14 @@
         <v>78</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X79" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="Y79" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="Y79" t="s" s="2">
-        <v>522</v>
-      </c>
       <c r="Z79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11342,7 +11339,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11357,16 +11354,16 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AK79" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AK79" t="s" s="2">
+      <c r="AL79" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="AL79" t="s" s="2">
+      <c r="AM79" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11374,11 +11371,11 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11397,16 +11394,16 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="K80" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="K80" t="s" s="2">
+      <c r="L80" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
@@ -11456,7 +11453,7 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
@@ -11471,16 +11468,16 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AK80" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="AK80" t="s" s="2">
+      <c r="AL80" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="AL80" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="AM80" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11488,7 +11485,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -11511,13 +11508,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11544,14 +11541,14 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X81" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="Y81" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="Y81" t="s" s="2">
-        <v>540</v>
-      </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11568,7 +11565,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
@@ -11589,10 +11586,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11600,7 +11597,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -11623,13 +11620,13 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K82" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="K82" t="s" s="2">
+      <c r="L82" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11680,28 +11677,28 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11712,7 +11709,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11738,10 +11735,10 @@
         <v>130</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="M83" t="s" s="2">
         <v>183</v>
@@ -11785,7 +11782,7 @@
         <v>133</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC83" t="s" s="2">
         <v>78</v>
@@ -11794,7 +11791,7 @@
         <v>134</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
@@ -11815,7 +11812,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11826,7 +11823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11849,19 +11846,19 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="K84" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="K84" t="s" s="2">
+      <c r="L84" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>78</v>
@@ -11886,11 +11883,11 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X84" s="2"/>
       <c r="Y84" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11908,7 +11905,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -11926,10 +11923,10 @@
         <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11940,7 +11937,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -11963,13 +11960,13 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K85" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="K85" t="s" s="2">
+      <c r="L85" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -12020,28 +12017,28 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL85" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -12052,7 +12049,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
@@ -12078,10 +12075,10 @@
         <v>130</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>183</v>
@@ -12125,7 +12122,7 @@
         <v>133</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC86" t="s" s="2">
         <v>78</v>
@@ -12134,7 +12131,7 @@
         <v>134</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12155,7 +12152,7 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -12166,7 +12163,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
@@ -12192,16 +12189,16 @@
         <v>99</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>78</v>
@@ -12250,7 +12247,7 @@
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
@@ -12268,10 +12265,10 @@
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL87" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12282,7 +12279,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12305,16 +12302,16 @@
         <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
@@ -12364,7 +12361,7 @@
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12382,10 +12379,10 @@
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AL88" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12396,7 +12393,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12422,14 +12419,14 @@
         <v>105</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
@@ -12478,7 +12475,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12496,10 +12493,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12510,7 +12507,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12533,17 +12530,17 @@
         <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
@@ -12592,7 +12589,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12610,10 +12607,10 @@
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL90" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12624,7 +12621,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12647,19 +12644,19 @@
         <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="K91" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="K91" t="s" s="2">
+      <c r="L91" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12708,7 +12705,7 @@
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12726,10 +12723,10 @@
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL91" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12740,7 +12737,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12763,19 +12760,19 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
@@ -12824,7 +12821,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12842,10 +12839,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL92" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12856,7 +12853,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12879,13 +12876,13 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -12936,7 +12933,7 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
@@ -12957,10 +12954,10 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12968,7 +12965,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -12991,16 +12988,16 @@
         <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
@@ -13026,14 +13023,14 @@
         <v>78</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X94" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="Y94" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="Y94" t="s" s="2">
-        <v>563</v>
-      </c>
       <c r="Z94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13050,7 +13047,7 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
@@ -13065,16 +13062,16 @@
         <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AK94" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AK94" t="s" s="2">
+      <c r="AL94" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="AL94" t="s" s="2">
+      <c r="AM94" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13082,7 +13079,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13105,16 +13102,16 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="K95" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="K95" t="s" s="2">
+      <c r="L95" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
@@ -13164,7 +13161,7 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13179,16 +13176,16 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AK95" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="AK95" t="s" s="2">
+      <c r="AL95" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AL95" t="s" s="2">
-        <v>575</v>
-      </c>
       <c r="AM95" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13196,7 +13193,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13219,13 +13216,13 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="K96" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="K96" t="s" s="2">
+      <c r="L96" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -13276,7 +13273,7 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
@@ -13291,13 +13288,13 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AK96" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="AK96" t="s" s="2">
+      <c r="AL96" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13308,11 +13305,11 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13331,16 +13328,16 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="K97" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="K97" t="s" s="2">
+      <c r="L97" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
@@ -13378,10 +13375,10 @@
         <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AB97" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AC97" t="s" s="2">
         <v>78</v>
@@ -13390,7 +13387,7 @@
         <v>134</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13405,13 +13402,13 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK97" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK97" t="s" s="2">
+      <c r="AL97" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13422,13 +13419,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C98" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C98" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13447,16 +13444,16 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13506,7 +13503,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13521,13 +13518,13 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK98" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK98" t="s" s="2">
+      <c r="AL98" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13538,13 +13535,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13563,16 +13560,16 @@
         <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="K99" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="K99" t="s" s="2">
+      <c r="L99" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13622,7 +13619,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13637,13 +13634,13 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK99" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK99" t="s" s="2">
+      <c r="AL99" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -13654,13 +13651,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -13679,16 +13676,16 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13738,7 +13735,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13753,13 +13750,13 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK100" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK100" t="s" s="2">
+      <c r="AL100" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13770,13 +13767,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13795,16 +13792,16 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13854,7 +13851,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13869,13 +13866,13 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK101" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK101" t="s" s="2">
+      <c r="AL101" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13886,13 +13883,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>146</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13911,16 +13908,16 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -13970,7 +13967,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -13985,13 +13982,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK102" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK102" t="s" s="2">
+      <c r="AL102" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14002,13 +13999,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14027,16 +14024,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14086,7 +14083,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14101,13 +14098,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK103" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK103" t="s" s="2">
+      <c r="AL103" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14118,13 +14115,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14143,16 +14140,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14202,7 +14199,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14217,13 +14214,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AK104" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="AK104" t="s" s="2">
+      <c r="AL104" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14234,7 +14231,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" t="s" s="2">
@@ -14257,16 +14254,16 @@
         <v>86</v>
       </c>
       <c r="J105" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="K105" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="K105" t="s" s="2">
+      <c r="L105" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14316,7 +14313,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14334,10 +14331,10 @@
         <v>78</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14348,11 +14345,11 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14371,19 +14368,19 @@
         <v>86</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>78</v>
@@ -14408,14 +14405,14 @@
         <v>78</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X106" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="Y106" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="Y106" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="Z106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14432,7 +14429,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14450,21 +14447,21 @@
         <v>78</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN106" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>622</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" t="s" s="2">
@@ -14487,13 +14484,13 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -14544,7 +14541,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14559,24 +14556,24 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AK107" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL107" t="s" s="2">
+      <c r="AM107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>628</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" t="s" s="2">
@@ -14599,13 +14596,13 @@
         <v>86</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L108" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -14656,7 +14653,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14674,10 +14671,10 @@
         <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14688,7 +14685,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" t="s" s="2">
@@ -14711,16 +14708,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="K109" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="K109" t="s" s="2">
+      <c r="L109" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14770,7 +14767,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14785,13 +14782,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$113</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="645">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -582,6 +582,16 @@
     <t>SubEspecialidad Médica Destino Código</t>
   </si>
   <si>
+    <t>PertinenciaInterconsulta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/PertinenciaInterconsulta}
+</t>
+  </si>
+  <si>
+    <t>Pertinencia Interconsulta</t>
+  </si>
+  <si>
     <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
@@ -621,13 +631,6 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
-    <t>value:type.coding.code}
-value:type.coding.system}</t>
-  </si>
-  <si>
-    <t>Slice creado para almacenar los identificadores</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -641,9 +644,6 @@
   </si>
   <si>
     <t>ClinicalStatement.identifier</t>
-  </si>
-  <si>
-    <t>IdInterconsulta</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
@@ -841,6 +841,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>IdInterconsulta</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -1270,9 +1273,6 @@
     <t>ServiceRequest.priority</t>
   </si>
   <si>
-    <t>Pertinencia Interconsulta</t>
-  </si>
-  <si>
     <t>Indicates how quickly the ServiceRequest should be addressed with respect to other requests.</t>
   </si>
   <si>
@@ -1333,11 +1333,14 @@
     <t>ServiceRequest.doNotPerform.extension</t>
   </si>
   <si>
-    <t>PertinenciaInterconsulta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/PertinenciaInterconsulta}
+    <t>MotivoNoPertinenciaCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MotivoNoPertinenciaCodigo}
 </t>
+  </si>
+  <si>
+    <t>Motivo No Pertinencia Codigo</t>
   </si>
   <si>
     <t>ServiceRequest.doNotPerform.value</t>
@@ -1387,6 +1390,21 @@
   </si>
   <si>
     <t>Procedure.procedureCode</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.text</t>
+  </si>
+  <si>
+    <t>derivado a especialidad</t>
   </si>
   <si>
     <t>ServiceRequest.orderDetail</t>
@@ -2320,7 +2338,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN109"/>
+  <dimension ref="A1:AN113"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -2349,8 +2367,8 @@
     <col min="24" max="24" width="255.0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="25.8515625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="44.640625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
@@ -4873,45 +4891,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>181</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4959,7 +4975,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -4968,7 +4984,7 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>136</v>
@@ -4980,7 +4996,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4991,41 +5007,43 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I24" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="K24" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5061,19 +5079,19 @@
         <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="AC24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5085,43 +5103,41 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -5130,16 +5146,16 @@
         <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -5189,7 +5205,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5201,22 +5217,22 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5337,7 +5353,7 @@
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -5365,7 +5381,7 @@
         <v>207</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
@@ -5795,7 +5811,7 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5823,7 +5839,7 @@
         <v>207</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
@@ -6137,7 +6153,7 @@
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -6165,7 +6181,7 @@
         <v>207</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
@@ -6520,7 +6536,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6559,7 +6575,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6577,10 +6593,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6591,7 +6607,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6617,14 +6633,14 @@
         <v>200</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6673,7 +6689,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6691,10 +6707,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6705,7 +6721,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6728,19 +6744,19 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6789,7 +6805,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6807,10 +6823,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6821,7 +6837,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6847,16 +6863,16 @@
         <v>200</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6905,7 +6921,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6923,10 +6939,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6937,7 +6953,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6963,16 +6979,16 @@
         <v>99</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -6985,7 +7001,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7021,7 +7037,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7039,10 +7055,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7053,7 +7069,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7079,13 +7095,13 @@
         <v>200</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -7099,7 +7115,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7135,7 +7151,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7153,10 +7169,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7167,7 +7183,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7190,13 +7206,13 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -7247,7 +7263,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7265,10 +7281,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7279,7 +7295,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7302,16 +7318,16 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
@@ -7361,7 +7377,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7379,10 +7395,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7393,7 +7409,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7416,16 +7432,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7475,7 +7491,7 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
@@ -7490,13 +7506,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7507,7 +7523,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7533,13 +7549,13 @@
         <v>99</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7589,7 +7605,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7604,13 +7620,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7621,11 +7637,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7644,13 +7660,13 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7701,7 +7717,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7716,13 +7732,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7733,11 +7749,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7756,13 +7772,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7813,7 +7829,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7828,13 +7844,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7845,11 +7861,11 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7868,19 +7884,19 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O49" t="s" s="2">
         <v>78</v>
@@ -7929,7 +7945,7 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
@@ -7944,13 +7960,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7961,7 +7977,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7987,13 +8003,13 @@
         <v>105</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
@@ -8022,10 +8038,10 @@
         <v>215</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8043,7 +8059,7 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>85</v>
@@ -8058,24 +8074,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8101,13 +8117,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8136,10 +8152,10 @@
         <v>215</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8157,7 +8173,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8172,16 +8188,16 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8189,7 +8205,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8215,16 +8231,16 @@
         <v>221</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
@@ -8249,13 +8265,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8273,7 +8289,7 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>76</v>
@@ -8291,13 +8307,13 @@
         <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8305,7 +8321,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8417,11 +8433,11 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8449,7 +8465,7 @@
         <v>207</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -8531,7 +8547,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8647,7 +8663,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8759,11 +8775,11 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8791,7 +8807,7 @@
         <v>207</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
@@ -8873,7 +8889,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8881,7 +8897,7 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>85</v>
@@ -8989,7 +9005,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9103,7 +9119,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9165,7 +9181,7 @@
       </c>
       <c r="X60" s="2"/>
       <c r="Y60" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9183,7 +9199,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9201,10 +9217,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9215,7 +9231,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9241,14 +9257,14 @@
         <v>200</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9297,7 +9313,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9315,10 +9331,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9329,7 +9345,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9352,19 +9368,19 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9413,7 +9429,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9431,10 +9447,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9445,7 +9461,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9471,16 +9487,16 @@
         <v>200</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9529,7 +9545,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9547,10 +9563,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9561,7 +9577,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9587,7 +9603,7 @@
         <v>105</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>403</v>
+        <v>181</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>404</v>
@@ -9643,7 +9659,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9698,7 +9714,7 @@
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>413</v>
@@ -10043,10 +10059,10 @@
         <v>425</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10129,7 +10145,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -10152,13 +10168,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10209,7 +10225,7 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
@@ -10239,13 +10255,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10255,7 +10271,7 @@
         <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10267,13 +10283,13 @@
         <v>221</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
@@ -10299,13 +10315,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10323,7 +10339,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10338,35 +10354,35 @@
         <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>78</v>
@@ -10375,20 +10391,18 @@
         <v>78</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>444</v>
+        <v>201</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>78</v>
@@ -10413,13 +10427,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>447</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10437,50 +10451,50 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>442</v>
+        <v>203</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>439</v>
+        <v>204</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>78</v>
@@ -10489,21 +10503,21 @@
         <v>78</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>452</v>
+        <v>130</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>453</v>
+        <v>206</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M72" s="2"/>
-      <c r="N72" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10539,40 +10553,40 @@
         <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AC72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD72" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>451</v>
+        <v>209</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>456</v>
+        <v>204</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10581,9 +10595,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10591,13 +10605,13 @@
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10606,16 +10620,20 @@
         <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>458</v>
+        <v>234</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>459</v>
+        <v>235</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10663,13 +10681,13 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>457</v>
+        <v>239</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>78</v>
@@ -10678,38 +10696,38 @@
         <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>461</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>462</v>
+        <v>240</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>463</v>
+        <v>241</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>464</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>465</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10718,16 +10736,20 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>468</v>
+        <v>200</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>469</v>
+        <v>284</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10736,7 +10758,7 @@
         <v>78</v>
       </c>
       <c r="R74" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>78</v>
@@ -10775,7 +10797,7 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>466</v>
+        <v>288</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
@@ -10790,35 +10812,35 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>471</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>472</v>
+        <v>289</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>473</v>
+        <v>290</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>474</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>477</v>
+        <v>449</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>78</v>
@@ -10830,15 +10852,17 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>478</v>
+        <v>221</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M75" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
         <v>78</v>
@@ -10863,13 +10887,13 @@
         <v>78</v>
       </c>
       <c r="W75" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>78</v>
@@ -10887,39 +10911,39 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>481</v>
+        <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>483</v>
+        <v>440</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>485</v>
+        <v>442</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>457</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10942,16 +10966,18 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
+      <c r="N76" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10975,13 +11001,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>490</v>
+        <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>491</v>
+        <v>78</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -10999,7 +11025,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>486</v>
+        <v>457</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11017,29 +11043,29 @@
         <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>493</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>85</v>
@@ -11054,13 +11080,13 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>498</v>
+        <v>466</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -11111,10 +11137,10 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>85</v>
@@ -11126,28 +11152,28 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>503</v>
+        <v>471</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -11157,7 +11183,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11166,17 +11192,15 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
@@ -11225,7 +11249,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -11240,28 +11264,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>510</v>
+        <v>477</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>513</v>
+        <v>480</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>514</v>
+        <v>481</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>516</v>
+        <v>483</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11280,17 +11304,15 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>221</v>
+        <v>484</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>517</v>
+        <v>485</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
         <v>78</v>
@@ -11315,13 +11337,13 @@
         <v>78</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>521</v>
+        <v>78</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>78</v>
@@ -11339,7 +11361,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>515</v>
+        <v>482</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11354,35 +11376,35 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>522</v>
+        <v>487</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>523</v>
+        <v>488</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>524</v>
+        <v>489</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>525</v>
+        <v>490</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>527</v>
+        <v>78</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>78</v>
@@ -11394,17 +11416,15 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>528</v>
+        <v>493</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>529</v>
+        <v>494</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
         <v>78</v>
@@ -11429,13 +11449,13 @@
         <v>78</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
+        <v>496</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>78</v>
@@ -11453,13 +11473,13 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>526</v>
+        <v>492</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>78</v>
@@ -11468,28 +11488,28 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>534</v>
+        <v>498</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>78</v>
+        <v>499</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>535</v>
+        <v>500</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>78</v>
+        <v>501</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11508,13 +11528,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>221</v>
+        <v>502</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>536</v>
+        <v>503</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>537</v>
+        <v>504</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11541,13 +11561,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>538</v>
+        <v>78</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>539</v>
+        <v>78</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11565,13 +11585,13 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>535</v>
+        <v>500</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>78</v>
@@ -11580,28 +11600,28 @@
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>506</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>78</v>
+        <v>509</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>541</v>
+        <v>510</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>78</v>
+        <v>511</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11611,24 +11631,26 @@
         <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>200</v>
+        <v>512</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>201</v>
+        <v>513</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M82" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>78</v>
@@ -11677,7 +11699,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>203</v>
+        <v>510</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11689,38 +11711,38 @@
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>78</v>
+        <v>516</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>204</v>
+        <v>518</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>519</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>78</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>180</v>
+        <v>522</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>78</v>
@@ -11729,19 +11751,19 @@
         <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>130</v>
+        <v>221</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>206</v>
+        <v>523</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>207</v>
+        <v>524</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>183</v>
+        <v>525</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
@@ -11767,77 +11789,77 @@
         <v>78</v>
       </c>
       <c r="W83" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>209</v>
+        <v>521</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>78</v>
+        <v>528</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>204</v>
+        <v>530</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11846,20 +11868,18 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>234</v>
+        <v>534</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>235</v>
+        <v>535</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>236</v>
+        <v>536</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11883,11 +11903,13 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="X84" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y84" t="s" s="2">
-        <v>544</v>
+        <v>78</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11905,7 +11927,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>239</v>
+        <v>532</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -11920,24 +11942,24 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>78</v>
+        <v>538</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>240</v>
+        <v>539</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>241</v>
+        <v>540</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -11951,22 +11973,22 @@
         <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>201</v>
+        <v>542</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>202</v>
+        <v>543</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -11993,13 +12015,13 @@
         <v>78</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>78</v>
@@ -12017,19 +12039,19 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>203</v>
+        <v>541</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>78</v>
@@ -12038,10 +12060,10 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>204</v>
+        <v>546</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12049,18 +12071,18 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>78</v>
@@ -12072,17 +12094,15 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
@@ -12119,31 +12139,31 @@
         <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD86" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
@@ -12161,45 +12181,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>246</v>
+        <v>207</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12235,40 +12253,40 @@
         <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AC87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>251</v>
+        <v>204</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12277,9 +12295,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12287,13 +12305,13 @@
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12302,18 +12320,20 @@
         <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12337,13 +12357,11 @@
         <v>78</v>
       </c>
       <c r="W88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="X88" s="2"/>
       <c r="Y88" t="s" s="2">
-        <v>78</v>
+        <v>550</v>
       </c>
       <c r="Z88" t="s" s="2">
         <v>78</v>
@@ -12361,13 +12379,13 @@
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>78</v>
@@ -12379,10 +12397,10 @@
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12391,9 +12409,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12401,33 +12419,31 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="M89" s="2"/>
-      <c r="N89" t="s" s="2">
-        <v>262</v>
-      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12475,7 +12491,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>263</v>
+        <v>203</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12487,16 +12503,16 @@
         <v>78</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>264</v>
+        <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>265</v>
+        <v>204</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12505,43 +12521,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M90" s="2"/>
-      <c r="N90" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12577,40 +12593,40 @@
         <v>78</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="AC90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>270</v>
+        <v>209</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>272</v>
+        <v>204</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12619,9 +12635,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12629,13 +12645,13 @@
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -12644,19 +12660,19 @@
         <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>274</v>
+        <v>99</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12705,7 +12721,7 @@
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12723,10 +12739,10 @@
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12737,7 +12753,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12763,17 +12779,15 @@
         <v>200</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12821,7 +12835,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12839,10 +12853,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12851,9 +12865,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12861,13 +12875,13 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12876,16 +12890,18 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>554</v>
+        <v>105</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>536</v>
+        <v>260</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>555</v>
+        <v>261</v>
       </c>
       <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
+      <c r="N93" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="O93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12933,13 +12949,13 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>553</v>
+        <v>264</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>78</v>
@@ -12951,13 +12967,13 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>78</v>
+        <v>265</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>556</v>
+        <v>266</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12965,7 +12981,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -12988,18 +13004,18 @@
         <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>558</v>
+        <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="M94" s="2"/>
+      <c r="N94" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13023,13 +13039,13 @@
         <v>78</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>561</v>
+        <v>78</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>562</v>
+        <v>78</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>78</v>
@@ -13047,13 +13063,13 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>557</v>
+        <v>271</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
@@ -13062,16 +13078,16 @@
         <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>564</v>
+        <v>272</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>565</v>
+        <v>273</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>566</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13079,7 +13095,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13090,7 +13106,7 @@
         <v>76</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>78</v>
@@ -13102,18 +13118,20 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>568</v>
+        <v>275</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>569</v>
+        <v>276</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>570</v>
+        <v>277</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13161,13 +13179,13 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>567</v>
+        <v>280</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>78</v>
@@ -13176,16 +13194,16 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>572</v>
+        <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>573</v>
+        <v>281</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>574</v>
+        <v>282</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>566</v>
+        <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13193,7 +13211,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13204,7 +13222,7 @@
         <v>76</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>78</v>
@@ -13213,19 +13231,23 @@
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>576</v>
+        <v>200</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>577</v>
+        <v>284</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13273,13 +13295,13 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>575</v>
+        <v>288</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>78</v>
@@ -13288,13 +13310,13 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>579</v>
+        <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>580</v>
+        <v>289</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>581</v>
+        <v>290</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13305,11 +13327,11 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>583</v>
+        <v>78</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -13319,26 +13341,24 @@
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I97" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J97" t="s" s="2">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>585</v>
+        <v>542</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="M97" s="2"/>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
         <v>78</v>
@@ -13375,19 +13395,19 @@
         <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>588</v>
+        <v>78</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>589</v>
+        <v>78</v>
       </c>
       <c r="AC97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13402,16 +13422,16 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>590</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>591</v>
+        <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>592</v>
+        <v>562</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13419,13 +13439,11 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
-        <v>583</v>
+        <v>78</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -13441,19 +13459,19 @@
         <v>78</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>594</v>
+        <v>221</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
@@ -13479,13 +13497,13 @@
         <v>78</v>
       </c>
       <c r="W98" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>78</v>
+        <v>567</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>78</v>
@@ -13503,7 +13521,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>582</v>
+        <v>563</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13518,58 +13536,56 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>78</v>
+        <v>572</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
-        <v>583</v>
+        <v>78</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I99" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J99" t="s" s="2">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13619,7 +13635,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13634,40 +13650,38 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>78</v>
+        <v>572</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
-        <v>583</v>
+        <v>78</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13676,17 +13690,15 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
         <v>78</v>
@@ -13735,7 +13747,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13750,13 +13762,13 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13765,22 +13777,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>86</v>
@@ -13792,16 +13802,16 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13839,19 +13849,19 @@
         <v>78</v>
       </c>
       <c r="AA101" t="s" s="2">
-        <v>78</v>
+        <v>594</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="AC101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD101" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13866,13 +13876,13 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13883,13 +13893,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>146</v>
+        <v>599</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13911,13 +13921,13 @@
         <v>600</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -13967,7 +13977,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -13982,13 +13992,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -13999,13 +14009,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>601</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14024,16 +14034,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14083,7 +14093,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14098,13 +14108,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14115,13 +14125,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14140,16 +14150,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14199,7 +14209,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14214,13 +14224,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14229,41 +14239,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B105" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>604</v>
+      </c>
       <c r="C105" t="s" s="2">
-        <v>78</v>
+        <v>589</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14313,7 +14325,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14328,13 +14340,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14343,45 +14355,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="B106" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="C106" t="s" s="2">
-        <v>613</v>
+        <v>589</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>221</v>
+        <v>606</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>615</v>
+        <v>592</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>617</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14405,13 +14417,13 @@
         <v>78</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>618</v>
+        <v>78</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>619</v>
+        <v>78</v>
       </c>
       <c r="Z106" t="s" s="2">
         <v>78</v>
@@ -14429,7 +14441,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>612</v>
+        <v>588</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14444,38 +14456,40 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>621</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B107" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="C107" t="s" s="2">
-        <v>78</v>
+        <v>589</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14484,15 +14498,17 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>47</v>
+        <v>591</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M107" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
         <v>78</v>
@@ -14541,7 +14557,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>622</v>
+        <v>588</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14556,28 +14572,30 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>625</v>
+        <v>596</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>450</v>
+        <v>597</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>626</v>
+        <v>598</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>627</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B108" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="C108" t="s" s="2">
-        <v>78</v>
+        <v>589</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14587,24 +14605,26 @@
         <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>200</v>
+        <v>610</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>629</v>
+        <v>591</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M108" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
         <v>78</v>
@@ -14653,13 +14673,13 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>628</v>
+        <v>588</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>78</v>
@@ -14668,13 +14688,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>450</v>
+        <v>597</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>631</v>
+        <v>598</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14685,7 +14705,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" t="s" s="2">
@@ -14705,19 +14725,19 @@
         <v>78</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14767,7 +14787,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14782,23 +14802,477 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B110" s="2"/>
+      <c r="C110" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="D110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P110" s="2"/>
+      <c r="Q110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B111" s="2"/>
+      <c r="C111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M111" s="2"/>
+      <c r="N111" s="2"/>
+      <c r="O111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B112" s="2"/>
+      <c r="C112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M112" s="2"/>
+      <c r="N112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P112" s="2"/>
+      <c r="Q112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AK109" t="s" s="2">
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AK113" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AL109" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN109" t="s" s="2">
+      <c r="AL113" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN109">
+  <autoFilter ref="A1:AN113">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14808,7 +15282,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI108">
+  <conditionalFormatting sqref="A2:AI112">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -580,6 +580,16 @@
   </si>
   <si>
     <t>SubEspecialidad Médica Destino Código</t>
+  </si>
+  <si>
+    <t>DestinoAtencionCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/DestinoAtencionCodigo}
+</t>
+  </si>
+  <si>
+    <t>Destino Atención Codigo</t>
   </si>
   <si>
     <t>PertinenciaInterconsulta</t>
@@ -2338,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN113"/>
+  <dimension ref="A1:AN114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -5005,45 +5015,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5091,7 +5099,7 @@
         <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5100,7 +5108,7 @@
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>136</v>
@@ -5112,7 +5120,7 @@
         <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>78</v>
@@ -5123,11 +5131,11 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -5140,24 +5148,26 @@
         <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="K25" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5205,7 +5215,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5217,27 +5227,27 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -5248,7 +5258,7 @@
         <v>76</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>78</v>
@@ -5257,18 +5267,20 @@
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M26" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>78</v>
@@ -5317,13 +5329,13 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>78</v>
@@ -5332,35 +5344,35 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>78</v>
@@ -5372,17 +5384,15 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
@@ -5419,31 +5429,31 @@
         <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>78</v>
@@ -5452,7 +5462,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5463,43 +5473,41 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5523,52 +5531,52 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5577,9 +5585,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5587,34 +5595,34 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5639,13 +5647,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5663,7 +5671,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5681,10 +5689,10 @@
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5693,9 +5701,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5703,31 +5711,35 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5751,13 +5763,13 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>78</v>
+        <v>229</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
@@ -5775,7 +5787,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5787,16 +5799,16 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5807,18 +5819,18 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>78</v>
@@ -5830,17 +5842,15 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>78</v>
@@ -5877,31 +5887,31 @@
         <v>78</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
@@ -5910,7 +5920,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5919,45 +5929,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5993,19 +6001,19 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6017,16 +6025,16 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6035,9 +6043,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6045,31 +6053,35 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6117,28 +6129,28 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6149,18 +6161,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>78</v>
@@ -6172,17 +6184,15 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>78</v>
@@ -6219,31 +6229,31 @@
         <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
@@ -6252,7 +6262,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6261,45 +6271,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6335,40 +6343,40 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6377,9 +6385,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6387,13 +6395,13 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -6402,18 +6410,20 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6461,7 +6471,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6479,10 +6489,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6491,9 +6501,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6501,13 +6511,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6516,18 +6526,18 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M37" s="2"/>
-      <c r="N37" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6536,7 +6546,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6575,7 +6585,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6593,10 +6603,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6607,7 +6617,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6615,7 +6625,7 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
@@ -6630,17 +6640,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6650,7 +6660,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6689,7 +6699,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6707,10 +6717,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6719,9 +6729,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6735,7 +6745,7 @@
         <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6744,19 +6754,17 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6805,7 +6813,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6823,10 +6831,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6837,7 +6845,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6860,19 +6868,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6921,7 +6929,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6939,10 +6947,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6953,7 +6961,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6976,19 +6984,19 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -7001,7 +7009,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7037,7 +7045,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7055,10 +7063,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7067,9 +7075,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7077,13 +7085,13 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7092,18 +7100,20 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7115,7 +7125,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7151,7 +7161,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7169,10 +7179,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7181,9 +7191,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7191,13 +7201,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7206,15 +7216,17 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>309</v>
+        <v>203</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="M43" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
         <v>78</v>
@@ -7227,7 +7239,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7263,7 +7275,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7281,10 +7293,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7295,7 +7307,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7318,17 +7330,15 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7377,7 +7387,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7395,10 +7405,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7409,7 +7419,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7420,7 +7430,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7432,16 +7442,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7497,7 +7507,7 @@
         <v>76</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>78</v>
@@ -7506,13 +7516,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7523,7 +7533,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7546,16 +7556,16 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>99</v>
+        <v>327</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7605,7 +7615,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7620,13 +7630,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7637,11 +7647,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7660,15 +7670,17 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M47" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7717,7 +7729,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7732,13 +7744,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7749,11 +7761,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7772,13 +7784,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7829,7 +7841,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7844,13 +7856,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7861,18 +7873,18 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>78</v>
@@ -7884,20 +7896,16 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>190</v>
+        <v>349</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7945,13 +7953,13 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -7960,13 +7968,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7975,43 +7983,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8035,13 +8045,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>365</v>
+        <v>78</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8059,10 +8069,10 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -8074,24 +8084,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8117,13 +8127,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8149,13 +8159,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8173,7 +8183,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8188,24 +8198,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>128</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8213,7 +8223,7 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>85</v>
@@ -8222,26 +8232,24 @@
         <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>221</v>
+        <v>105</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8265,13 +8273,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>386</v>
+        <v>218</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8289,13 +8297,13 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>78</v>
@@ -8304,24 +8312,24 @@
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>389</v>
+        <v>128</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8335,25 +8343,29 @@
         <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>201</v>
+        <v>385</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8377,13 +8389,13 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -8401,31 +8413,31 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>203</v>
+        <v>384</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>204</v>
+        <v>393</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8433,18 +8445,18 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>78</v>
@@ -8456,17 +8468,15 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>78</v>
@@ -8503,31 +8513,31 @@
         <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
@@ -8536,7 +8546,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8545,45 +8555,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8619,19 +8627,19 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8643,16 +8651,16 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8661,9 +8669,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8671,31 +8679,35 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8743,28 +8755,28 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8775,18 +8787,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>78</v>
@@ -8798,17 +8810,15 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>78</v>
@@ -8845,31 +8855,31 @@
         <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
@@ -8878,7 +8888,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8887,45 +8897,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8961,40 +8969,40 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9003,9 +9011,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9019,7 +9027,7 @@
         <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -9028,18 +9036,20 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9087,7 +9097,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9105,10 +9115,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9117,9 +9127,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9127,13 +9137,13 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9142,18 +9152,18 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M60" s="2"/>
-      <c r="N60" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9177,11 +9187,13 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="X60" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y60" t="s" s="2">
-        <v>399</v>
+        <v>78</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9199,7 +9211,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9217,10 +9229,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9231,7 +9243,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9239,7 +9251,7 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
@@ -9254,17 +9266,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9289,13 +9301,11 @@
         <v>78</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="X61" s="2"/>
       <c r="Y61" t="s" s="2">
-        <v>78</v>
+        <v>402</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9313,7 +9323,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9331,10 +9341,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9343,9 +9353,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9359,7 +9369,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9368,19 +9378,17 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M62" s="2"/>
       <c r="N62" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9429,7 +9437,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9447,10 +9455,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9461,7 +9469,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9484,19 +9492,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9545,7 +9553,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9563,10 +9571,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9575,9 +9583,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9591,7 +9599,7 @@
         <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9600,22 +9608,24 @@
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>181</v>
+        <v>287</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P64" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9635,13 +9645,13 @@
         <v>78</v>
       </c>
       <c r="W64" t="s" s="2">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>407</v>
+        <v>78</v>
       </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
@@ -9659,7 +9669,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>403</v>
+        <v>291</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9674,16 +9684,16 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>409</v>
+        <v>292</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>410</v>
+        <v>293</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9691,7 +9701,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9708,31 +9718,27 @@
         <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>275</v>
+        <v>105</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>413</v>
+        <v>184</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
@@ -9753,13 +9759,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9777,7 +9783,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9792,24 +9798,24 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9823,94 +9829,100 @@
         <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="Q66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="AK66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P66" s="2"/>
-      <c r="Q66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9932,7 +9944,7 @@
         <v>76</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>78</v>
@@ -9944,13 +9956,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>131</v>
+        <v>424</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>132</v>
+        <v>425</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -9989,29 +10001,31 @@
         <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB67" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -10029,13 +10043,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10044,10 +10056,10 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10056,13 +10068,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>425</v>
+        <v>130</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>426</v>
+        <v>131</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10101,19 +10113,17 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB68" s="2"/>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10122,7 +10132,7 @@
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>136</v>
@@ -10143,11 +10153,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10159,7 +10171,7 @@
         <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10168,10 +10180,10 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>275</v>
+        <v>428</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>429</v>
@@ -10225,43 +10237,43 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10271,26 +10283,24 @@
         <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>78</v>
@@ -10315,13 +10325,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>436</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10339,7 +10349,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10351,31 +10361,31 @@
         <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10385,24 +10395,26 @@
         <v>85</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>201</v>
+        <v>436</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M71" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>78</v>
@@ -10427,13 +10439,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10451,7 +10463,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>203</v>
+        <v>434</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10463,38 +10475,38 @@
         <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>204</v>
+        <v>443</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>78</v>
@@ -10506,17 +10518,15 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>78</v>
@@ -10553,31 +10563,31 @@
         <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD72" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>78</v>
@@ -10586,7 +10596,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10597,11 +10607,11 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10617,23 +10627,21 @@
         <v>78</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10669,19 +10677,19 @@
         <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD73" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>76</v>
@@ -10693,16 +10701,16 @@
         <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10711,9 +10719,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10721,13 +10729,13 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10736,19 +10744,19 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>78</v>
@@ -10758,7 +10766,7 @@
         <v>78</v>
       </c>
       <c r="R74" t="s" s="2">
-        <v>447</v>
+        <v>78</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>78</v>
@@ -10797,13 +10805,13 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>78</v>
@@ -10815,10 +10823,10 @@
         <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10827,23 +10835,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10852,18 +10860,20 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>450</v>
+        <v>287</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>451</v>
+        <v>288</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10872,7 +10882,7 @@
         <v>78</v>
       </c>
       <c r="R75" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -10887,13 +10897,13 @@
         <v>78</v>
       </c>
       <c r="W75" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>78</v>
@@ -10911,16 +10921,16 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>448</v>
+        <v>291</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>455</v>
+        <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>97</v>
@@ -10929,32 +10939,32 @@
         <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>456</v>
+        <v>292</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>440</v>
+        <v>293</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>78</v>
@@ -10966,18 +10976,18 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>458</v>
+        <v>224</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M76" s="2"/>
-      <c r="N76" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11001,13 +11011,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11025,16 +11035,16 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>78</v>
+        <v>458</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>97</v>
@@ -11043,21 +11053,21 @@
         <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -11065,13 +11075,13 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11080,16 +11090,18 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M77" s="2"/>
+      <c r="N77" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="K77" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11137,10 +11149,10 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>85</v>
@@ -11152,38 +11164,38 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>471</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>473</v>
+        <v>78</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11192,13 +11204,13 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -11249,10 +11261,10 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>85</v>
@@ -11264,28 +11276,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11304,13 +11316,13 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -11361,7 +11373,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11376,28 +11388,28 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11416,13 +11428,13 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -11449,13 +11461,13 @@
         <v>78</v>
       </c>
       <c r="W80" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>496</v>
+        <v>78</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>497</v>
+        <v>78</v>
       </c>
       <c r="Z80" t="s" s="2">
         <v>78</v>
@@ -11473,7 +11485,7 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
@@ -11488,28 +11500,28 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11519,7 +11531,7 @@
         <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11528,13 +11540,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11561,13 +11573,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>78</v>
+        <v>499</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11585,7 +11597,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
@@ -11600,28 +11612,28 @@
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11640,17 +11652,15 @@
         <v>86</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
         <v>78</v>
@@ -11699,7 +11709,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11714,28 +11724,28 @@
         <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11745,7 +11755,7 @@
         <v>85</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11754,16 +11764,16 @@
         <v>86</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>221</v>
+        <v>515</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
@@ -11789,13 +11799,13 @@
         <v>78</v>
       </c>
       <c r="W83" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>527</v>
+        <v>78</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
@@ -11813,7 +11823,7 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
@@ -11828,35 +11838,35 @@
         <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>78</v>
@@ -11868,16 +11878,16 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>534</v>
+        <v>224</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
@@ -11903,13 +11913,13 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>78</v>
+        <v>529</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>78</v>
+        <v>530</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11927,13 +11937,13 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>78</v>
@@ -11942,38 +11952,38 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>78</v>
+        <v>536</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -11982,15 +11992,17 @@
         <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>221</v>
+        <v>537</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="M85" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
         <v>78</v>
@@ -12015,13 +12027,13 @@
         <v>78</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>544</v>
+        <v>78</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>78</v>
@@ -12039,7 +12051,7 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
@@ -12054,24 +12066,24 @@
         <v>97</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>78</v>
+        <v>542</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
@@ -12085,22 +12097,22 @@
         <v>85</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>201</v>
+        <v>545</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>202</v>
+        <v>546</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -12127,13 +12139,13 @@
         <v>78</v>
       </c>
       <c r="W86" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>78</v>
+        <v>547</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>78</v>
+        <v>548</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>78</v>
@@ -12151,19 +12163,19 @@
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>203</v>
+        <v>544</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
@@ -12172,10 +12184,10 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>204</v>
+        <v>549</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12183,18 +12195,18 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>78</v>
@@ -12206,17 +12218,15 @@
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
         <v>78</v>
@@ -12253,31 +12263,31 @@
         <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
@@ -12286,7 +12296,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12295,45 +12305,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12357,29 +12365,31 @@
         <v>78</v>
       </c>
       <c r="W88" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="X88" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y88" t="s" s="2">
-        <v>550</v>
+        <v>78</v>
       </c>
       <c r="Z88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA88" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD88" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12391,16 +12401,16 @@
         <v>78</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12409,9 +12419,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12419,31 +12429,35 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>201</v>
+        <v>238</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12467,13 +12481,11 @@
         <v>78</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="X89" s="2"/>
       <c r="Y89" t="s" s="2">
-        <v>78</v>
+        <v>553</v>
       </c>
       <c r="Z89" t="s" s="2">
         <v>78</v>
@@ -12491,28 +12503,28 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>203</v>
+        <v>242</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12523,18 +12535,18 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
-        <v>183</v>
+        <v>78</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>78</v>
@@ -12546,17 +12558,15 @@
         <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
         <v>78</v>
@@ -12593,31 +12603,31 @@
         <v>78</v>
       </c>
       <c r="AA90" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>78</v>
@@ -12626,7 +12636,7 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12635,45 +12645,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12709,40 +12717,40 @@
         <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="AC91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD91" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12751,9 +12759,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12761,13 +12769,13 @@
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12776,18 +12784,20 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12835,7 +12845,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12853,10 +12863,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12865,9 +12875,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12875,13 +12885,13 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12890,18 +12900,18 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M93" s="2"/>
-      <c r="N93" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12949,7 +12959,7 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
@@ -12967,10 +12977,10 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -12981,7 +12991,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -12989,7 +12999,7 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>85</v>
@@ -13004,17 +13014,17 @@
         <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>78</v>
@@ -13063,7 +13073,7 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
@@ -13081,10 +13091,10 @@
         <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -13093,9 +13103,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13109,7 +13119,7 @@
         <v>85</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13118,19 +13128,17 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="M95" s="2"/>
       <c r="N95" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>78</v>
@@ -13179,7 +13187,7 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13197,10 +13205,10 @@
         <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13211,7 +13219,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13234,19 +13242,19 @@
         <v>86</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>78</v>
@@ -13295,7 +13303,7 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
@@ -13313,10 +13321,10 @@
         <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13327,7 +13335,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13338,7 +13346,7 @@
         <v>76</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>78</v>
@@ -13350,16 +13358,20 @@
         <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>560</v>
+        <v>203</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>542</v>
+        <v>287</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13407,13 +13419,13 @@
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>559</v>
+        <v>291</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>78</v>
@@ -13425,21 +13437,21 @@
         <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="AL97" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13450,10 +13462,10 @@
         <v>76</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13462,17 +13474,15 @@
         <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>221</v>
+        <v>563</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L98" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>566</v>
-      </c>
+      <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
         <v>78</v>
@@ -13497,13 +13507,13 @@
         <v>78</v>
       </c>
       <c r="W98" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>567</v>
+        <v>78</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="Z98" t="s" s="2">
         <v>78</v>
@@ -13521,7 +13531,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13536,24 +13546,24 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>569</v>
+        <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>570</v>
+        <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>572</v>
+        <v>534</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
@@ -13564,10 +13574,10 @@
         <v>76</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13576,16 +13586,16 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>574</v>
+        <v>224</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13611,13 +13621,13 @@
         <v>78</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>78</v>
+        <v>570</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>78</v>
+        <v>571</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>78</v>
@@ -13635,7 +13645,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13650,16 +13660,16 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13667,7 +13677,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13687,18 +13697,20 @@
         <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="M100" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
         <v>78</v>
@@ -13747,7 +13759,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13762,16 +13774,16 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>575</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13779,11 +13791,11 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
-        <v>589</v>
+        <v>78</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -13793,7 +13805,7 @@
         <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13802,17 +13814,15 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
         <v>78</v>
@@ -13849,19 +13859,19 @@
         <v>78</v>
       </c>
       <c r="AA101" t="s" s="2">
-        <v>594</v>
+        <v>78</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>595</v>
+        <v>78</v>
       </c>
       <c r="AC101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD101" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13876,13 +13886,13 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13891,22 +13901,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>86</v>
@@ -13918,16 +13926,16 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -13965,19 +13973,19 @@
         <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>78</v>
+        <v>597</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="AC102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -13992,13 +14000,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14009,13 +14017,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14034,16 +14042,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14093,7 +14101,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14108,13 +14116,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14125,13 +14133,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14150,16 +14158,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14209,7 +14217,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14224,13 +14232,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14241,13 +14249,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14266,16 +14274,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14325,7 +14333,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14340,13 +14348,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14357,13 +14365,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>146</v>
+        <v>607</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14382,16 +14390,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14441,7 +14449,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14456,13 +14464,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14473,13 +14481,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>607</v>
+        <v>146</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14498,16 +14506,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14557,7 +14565,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14572,13 +14580,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14589,13 +14597,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14614,16 +14622,16 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14673,7 +14681,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14688,13 +14696,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14703,41 +14711,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B109" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>612</v>
+      </c>
       <c r="C109" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14787,7 +14797,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14802,13 +14812,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>78</v>
+        <v>599</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14819,11 +14829,11 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" t="s" s="2">
-        <v>619</v>
+        <v>78</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14842,20 +14852,18 @@
         <v>86</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>221</v>
+        <v>615</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
         <v>78</v>
       </c>
@@ -14879,13 +14887,13 @@
         <v>78</v>
       </c>
       <c r="W110" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>624</v>
+        <v>78</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>625</v>
+        <v>78</v>
       </c>
       <c r="Z110" t="s" s="2">
         <v>78</v>
@@ -14903,7 +14911,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14921,25 +14929,25 @@
         <v>78</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>627</v>
+        <v>78</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
-        <v>78</v>
+        <v>622</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14955,19 +14963,23 @@
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>629</v>
+        <v>224</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>47</v>
+        <v>623</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M111" s="2"/>
-      <c r="N111" s="2"/>
+        <v>624</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="O111" t="s" s="2">
         <v>78</v>
       </c>
@@ -14991,13 +15003,13 @@
         <v>78</v>
       </c>
       <c r="W111" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>78</v>
+        <v>627</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>78</v>
+        <v>628</v>
       </c>
       <c r="Z111" t="s" s="2">
         <v>78</v>
@@ -15015,7 +15027,7 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
@@ -15030,24 +15042,24 @@
         <v>97</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>631</v>
+        <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>456</v>
+        <v>619</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
@@ -15058,7 +15070,7 @@
         <v>76</v>
       </c>
       <c r="F112" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G112" t="s" s="2">
         <v>78</v>
@@ -15067,16 +15079,16 @@
         <v>78</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>200</v>
+        <v>632</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>635</v>
+        <v>47</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -15127,13 +15139,13 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>78</v>
@@ -15142,24 +15154,24 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>78</v>
+        <v>634</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>78</v>
+        <v>636</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
@@ -15170,7 +15182,7 @@
         <v>76</v>
       </c>
       <c r="F113" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>78</v>
@@ -15179,20 +15191,18 @@
         <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J113" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="K113" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>642</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
         <v>78</v>
@@ -15241,13 +15251,13 @@
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>78</v>
@@ -15256,23 +15266,137 @@
         <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B114" s="2"/>
+      <c r="C114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="K114" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AK113" t="s" s="2">
+      <c r="L114" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AK114" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AL113" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN113" t="s" s="2">
+      <c r="AL114" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN113">
+  <autoFilter ref="A1:AN114">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15282,7 +15406,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI112">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="649">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -540,6 +540,9 @@
   </si>
   <si>
     <t>Fundamente de la Priorización</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
     <t>EstadoInterconsultaCodigo</t>
@@ -4364,7 +4367,7 @@
         <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -4436,7 +4439,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4450,7 +4453,7 @@
         <v>129</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>78</v>
@@ -4472,13 +4475,13 @@
         <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -4564,7 +4567,7 @@
         <v>129</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>78</v>
@@ -4586,13 +4589,13 @@
         <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -4678,7 +4681,7 @@
         <v>129</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>78</v>
@@ -4700,13 +4703,13 @@
         <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -4792,7 +4795,7 @@
         <v>129</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>78</v>
@@ -4814,13 +4817,13 @@
         <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -4906,7 +4909,7 @@
         <v>129</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>78</v>
@@ -4928,13 +4931,13 @@
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -5020,7 +5023,7 @@
         <v>129</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>78</v>
@@ -5042,13 +5045,13 @@
         <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -5131,11 +5134,11 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -5157,16 +5160,16 @@
         <v>130</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O25" t="s" s="2">
         <v>78</v>
@@ -5215,7 +5218,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5247,7 +5250,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -5270,16 +5273,16 @@
         <v>86</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
@@ -5329,7 +5332,7 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
@@ -5344,24 +5347,24 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5384,13 +5387,13 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -5441,7 +5444,7 @@
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
@@ -5462,7 +5465,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5473,11 +5476,11 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -5499,13 +5502,13 @@
         <v>130</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
@@ -5546,7 +5549,7 @@
         <v>133</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
@@ -5555,7 +5558,7 @@
         <v>134</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
@@ -5576,7 +5579,7 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5587,7 +5590,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5613,16 +5616,16 @@
         <v>105</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5647,13 +5650,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5671,7 +5674,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5692,7 +5695,7 @@
         <v>128</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5703,7 +5706,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5726,19 +5729,19 @@
         <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
@@ -5763,13 +5766,13 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
@@ -5787,7 +5790,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5805,10 +5808,10 @@
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5819,7 +5822,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5842,13 +5845,13 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -5899,7 +5902,7 @@
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
@@ -5920,7 +5923,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5931,11 +5934,11 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5957,13 +5960,13 @@
         <v>130</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
@@ -6004,7 +6007,7 @@
         <v>133</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
@@ -6013,7 +6016,7 @@
         <v>134</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6034,7 +6037,7 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6045,7 +6048,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6068,19 +6071,19 @@
         <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>78</v>
@@ -6129,7 +6132,7 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
@@ -6147,10 +6150,10 @@
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6161,7 +6164,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -6184,13 +6187,13 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -6241,7 +6244,7 @@
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
@@ -6262,7 +6265,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6273,11 +6276,11 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -6299,13 +6302,13 @@
         <v>130</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
@@ -6346,7 +6349,7 @@
         <v>133</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
@@ -6355,7 +6358,7 @@
         <v>134</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
@@ -6376,7 +6379,7 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6387,7 +6390,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6413,16 +6416,16 @@
         <v>99</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>78</v>
@@ -6471,7 +6474,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6489,10 +6492,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6503,7 +6506,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6526,16 +6529,16 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
@@ -6585,7 +6588,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6603,10 +6606,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6617,7 +6620,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6643,14 +6646,14 @@
         <v>105</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6660,7 +6663,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6699,7 +6702,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6717,10 +6720,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6731,7 +6734,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6754,17 +6757,17 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6813,7 +6816,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6831,10 +6834,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6845,7 +6848,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6868,19 +6871,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6929,7 +6932,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6947,10 +6950,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6961,7 +6964,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6984,19 +6987,19 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -7045,7 +7048,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7063,10 +7066,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7077,7 +7080,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7103,16 +7106,16 @@
         <v>99</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
@@ -7125,7 +7128,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7161,7 +7164,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7179,10 +7182,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7193,7 +7196,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7216,16 +7219,16 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -7239,7 +7242,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7275,7 +7278,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7293,10 +7296,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7307,7 +7310,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7330,13 +7333,13 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -7387,7 +7390,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7405,10 +7408,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7419,7 +7422,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7442,16 +7445,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7501,7 +7504,7 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
@@ -7519,10 +7522,10 @@
         <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7533,7 +7536,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7556,16 +7559,16 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7615,7 +7618,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7630,13 +7633,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7647,7 +7650,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7673,13 +7676,13 @@
         <v>99</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
@@ -7729,7 +7732,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7744,13 +7747,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7761,11 +7764,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7784,13 +7787,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7841,7 +7844,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7856,13 +7859,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7873,11 +7876,11 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7896,13 +7899,13 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
@@ -7953,7 +7956,7 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
@@ -7968,13 +7971,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7985,11 +7988,11 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -8008,19 +8011,19 @@
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O50" t="s" s="2">
         <v>78</v>
@@ -8069,7 +8072,7 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>76</v>
@@ -8084,13 +8087,13 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -8101,7 +8104,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8127,13 +8130,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8159,13 +8162,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8183,7 +8186,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8198,24 +8201,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8241,13 +8244,13 @@
         <v>105</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
@@ -8273,13 +8276,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8297,7 +8300,7 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>85</v>
@@ -8312,16 +8315,16 @@
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -8329,7 +8332,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8352,19 +8355,19 @@
         <v>86</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>78</v>
@@ -8389,13 +8392,13 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -8413,7 +8416,7 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
@@ -8431,13 +8434,13 @@
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8445,7 +8448,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8468,13 +8471,13 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
@@ -8525,7 +8528,7 @@
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
@@ -8546,7 +8549,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8557,11 +8560,11 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8583,13 +8586,13 @@
         <v>130</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
@@ -8630,7 +8633,7 @@
         <v>133</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
@@ -8639,7 +8642,7 @@
         <v>134</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8660,7 +8663,7 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8671,7 +8674,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8694,19 +8697,19 @@
         <v>86</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>78</v>
@@ -8755,7 +8758,7 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
@@ -8773,10 +8776,10 @@
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8787,7 +8790,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8810,13 +8813,13 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8867,7 +8870,7 @@
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
@@ -8888,7 +8891,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8899,11 +8902,11 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8925,13 +8928,13 @@
         <v>130</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
@@ -8972,7 +8975,7 @@
         <v>133</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
@@ -8981,7 +8984,7 @@
         <v>134</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
@@ -9002,7 +9005,7 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9013,7 +9016,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9039,16 +9042,16 @@
         <v>99</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>78</v>
@@ -9097,7 +9100,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9115,10 +9118,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9129,7 +9132,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9152,16 +9155,16 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
@@ -9211,7 +9214,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9229,10 +9232,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9243,7 +9246,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9269,14 +9272,14 @@
         <v>105</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9301,11 +9304,11 @@
         <v>78</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="X61" s="2"/>
       <c r="Y61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9323,7 +9326,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9341,10 +9344,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9355,7 +9358,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9378,17 +9381,17 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9437,7 +9440,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9455,10 +9458,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9469,7 +9472,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9492,19 +9495,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9553,7 +9556,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9571,10 +9574,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9585,7 +9588,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9608,19 +9611,19 @@
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>78</v>
@@ -9669,7 +9672,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9687,10 +9690,10 @@
         <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9701,7 +9704,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9727,10 +9730,10 @@
         <v>105</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -9738,7 +9741,7 @@
         <v>78</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
@@ -9759,13 +9762,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9783,7 +9786,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9798,16 +9801,16 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9815,7 +9818,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9838,70 +9841,70 @@
         <v>86</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="Q66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE66" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="Q66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9916,13 +9919,13 @@
         <v>97</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9933,7 +9936,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9956,13 +9959,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -10013,7 +10016,7 @@
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
@@ -10045,7 +10048,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -10123,7 +10126,7 @@
         <v>134</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10155,10 +10158,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>78</v>
@@ -10180,13 +10183,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10237,7 +10240,7 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
@@ -10269,7 +10272,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -10292,13 +10295,13 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -10349,7 +10352,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10381,11 +10384,11 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10404,16 +10407,16 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10439,13 +10442,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10463,7 +10466,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10478,24 +10481,24 @@
         <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10518,13 +10521,13 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -10575,7 +10578,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
@@ -10596,7 +10599,7 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10607,11 +10610,11 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10633,13 +10636,13 @@
         <v>130</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
@@ -10680,7 +10683,7 @@
         <v>133</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC73" t="s" s="2">
         <v>78</v>
@@ -10689,7 +10692,7 @@
         <v>134</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>76</v>
@@ -10710,7 +10713,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10721,7 +10724,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10744,19 +10747,19 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" t="s" s="2">
         <v>78</v>
@@ -10805,7 +10808,7 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
@@ -10823,10 +10826,10 @@
         <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10837,7 +10840,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
@@ -10860,19 +10863,19 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>78</v>
@@ -10882,7 +10885,7 @@
         <v>78</v>
       </c>
       <c r="R75" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -10921,7 +10924,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10939,10 +10942,10 @@
         <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -10953,11 +10956,11 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10976,16 +10979,16 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
@@ -11011,13 +11014,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11035,7 +11038,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -11044,7 +11047,7 @@
         <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>97</v>
@@ -11053,21 +11056,21 @@
         <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -11090,17 +11093,17 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>78</v>
@@ -11149,7 +11152,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11167,10 +11170,10 @@
         <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -11181,7 +11184,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -11204,13 +11207,13 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -11261,7 +11264,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>85</v>
@@ -11276,28 +11279,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11316,13 +11319,13 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -11373,7 +11376,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11388,28 +11391,28 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11428,13 +11431,13 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -11485,7 +11488,7 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
@@ -11500,24 +11503,24 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -11540,13 +11543,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11573,13 +11576,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11597,7 +11600,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
@@ -11618,22 +11621,22 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11652,13 +11655,13 @@
         <v>86</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11709,7 +11712,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11724,28 +11727,28 @@
         <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11764,16 +11767,16 @@
         <v>86</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
@@ -11823,7 +11826,7 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
@@ -11838,28 +11841,28 @@
         <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11878,16 +11881,16 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
@@ -11913,13 +11916,13 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11937,7 +11940,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -11952,16 +11955,16 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11969,11 +11972,11 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11992,16 +11995,16 @@
         <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
@@ -12051,7 +12054,7 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
@@ -12066,16 +12069,16 @@
         <v>97</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12083,7 +12086,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
@@ -12106,13 +12109,13 @@
         <v>86</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -12139,13 +12142,13 @@
         <v>78</v>
       </c>
       <c r="W86" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>78</v>
@@ -12163,7 +12166,7 @@
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12184,10 +12187,10 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12195,7 +12198,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
@@ -12218,13 +12221,13 @@
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -12275,7 +12278,7 @@
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
@@ -12296,7 +12299,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12307,11 +12310,11 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -12333,13 +12336,13 @@
         <v>130</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
@@ -12380,7 +12383,7 @@
         <v>133</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC88" t="s" s="2">
         <v>78</v>
@@ -12389,7 +12392,7 @@
         <v>134</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
@@ -12410,7 +12413,7 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12421,7 +12424,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12444,19 +12447,19 @@
         <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
@@ -12481,11 +12484,11 @@
         <v>78</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="X89" s="2"/>
       <c r="Y89" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Z89" t="s" s="2">
         <v>78</v>
@@ -12503,7 +12506,7 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12521,10 +12524,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12535,7 +12538,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12558,13 +12561,13 @@
         <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -12615,7 +12618,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12636,7 +12639,7 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12647,11 +12650,11 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12673,13 +12676,13 @@
         <v>130</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
@@ -12720,7 +12723,7 @@
         <v>133</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AC91" t="s" s="2">
         <v>78</v>
@@ -12729,7 +12732,7 @@
         <v>134</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
@@ -12750,7 +12753,7 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12761,7 +12764,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12787,16 +12790,16 @@
         <v>99</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
@@ -12845,7 +12848,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12863,10 +12866,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12877,7 +12880,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12900,16 +12903,16 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
@@ -12959,7 +12962,7 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
@@ -12977,10 +12980,10 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -12991,7 +12994,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -13017,14 +13020,14 @@
         <v>105</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>78</v>
@@ -13073,7 +13076,7 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
@@ -13091,10 +13094,10 @@
         <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -13105,7 +13108,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13128,17 +13131,17 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>78</v>
@@ -13187,7 +13190,7 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13205,10 +13208,10 @@
         <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13219,7 +13222,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13242,19 +13245,19 @@
         <v>86</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>78</v>
@@ -13303,7 +13306,7 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
@@ -13321,10 +13324,10 @@
         <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13335,7 +13338,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13358,19 +13361,19 @@
         <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O97" t="s" s="2">
         <v>78</v>
@@ -13419,7 +13422,7 @@
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13437,10 +13440,10 @@
         <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13451,7 +13454,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13474,13 +13477,13 @@
         <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
@@ -13531,7 +13534,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13552,10 +13555,10 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13563,7 +13566,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
@@ -13586,16 +13589,16 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13621,13 +13624,13 @@
         <v>78</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>78</v>
@@ -13645,7 +13648,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13660,16 +13663,16 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13677,7 +13680,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13700,16 +13703,16 @@
         <v>86</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13759,7 +13762,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13774,16 +13777,16 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13791,7 +13794,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
@@ -13814,13 +13817,13 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
@@ -13871,7 +13874,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13886,13 +13889,13 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13903,11 +13906,11 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13926,16 +13929,16 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -13973,10 +13976,10 @@
         <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AC102" t="s" s="2">
         <v>78</v>
@@ -13985,7 +13988,7 @@
         <v>134</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14000,13 +14003,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14017,13 +14020,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14042,16 +14045,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14101,7 +14104,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14116,13 +14119,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14133,13 +14136,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14158,16 +14161,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14217,7 +14220,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14232,13 +14235,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14249,13 +14252,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14274,16 +14277,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14333,7 +14336,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14348,13 +14351,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14365,13 +14368,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14390,16 +14393,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14449,7 +14452,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14464,13 +14467,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14481,13 +14484,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>146</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14506,16 +14509,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14565,7 +14568,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14580,13 +14583,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14597,13 +14600,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14622,16 +14625,16 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14681,7 +14684,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14696,13 +14699,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14713,13 +14716,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14738,16 +14741,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14797,7 +14800,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14812,13 +14815,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14829,7 +14832,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" t="s" s="2">
@@ -14852,16 +14855,16 @@
         <v>86</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
@@ -14911,7 +14914,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14929,10 +14932,10 @@
         <v>78</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14943,11 +14946,11 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14966,19 +14969,19 @@
         <v>86</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>78</v>
@@ -15003,13 +15006,13 @@
         <v>78</v>
       </c>
       <c r="W111" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Z111" t="s" s="2">
         <v>78</v>
@@ -15027,7 +15030,7 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
@@ -15045,21 +15048,21 @@
         <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
@@ -15082,13 +15085,13 @@
         <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -15139,7 +15142,7 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
@@ -15154,24 +15157,24 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
@@ -15194,13 +15197,13 @@
         <v>86</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -15251,7 +15254,7 @@
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>76</v>
@@ -15269,10 +15272,10 @@
         <v>78</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15283,7 +15286,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" t="s" s="2">
@@ -15306,16 +15309,16 @@
         <v>78</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
@@ -15365,7 +15368,7 @@
         <v>78</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AF114" t="s" s="2">
         <v>76</v>
@@ -15380,13 +15383,13 @@
         <v>97</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$109</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="641">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -585,14 +585,758 @@
     <t>SubEspecialidad Médica Destino Código</t>
   </si>
   <si>
-    <t>DestinoAtencionCodigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/DestinoAtencionCodigo}
+    <t>ServiceRequest.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Destino Atención Codigo</t>
+    <t>Identifiers assigned to this order</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
+  </si>
+  <si>
+    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
+  </si>
+  <si>
+    <t>value:type.coding.code}
+value:type.coding.system}</t>
+  </si>
+  <si>
+    <t>Slice creado para almacenar los identificadores</t>
+  </si>
+  <si>
+    <t>Request.identifier</t>
+  </si>
+  <si>
+    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>ClinicalStatement.identifier</t>
+  </si>
+  <si>
+    <t>IdInterconsulta</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>ServiceRequest.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+</t>
+  </si>
+  <si>
+    <t>Instantiates FHIR protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
+  </si>
+  <si>
+    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Request.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Instantiates external protocol or definition</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Request.instantiatesUri</t>
+  </si>
+  <si>
+    <t>ServiceRequest.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
+</t>
+  </si>
+  <si>
+    <t>What request fulfills</t>
+  </si>
+  <si>
+    <t>Plan/proposal/order fulfilled by this request.</t>
+  </si>
+  <si>
+    <t>Request.basedOn</t>
+  </si>
+  <si>
+    <t>ORC.8 (plus others)</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.replaces</t>
+  </si>
+  <si>
+    <t>supersedes
+priorrenewed order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ServiceRequest)
+</t>
+  </si>
+  <si>
+    <t>What request replaces</t>
+  </si>
+  <si>
+    <t>The request takes the place of the referenced completed or terminated request(s).</t>
+  </si>
+  <si>
+    <t>Request.replaces</t>
+  </si>
+  <si>
+    <t>Handled by message location of ORC (ORC.1=RO or RU)</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RPLC].target</t>
+  </si>
+  <si>
+    <t>ServiceRequest.requisition</t>
+  </si>
+  <si>
+    <t>grouperId
+groupIdentifier</t>
+  </si>
+  <si>
+    <t>Composite Request ID</t>
+  </si>
+  <si>
+    <t>A shared identifier common to all service requests that were authorized more or less simultaneously by a single author, representing the composite or group identifier.</t>
+  </si>
+  <si>
+    <t>Requests are linked either by a "basedOn" relationship (i.e. one request is fulfilling another) or by having a common requisition. Requests that are part of the same requisition are generally treated independently from the perspective of changing their state or maintaining them after initial creation.</t>
+  </si>
+  <si>
+    <t>Some business processes need to know if multiple items were ordered as part of the same "requisition" for billing or other purposes.</t>
+  </si>
+  <si>
+    <t>Request.groupIdentifier</t>
+  </si>
+  <si>
+    <t>ORC.4</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=COMP].source[moodCode=INT].identifier</t>
+  </si>
+  <si>
+    <t>ServiceRequest.status</t>
+  </si>
+  <si>
+    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>The status of the order.</t>
+  </si>
+  <si>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
+  </si>
+  <si>
+    <t>The status of a service order.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.status</t>
+  </si>
+  <si>
+    <t>ORC.5,RF1-1</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Action.currentStatus</t>
+  </si>
+  <si>
+    <t>ServiceRequest.intent</t>
+  </si>
+  <si>
+    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
+  </si>
+  <si>
+    <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
+  </si>
+  <si>
+    <t>The kind of service request.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.intent</t>
+  </si>
+  <si>
+    <t>.moodCode (nuances beyond PRP/PLAN/RQO would need to be elsewhere)</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category</t>
+  </si>
+  <si>
+    <t>Classification of service</t>
+  </si>
+  <si>
+    <t>A code that classifies the service for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+  </si>
+  <si>
+    <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what service request are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Classification of the requested service.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+  </si>
+  <si>
+    <t>RF1-5</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="INT"].code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding.system</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding.version</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding.code</t>
+  </si>
+  <si>
+    <t>http://minsal.cl/listaespera/ValueSet/VSModalidadAtencionCodigo</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding.display</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t>ServiceRequest.category.text</t>
+  </si>
+  <si>
+    <t>ServiceRequest.priority</t>
+  </si>
+  <si>
+    <t>Pertinencia Interconsulta</t>
+  </si>
+  <si>
+    <t>Indicates how quickly the ServiceRequest should be addressed with respect to other requests.</t>
+  </si>
+  <si>
+    <t>If missing, this task should be performed with normal priority</t>
+  </si>
+  <si>
+    <t>Identifies the level of importance to be assigned to actioning the request.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.priority</t>
+  </si>
+  <si>
+    <t>TQ1.9, RF1-2</t>
+  </si>
+  <si>
+    <t>.priorityCode</t>
+  </si>
+  <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
+    <t>ServiceRequest.doNotPerform</t>
+  </si>
+  <si>
+    <t>True if service/procedure should not be performed</t>
+  </si>
+  <si>
+    <t>Set this to true if the record is saying that the service/procedure should NOT be performed.</t>
+  </si>
+  <si>
+    <t>In general, only the code and timeframe will be present, though occasional additional qualifiers such as body site or even performer could be included to narrow the scope of the prohibition.  If the ServiceRequest.code and ServiceRequest.doNotPerform both contain negation, that will reinforce prohibition and should not have a double negative interpretation.</t>
+  </si>
+  <si>
+    <t>Used for do not ambulate, do not elevate head of bed, do not flush NG tube, do not take blood pressure on a certain arm, etc.</t>
+  </si>
+  <si>
+    <t>If missing, the request is a positive request e.g. "do perform"</t>
+  </si>
+  <si>
+    <t>Request.doNotPerform</t>
+  </si>
+  <si>
+    <t>.actionNegationInd</t>
+  </si>
+  <si>
+    <t>ServiceRequest.doNotPerform.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.doNotPerform.extension</t>
   </si>
   <si>
     <t>PertinenciaInterconsulta</t>
@@ -602,760 +1346,6 @@
 </t>
   </si>
   <si>
-    <t>Pertinencia Interconsulta</t>
-  </si>
-  <si>
-    <t>ServiceRequest.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifiers assigned to this order</t>
-  </si>
-  <si>
-    <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
-  </si>
-  <si>
-    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
-  </si>
-  <si>
-    <t>Request.identifier</t>
-  </si>
-  <si>
-    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>ClinicalStatement.identifier</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>IdInterconsulta</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>ServiceRequest.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
-</t>
-  </si>
-  <si>
-    <t>Instantiates FHIR protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
-  </si>
-  <si>
-    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Request.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t>Varies by domain</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>ServiceRequest.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Instantiates external protocol or definition</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Request.instantiatesUri</t>
-  </si>
-  <si>
-    <t>ServiceRequest.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
-</t>
-  </si>
-  <si>
-    <t>What request fulfills</t>
-  </si>
-  <si>
-    <t>Plan/proposal/order fulfilled by this request.</t>
-  </si>
-  <si>
-    <t>Request.basedOn</t>
-  </si>
-  <si>
-    <t>ORC.8 (plus others)</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>ServiceRequest.replaces</t>
-  </si>
-  <si>
-    <t>supersedes
-priorrenewed order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
-</t>
-  </si>
-  <si>
-    <t>What request replaces</t>
-  </si>
-  <si>
-    <t>The request takes the place of the referenced completed or terminated request(s).</t>
-  </si>
-  <si>
-    <t>Request.replaces</t>
-  </si>
-  <si>
-    <t>Handled by message location of ORC (ORC.1=RO or RU)</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RPLC].target</t>
-  </si>
-  <si>
-    <t>ServiceRequest.requisition</t>
-  </si>
-  <si>
-    <t>grouperId
-groupIdentifier</t>
-  </si>
-  <si>
-    <t>Composite Request ID</t>
-  </si>
-  <si>
-    <t>A shared identifier common to all service requests that were authorized more or less simultaneously by a single author, representing the composite or group identifier.</t>
-  </si>
-  <si>
-    <t>Requests are linked either by a "basedOn" relationship (i.e. one request is fulfilling another) or by having a common requisition. Requests that are part of the same requisition are generally treated independently from the perspective of changing their state or maintaining them after initial creation.</t>
-  </si>
-  <si>
-    <t>Some business processes need to know if multiple items were ordered as part of the same "requisition" for billing or other purposes.</t>
-  </si>
-  <si>
-    <t>Request.groupIdentifier</t>
-  </si>
-  <si>
-    <t>ORC.4</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=COMP].source[moodCode=INT].identifier</t>
-  </si>
-  <si>
-    <t>ServiceRequest.status</t>
-  </si>
-  <si>
-    <t>draft | active | on-hold | revoked | completed | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>The status of the order.</t>
-  </si>
-  <si>
-    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
-  </si>
-  <si>
-    <t>The status of a service order.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.status</t>
-  </si>
-  <si>
-    <t>ORC.5,RF1-1</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Action.currentStatus</t>
-  </si>
-  <si>
-    <t>ServiceRequest.intent</t>
-  </si>
-  <si>
-    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
-  </si>
-  <si>
-    <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
-  </si>
-  <si>
-    <t>The kind of service request.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.intent</t>
-  </si>
-  <si>
-    <t>.moodCode (nuances beyond PRP/PLAN/RQO would need to be elsewhere)</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category</t>
-  </si>
-  <si>
-    <t>Classification of service</t>
-  </si>
-  <si>
-    <t>A code that classifies the service for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
-  </si>
-  <si>
-    <t>There may be multiple axis of categorization depending on the context or use case for retrieving or displaying the resource.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what service request are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Classification of the requested service.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
-  </si>
-  <si>
-    <t>RF1-5</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="INT"].code</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding.system</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding.version</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding.code</t>
-  </si>
-  <si>
-    <t>http://minsal.cl/listaespera/ValueSet/VSModalidadAtencionCodigo</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding.display</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t>ServiceRequest.category.text</t>
-  </si>
-  <si>
-    <t>ServiceRequest.priority</t>
-  </si>
-  <si>
-    <t>Indicates how quickly the ServiceRequest should be addressed with respect to other requests.</t>
-  </si>
-  <si>
-    <t>If missing, this task should be performed with normal priority</t>
-  </si>
-  <si>
-    <t>Identifies the level of importance to be assigned to actioning the request.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.priority</t>
-  </si>
-  <si>
-    <t>TQ1.9, RF1-2</t>
-  </si>
-  <si>
-    <t>.priorityCode</t>
-  </si>
-  <si>
-    <t>FiveWs.grade</t>
-  </si>
-  <si>
-    <t>ServiceRequest.doNotPerform</t>
-  </si>
-  <si>
-    <t>True if service/procedure should not be performed</t>
-  </si>
-  <si>
-    <t>Set this to true if the record is saying that the service/procedure should NOT be performed.</t>
-  </si>
-  <si>
-    <t>In general, only the code and timeframe will be present, though occasional additional qualifiers such as body site or even performer could be included to narrow the scope of the prohibition.  If the ServiceRequest.code and ServiceRequest.doNotPerform both contain negation, that will reinforce prohibition and should not have a double negative interpretation.</t>
-  </si>
-  <si>
-    <t>Used for do not ambulate, do not elevate head of bed, do not flush NG tube, do not take blood pressure on a certain arm, etc.</t>
-  </si>
-  <si>
-    <t>If missing, the request is a positive request e.g. "do perform"</t>
-  </si>
-  <si>
-    <t>Request.doNotPerform</t>
-  </si>
-  <si>
-    <t>.actionNegationInd</t>
-  </si>
-  <si>
-    <t>ServiceRequest.doNotPerform.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.doNotPerform.extension</t>
-  </si>
-  <si>
-    <t>MotivoNoPertinenciaCodigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MotivoNoPertinenciaCodigo}
-</t>
-  </si>
-  <si>
-    <t>Motivo No Pertinencia Codigo</t>
-  </si>
-  <si>
     <t>ServiceRequest.doNotPerform.value</t>
   </si>
   <si>
@@ -1403,21 +1393,6 @@
   </si>
   <si>
     <t>Procedure.procedureCode</t>
-  </si>
-  <si>
-    <t>ServiceRequest.code.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.code.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.code.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.code.text</t>
-  </si>
-  <si>
-    <t>derivado a especialidad</t>
   </si>
   <si>
     <t>ServiceRequest.orderDetail</t>
@@ -2351,7 +2326,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN114"/>
+  <dimension ref="A1:AN109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -2380,8 +2355,8 @@
     <col min="24" max="24" width="255.0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="25.8515625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="44.640625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
@@ -4904,43 +4879,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B23" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4988,7 +4965,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -4997,7 +4974,7 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>136</v>
@@ -5009,7 +4986,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -5018,22 +4995,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>85</v>
+        <v>188</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>86</v>
@@ -5042,18 +5017,20 @@
         <v>78</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M24" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
@@ -5090,19 +5067,19 @@
         <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="AC24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5111,66 +5088,66 @@
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>197</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="C25" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I25" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I25" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J25" t="s" s="2">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5218,7 +5195,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5230,27 +5207,27 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -5261,7 +5238,7 @@
         <v>76</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>78</v>
@@ -5270,20 +5247,18 @@
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>78</v>
@@ -5332,13 +5307,13 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>78</v>
@@ -5347,35 +5322,35 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>78</v>
@@ -5387,15 +5362,17 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M27" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
@@ -5432,31 +5409,31 @@
         <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>78</v>
@@ -5465,7 +5442,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5476,41 +5453,43 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5534,52 +5513,52 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5588,9 +5567,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5598,34 +5577,34 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5650,13 +5629,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5674,7 +5653,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5692,10 +5671,10 @@
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5704,9 +5683,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5714,35 +5693,31 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5766,13 +5741,13 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
@@ -5790,7 +5765,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5802,16 +5777,16 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>234</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5822,18 +5797,18 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>78</v>
@@ -5845,15 +5820,17 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M31" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>78</v>
@@ -5890,31 +5867,31 @@
         <v>78</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
@@ -5923,7 +5900,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5932,43 +5909,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O32" t="s" s="2">
         <v>78</v>
       </c>
@@ -6004,19 +5983,19 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6028,16 +6007,16 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6046,9 +6025,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6056,35 +6035,31 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6132,28 +6107,28 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6164,18 +6139,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>78</v>
@@ -6187,15 +6162,17 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M34" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>78</v>
@@ -6232,31 +6209,31 @@
         <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
@@ -6265,7 +6242,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6274,43 +6251,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6346,40 +6325,40 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6388,9 +6367,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6398,13 +6377,13 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -6413,20 +6392,18 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6474,7 +6451,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6492,10 +6469,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6504,9 +6481,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6514,13 +6491,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6529,18 +6506,18 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6549,7 +6526,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6588,7 +6565,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6606,10 +6583,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6620,7 +6597,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6628,7 +6605,7 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
@@ -6643,17 +6620,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6663,7 +6640,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6702,7 +6679,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6720,10 +6697,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6732,9 +6709,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6748,7 +6725,7 @@
         <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6757,17 +6734,19 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M39" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="N39" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6816,7 +6795,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6834,10 +6813,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6848,7 +6827,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6871,19 +6850,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>279</v>
+        <v>202</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6932,7 +6911,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6950,10 +6929,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6964,7 +6943,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6987,19 +6966,19 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -7012,7 +6991,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7048,7 +7027,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7066,10 +7045,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7078,9 +7057,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7088,13 +7067,13 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7103,20 +7082,18 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7128,7 +7105,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7164,7 +7141,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7182,10 +7159,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7194,9 +7171,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7204,13 +7181,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7219,17 +7196,15 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
         <v>78</v>
@@ -7242,7 +7217,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7278,7 +7253,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7296,10 +7271,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7310,7 +7285,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7333,15 +7308,17 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M44" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7390,7 +7367,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7408,10 +7385,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7422,7 +7399,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7433,7 +7410,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7445,16 +7422,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7510,7 +7487,7 @@
         <v>76</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>78</v>
@@ -7519,13 +7496,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7536,7 +7513,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7559,16 +7536,16 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>328</v>
+        <v>99</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7618,7 +7595,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7633,13 +7610,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7650,11 +7627,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7673,17 +7650,15 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>99</v>
+        <v>339</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7732,7 +7707,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7747,13 +7722,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7764,11 +7739,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7787,13 +7762,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7844,7 +7819,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7859,13 +7834,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7876,18 +7851,18 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>78</v>
@@ -7899,16 +7874,20 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>350</v>
+        <v>189</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="O49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7956,13 +7935,13 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -7971,13 +7950,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7986,45 +7965,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>357</v>
+        <v>78</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8048,13 +8025,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8072,10 +8049,10 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -8087,24 +8064,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8130,13 +8107,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8162,13 +8139,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8186,7 +8163,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8201,24 +8178,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>372</v>
+        <v>128</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8226,7 +8203,7 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>85</v>
@@ -8235,24 +8212,26 @@
         <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8276,13 +8255,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>219</v>
+        <v>387</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8300,13 +8279,13 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>78</v>
@@ -8315,24 +8294,24 @@
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>128</v>
+        <v>390</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8346,29 +8325,25 @@
         <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>386</v>
+        <v>203</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8392,13 +8367,13 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -8416,31 +8391,31 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>385</v>
+        <v>205</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>393</v>
+        <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>394</v>
+        <v>206</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8448,18 +8423,18 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>78</v>
@@ -8471,15 +8446,17 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M54" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>78</v>
@@ -8516,31 +8493,31 @@
         <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
@@ -8549,7 +8526,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8558,43 +8535,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8630,19 +8609,19 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8654,16 +8633,16 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8672,9 +8651,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8682,35 +8661,31 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8758,28 +8733,28 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>243</v>
+        <v>205</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8790,18 +8765,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>78</v>
@@ -8813,15 +8788,17 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M57" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>78</v>
@@ -8858,31 +8835,31 @@
         <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AC57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
@@ -8891,7 +8868,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8900,43 +8877,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8972,40 +8951,40 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9014,9 +8993,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -9030,7 +9009,7 @@
         <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -9039,20 +9018,18 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9100,7 +9077,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9118,10 +9095,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9130,9 +9107,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9140,13 +9117,13 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9155,18 +9132,18 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="M60" s="2"/>
+      <c r="N60" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9190,13 +9167,11 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="X60" s="2"/>
       <c r="Y60" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9214,7 +9189,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9232,10 +9207,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9246,7 +9221,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9254,7 +9229,7 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
@@ -9269,17 +9244,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9304,11 +9279,13 @@
         <v>78</v>
       </c>
       <c r="W61" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X61" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y61" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>78</v>
@@ -9326,7 +9303,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9344,10 +9321,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9356,9 +9333,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9372,7 +9349,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9381,17 +9358,19 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M62" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="N62" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9440,7 +9419,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9458,10 +9437,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9472,7 +9451,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9495,19 +9474,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>279</v>
+        <v>202</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9556,7 +9535,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9574,10 +9553,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9586,9 +9565,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9602,7 +9581,7 @@
         <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9611,24 +9590,22 @@
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>288</v>
+        <v>405</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="Q64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9648,13 +9625,13 @@
         <v>78</v>
       </c>
       <c r="W64" t="s" s="2">
-        <v>78</v>
+        <v>217</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>78</v>
+        <v>409</v>
       </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
@@ -9672,7 +9649,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>292</v>
+        <v>404</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9687,16 +9664,16 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>293</v>
+        <v>411</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>294</v>
+        <v>412</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9704,7 +9681,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9721,27 +9698,31 @@
         <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>105</v>
+        <v>276</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>185</v>
+        <v>415</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
@@ -9762,13 +9743,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9786,7 +9767,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9801,24 +9782,24 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>413</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9832,35 +9813,29 @@
         <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>279</v>
+        <v>202</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P66" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="P66" s="2"/>
       <c r="Q66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9904,7 +9879,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>416</v>
+        <v>205</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9916,16 +9891,16 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9936,7 +9911,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9947,7 +9922,7 @@
         <v>76</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>78</v>
@@ -9959,13 +9934,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>425</v>
+        <v>131</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>426</v>
+        <v>132</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -10004,31 +9979,29 @@
         <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB67" s="2"/>
       <c r="AC67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -10046,11 +10019,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="C68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10059,10 +10034,10 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10071,13 +10046,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>130</v>
+        <v>427</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>131</v>
+        <v>405</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>132</v>
+        <v>405</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10116,17 +10091,19 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB68" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10135,7 +10112,7 @@
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>136</v>
@@ -10156,13 +10133,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B69" t="s" s="2">
         <v>428</v>
       </c>
+      <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10174,7 +10149,7 @@
         <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10183,10 +10158,10 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="K69" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>430</v>
@@ -10240,19 +10215,19 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>213</v>
+        <v>431</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>78</v>
@@ -10272,11 +10247,11 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>78</v>
+        <v>433</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10292,18 +10267,20 @@
         <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>279</v>
+        <v>223</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M70" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>78</v>
@@ -10328,13 +10305,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10352,7 +10329,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -10364,41 +10341,41 @@
         <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10407,16 +10384,16 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10442,13 +10419,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10466,39 +10443,39 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10518,19 +10495,21 @@
         <v>78</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>204</v>
+        <v>454</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>205</v>
+        <v>455</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>206</v>
+        <v>456</v>
       </c>
       <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
+      <c r="N72" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10578,7 +10557,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>207</v>
+        <v>453</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
@@ -10590,16 +10569,16 @@
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>452</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>208</v>
+        <v>458</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10608,42 +10587,40 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>210</v>
+        <v>461</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>78</v>
@@ -10680,62 +10657,62 @@
         <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD73" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>213</v>
+        <v>459</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>78</v>
+        <v>464</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>208</v>
+        <v>465</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>466</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>78</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>78</v>
@@ -10747,20 +10724,16 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>238</v>
+        <v>470</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>239</v>
+        <v>471</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10808,13 +10781,13 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>243</v>
+        <v>468</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>78</v>
@@ -10823,38 +10796,38 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>78</v>
+        <v>473</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>244</v>
+        <v>474</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>245</v>
+        <v>475</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>78</v>
+        <v>476</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>78</v>
+        <v>477</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>78</v>
+        <v>479</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10863,20 +10836,16 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>204</v>
+        <v>480</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>288</v>
+        <v>481</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10885,7 +10854,7 @@
         <v>78</v>
       </c>
       <c r="R75" t="s" s="2">
-        <v>451</v>
+        <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -10924,7 +10893,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>292</v>
+        <v>478</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10939,35 +10908,35 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>293</v>
+        <v>484</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>294</v>
+        <v>485</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>78</v>
+        <v>487</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>78</v>
@@ -10979,17 +10948,15 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>225</v>
+        <v>489</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>454</v>
+        <v>490</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="M76" s="2"/>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
         <v>78</v>
@@ -11014,13 +10981,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>457</v>
+        <v>492</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>458</v>
+        <v>493</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11038,16 +11005,16 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>452</v>
+        <v>488</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>97</v>
@@ -11056,25 +11023,25 @@
         <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>446</v>
+        <v>495</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>461</v>
+        <v>496</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11084,7 +11051,7 @@
         <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11093,18 +11060,16 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>463</v>
+        <v>499</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>464</v>
+        <v>500</v>
       </c>
       <c r="M77" s="2"/>
-      <c r="N77" t="s" s="2">
-        <v>465</v>
-      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11152,7 +11117,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>461</v>
+        <v>496</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11167,32 +11132,32 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>78</v>
+        <v>501</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>460</v>
+        <v>502</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>78</v>
+        <v>507</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>85</v>
@@ -11207,15 +11172,17 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>468</v>
+        <v>508</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="M78" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
@@ -11264,10 +11231,10 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>467</v>
+        <v>506</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>85</v>
@@ -11279,28 +11246,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>475</v>
+        <v>516</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>477</v>
+        <v>518</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11319,15 +11286,17 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>478</v>
+        <v>223</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>479</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M79" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
         <v>78</v>
@@ -11352,13 +11321,13 @@
         <v>78</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>78</v>
@@ -11376,7 +11345,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11391,35 +11360,35 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>482</v>
+        <v>525</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>484</v>
+        <v>527</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>486</v>
+        <v>528</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>487</v>
+        <v>529</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>78</v>
@@ -11431,15 +11400,17 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>488</v>
+        <v>530</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>489</v>
+        <v>531</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M80" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
         <v>78</v>
@@ -11488,13 +11459,13 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>486</v>
+        <v>528</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>78</v>
@@ -11503,24 +11474,24 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>494</v>
+        <v>527</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -11534,7 +11505,7 @@
         <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11543,13 +11514,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>497</v>
+        <v>223</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>498</v>
+        <v>538</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>499</v>
+        <v>539</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11576,13 +11547,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>501</v>
+        <v>541</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11600,13 +11571,13 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>78</v>
@@ -11621,22 +11592,22 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>502</v>
+        <v>542</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11646,22 +11617,22 @@
         <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>506</v>
+        <v>202</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>507</v>
+        <v>203</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>508</v>
+        <v>204</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11712,7 +11683,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>504</v>
+        <v>205</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11724,59 +11695,59 @@
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>509</v>
+        <v>78</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>510</v>
+        <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>511</v>
+        <v>206</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>512</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>513</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>515</v>
+        <v>181</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>516</v>
+        <v>130</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>517</v>
+        <v>208</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>518</v>
+        <v>209</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>519</v>
+        <v>184</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
@@ -11814,65 +11785,65 @@
         <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AC83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>514</v>
+        <v>211</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>521</v>
+        <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>522</v>
+        <v>206</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>523</v>
+        <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>524</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11881,18 +11852,20 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>527</v>
+        <v>237</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>528</v>
+        <v>238</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="O84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11916,13 +11889,11 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="X84" s="2"/>
       <c r="Y84" t="s" s="2">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11940,13 +11911,13 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>525</v>
+        <v>241</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>78</v>
@@ -11955,16 +11926,16 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>533</v>
+        <v>242</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>534</v>
+        <v>243</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -11972,18 +11943,18 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>537</v>
+        <v>78</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>78</v>
@@ -11992,20 +11963,18 @@
         <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>538</v>
+        <v>202</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>539</v>
+        <v>203</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
         <v>78</v>
@@ -12054,70 +12023,72 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>536</v>
+        <v>205</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>543</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>544</v>
+        <v>206</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>546</v>
+        <v>208</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="M86" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
@@ -12142,31 +12113,31 @@
         <v>78</v>
       </c>
       <c r="W86" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>210</v>
       </c>
       <c r="AC86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD86" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>545</v>
+        <v>211</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12178,7 +12149,7 @@
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
@@ -12187,18 +12158,18 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>550</v>
+        <v>206</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
@@ -12206,31 +12177,35 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12278,7 +12253,7 @@
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
@@ -12290,16 +12265,16 @@
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12310,18 +12285,18 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>78</v>
@@ -12330,19 +12305,19 @@
         <v>78</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>190</v>
+        <v>257</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
@@ -12380,40 +12355,40 @@
         <v>78</v>
       </c>
       <c r="AA88" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD88" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12424,7 +12399,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12447,19 +12422,17 @@
         <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="M89" s="2"/>
       <c r="N89" t="s" s="2">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
@@ -12484,11 +12457,13 @@
         <v>78</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X89" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y89" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="Z89" t="s" s="2">
         <v>78</v>
@@ -12506,13 +12481,13 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>78</v>
@@ -12524,10 +12499,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12536,9 +12511,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12552,25 +12527,27 @@
         <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
+      <c r="N90" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12618,7 +12595,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>207</v>
+        <v>272</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12630,16 +12607,16 @@
         <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12650,18 +12627,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>78</v>
@@ -12670,21 +12647,23 @@
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>130</v>
+        <v>276</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="O91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12720,40 +12699,40 @@
         <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="AC91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD91" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>208</v>
+        <v>283</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12762,9 +12741,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12772,13 +12751,13 @@
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12787,19 +12766,19 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
@@ -12848,7 +12827,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12866,10 +12845,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12880,7 +12859,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12891,7 +12870,7 @@
         <v>76</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>78</v>
@@ -12903,17 +12882,15 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>204</v>
+        <v>556</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>257</v>
+        <v>538</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
         <v>78</v>
@@ -12962,13 +12939,13 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>260</v>
+        <v>555</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>78</v>
@@ -12980,13 +12957,13 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>262</v>
+        <v>558</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13002,7 +12979,7 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>85</v>
@@ -13017,18 +12994,18 @@
         <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>264</v>
+        <v>560</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M94" s="2"/>
-      <c r="N94" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13052,13 +13029,13 @@
         <v>78</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>78</v>
+        <v>563</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>78</v>
+        <v>564</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>78</v>
@@ -13076,13 +13053,13 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>268</v>
+        <v>559</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
@@ -13091,24 +13068,24 @@
         <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>565</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>269</v>
+        <v>566</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>270</v>
+        <v>567</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13119,10 +13096,10 @@
         <v>76</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13131,18 +13108,18 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>204</v>
+        <v>570</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>272</v>
+        <v>571</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M95" s="2"/>
-      <c r="N95" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13190,13 +13167,13 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>275</v>
+        <v>569</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>78</v>
@@ -13205,16 +13182,16 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>276</v>
+        <v>575</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>277</v>
+        <v>576</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>78</v>
+        <v>568</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13222,7 +13199,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13233,7 +13210,7 @@
         <v>76</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>78</v>
@@ -13242,23 +13219,19 @@
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>279</v>
+        <v>578</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>280</v>
+        <v>579</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="M96" s="2"/>
+      <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13306,13 +13279,13 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>284</v>
+        <v>577</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>78</v>
@@ -13321,13 +13294,13 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>78</v>
+        <v>581</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>285</v>
+        <v>582</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>286</v>
+        <v>583</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13338,43 +13311,41 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>204</v>
+        <v>586</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>288</v>
+        <v>587</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>289</v>
+        <v>588</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13410,25 +13381,25 @@
         <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AC97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>292</v>
+        <v>584</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>78</v>
@@ -13437,13 +13408,13 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>293</v>
+        <v>593</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>294</v>
+        <v>594</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13452,40 +13423,44 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B98" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="C98" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>564</v>
+        <v>596</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>546</v>
+        <v>587</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M98" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
         <v>78</v>
@@ -13534,7 +13509,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13549,16 +13524,16 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>78</v>
+        <v>593</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13566,11 +13541,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="B99" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="C99" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13586,19 +13563,19 @@
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>225</v>
+        <v>586</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13624,13 +13601,13 @@
         <v>78</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>390</v>
+        <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>572</v>
+        <v>78</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>78</v>
@@ -13648,7 +13625,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13663,56 +13640,58 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>576</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B100" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="C100" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13762,7 +13741,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13777,38 +13756,40 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="AL100" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AM100" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
+      <c r="B101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="B101" s="2"/>
-      <c r="C101" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13817,7 +13798,7 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>587</v>
@@ -13825,7 +13806,9 @@
       <c r="L101" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
         <v>78</v>
@@ -13874,7 +13857,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13889,13 +13872,13 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13904,20 +13887,22 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B102" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="C102" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>86</v>
@@ -13929,16 +13914,16 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -13976,19 +13961,19 @@
         <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>598</v>
+        <v>78</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>599</v>
+        <v>78</v>
       </c>
       <c r="AC102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14003,13 +13988,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14020,13 +14005,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>603</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14048,13 +14033,13 @@
         <v>604</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14104,7 +14089,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14119,13 +14104,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14136,13 +14121,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>605</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14161,16 +14146,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14220,7 +14205,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14235,13 +14220,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14250,43 +14235,41 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="B105" s="2"/>
       <c r="C105" t="s" s="2">
-        <v>593</v>
+        <v>78</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I105" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J105" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14336,7 +14319,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14351,13 +14334,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>600</v>
+        <v>78</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14366,45 +14349,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>608</v>
-      </c>
+        <v>614</v>
+      </c>
+      <c r="B106" s="2"/>
       <c r="C106" t="s" s="2">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I106" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J106" t="s" s="2">
-        <v>609</v>
+        <v>223</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N106" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="O106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14428,13 +14411,13 @@
         <v>78</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>78</v>
+        <v>387</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>78</v>
+        <v>620</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>78</v>
+        <v>621</v>
       </c>
       <c r="Z106" t="s" s="2">
         <v>78</v>
@@ -14452,7 +14435,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>592</v>
+        <v>614</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14467,40 +14450,38 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>600</v>
+        <v>78</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>78</v>
+        <v>623</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="B107" s="2"/>
       <c r="C107" t="s" s="2">
-        <v>593</v>
+        <v>78</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14509,17 +14490,15 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>595</v>
+        <v>47</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
         <v>78</v>
@@ -14568,7 +14547,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>592</v>
+        <v>624</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14583,30 +14562,28 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>600</v>
+        <v>627</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>601</v>
+        <v>452</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>78</v>
+        <v>629</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>611</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="B108" s="2"/>
       <c r="C108" t="s" s="2">
-        <v>593</v>
+        <v>78</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14616,26 +14593,24 @@
         <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J108" t="s" s="2">
-        <v>612</v>
+        <v>202</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>595</v>
+        <v>631</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
         <v>78</v>
@@ -14684,13 +14659,13 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>592</v>
+        <v>630</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>78</v>
@@ -14699,13 +14674,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>600</v>
+        <v>78</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>601</v>
+        <v>452</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>602</v>
+        <v>633</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14714,25 +14689,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="B109" s="2"/>
       <c r="C109" t="s" s="2">
-        <v>593</v>
+        <v>78</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14741,16 +14714,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>595</v>
+        <v>636</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>596</v>
+        <v>637</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>597</v>
+        <v>638</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14800,7 +14773,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>592</v>
+        <v>634</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14815,591 +14788,23 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>600</v>
+        <v>639</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>601</v>
+        <v>128</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>602</v>
+        <v>640</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B110" s="2"/>
-      <c r="C110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D110" s="2"/>
-      <c r="E110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P110" s="2"/>
-      <c r="Q110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B111" s="2"/>
-      <c r="C111" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="D111" s="2"/>
-      <c r="E111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P111" s="2"/>
-      <c r="Q111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="B112" s="2"/>
-      <c r="C112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D112" s="2"/>
-      <c r="E112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P112" s="2"/>
-      <c r="Q112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D113" s="2"/>
-      <c r="E113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F113" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P113" s="2"/>
-      <c r="Q113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B114" s="2"/>
-      <c r="C114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="D114" s="2"/>
-      <c r="E114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="F114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P114" s="2"/>
-      <c r="Q114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN114" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN114">
+  <autoFilter ref="A1:AN109">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15409,7 +14814,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI108">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3962" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T15:31:02+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -585,6 +585,26 @@
     <t>SubEspecialidad Médica Destino Código</t>
   </si>
   <si>
+    <t>DestinoAtencionCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/DestinoAtencionCodigo}
+</t>
+  </si>
+  <si>
+    <t>Destino Atención Codigo</t>
+  </si>
+  <si>
+    <t>PertinenciaInterconsulta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/PertinenciaInterconsulta}
+</t>
+  </si>
+  <si>
+    <t>Pertinencia Interconsulta</t>
+  </si>
+  <si>
     <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
@@ -611,9 +631,6 @@
     <t>ServiceRequest.identifier</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
@@ -627,13 +644,6 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
-    <t>value:type.coding.code}
-value:type.coding.system}</t>
-  </si>
-  <si>
-    <t>Slice creado para almacenar los identificadores</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -647,9 +657,6 @@
   </si>
   <si>
     <t>ClinicalStatement.identifier</t>
-  </si>
-  <si>
-    <t>IdInterconsulta</t>
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
@@ -847,6 +854,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>IdInterconsulta</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -1222,13 +1232,7 @@
     <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Classification of the requested service.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://minsal.cl/listaespera/ValueSet/VSModalidadAtencionCodigo</t>
   </si>
   <si>
     <t>RF1-5</t>
@@ -1261,9 +1265,6 @@
     <t>ServiceRequest.category.coding.code</t>
   </si>
   <si>
-    <t>http://minsal.cl/listaespera/ValueSet/VSModalidadAtencionCodigo</t>
-  </si>
-  <si>
     <t>ServiceRequest.category.coding.display</t>
   </si>
   <si>
@@ -1276,9 +1277,6 @@
     <t>ServiceRequest.priority</t>
   </si>
   <si>
-    <t>Pertinencia Interconsulta</t>
-  </si>
-  <si>
     <t>Indicates how quickly the ServiceRequest should be addressed with respect to other requests.</t>
   </si>
   <si>
@@ -1339,11 +1337,14 @@
     <t>ServiceRequest.doNotPerform.extension</t>
   </si>
   <si>
-    <t>PertinenciaInterconsulta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/PertinenciaInterconsulta}
+    <t>MotivoNoPertinenciaCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MotivoNoPertinenciaCodigo}
 </t>
+  </si>
+  <si>
+    <t>Motivo No Pertinencia Codigo</t>
   </si>
   <si>
     <t>ServiceRequest.doNotPerform.value</t>
@@ -1374,6 +1375,9 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred] and a valueset using LOINC Order codes is available [here](valueset-diagnostic-requests.html).</t>
   </si>
   <si>
@@ -1393,6 +1397,21 @@
   </si>
   <si>
     <t>Procedure.procedureCode</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.text</t>
+  </si>
+  <si>
+    <t>derivado a especialidad</t>
   </si>
   <si>
     <t>ServiceRequest.orderDetail</t>
@@ -1599,7 +1618,7 @@
 orderer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>
@@ -1668,7 +1687,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE)
 </t>
   </si>
   <si>
@@ -2326,7 +2345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN109"/>
+  <dimension ref="A1:AN114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -2355,8 +2374,8 @@
     <col min="24" max="24" width="255.0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="25.8515625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="44.640625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.4140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
@@ -4879,45 +4898,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>182</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
         <v>78</v>
       </c>
@@ -4965,7 +4982,7 @@
         <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>186</v>
+        <v>135</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>76</v>
@@ -4974,7 +4991,7 @@
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>136</v>
@@ -4986,7 +5003,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4995,20 +5012,22 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="B24" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="C24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>86</v>
@@ -5017,20 +5036,18 @@
         <v>78</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
         <v>78</v>
@@ -5067,19 +5084,19 @@
         <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="AC24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>76</v>
@@ -5088,66 +5105,66 @@
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H25" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="I25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="K25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5195,7 +5212,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5207,27 +5224,27 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>197</v>
+        <v>128</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -5238,7 +5255,7 @@
         <v>76</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>78</v>
@@ -5247,18 +5264,20 @@
         <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M26" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>78</v>
@@ -5307,13 +5326,13 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>78</v>
@@ -5322,35 +5341,35 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>78</v>
+        <v>201</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>78</v>
@@ -5362,17 +5381,15 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
@@ -5409,31 +5426,31 @@
         <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>78</v>
@@ -5442,7 +5459,7 @@
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5453,43 +5470,41 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5513,52 +5528,52 @@
         <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5567,9 +5582,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5577,34 +5592,34 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="O29" t="s" s="2">
         <v>78</v>
@@ -5629,13 +5644,13 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
@@ -5653,7 +5668,7 @@
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
@@ -5671,10 +5686,10 @@
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>232</v>
+        <v>128</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5683,9 +5698,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5693,31 +5708,35 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
       </c>
@@ -5741,13 +5760,13 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>78</v>
+        <v>231</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
@@ -5765,7 +5784,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5777,16 +5796,16 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5797,18 +5816,18 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>78</v>
@@ -5820,17 +5839,15 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
         <v>78</v>
@@ -5867,31 +5884,31 @@
         <v>78</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AC31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
@@ -5900,7 +5917,7 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5909,45 +5926,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>236</v>
+        <v>130</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>78</v>
       </c>
@@ -5983,19 +5998,19 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>76</v>
@@ -6007,16 +6022,16 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
@@ -6025,9 +6040,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -6035,31 +6050,35 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6107,28 +6126,28 @@
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6139,18 +6158,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>78</v>
@@ -6162,17 +6181,15 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
         <v>78</v>
@@ -6209,31 +6226,31 @@
         <v>78</v>
       </c>
       <c r="AA34" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AC34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD34" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
@@ -6242,7 +6259,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6251,45 +6268,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6325,40 +6340,40 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6367,9 +6382,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -6377,13 +6392,13 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
@@ -6392,18 +6407,20 @@
         <v>86</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6451,7 +6468,7 @@
         <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
@@ -6469,10 +6486,10 @@
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6481,9 +6498,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6491,13 +6508,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6506,18 +6523,18 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="M37" s="2"/>
-      <c r="N37" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6526,7 +6543,7 @@
         <v>78</v>
       </c>
       <c r="R37" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6565,7 +6582,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6583,10 +6600,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6597,7 +6614,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6605,7 +6622,7 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
@@ -6620,17 +6637,17 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>78</v>
@@ -6640,7 +6657,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>78</v>
+        <v>267</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6679,7 +6696,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6697,10 +6714,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6709,9 +6726,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6725,7 +6742,7 @@
         <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
@@ -6734,19 +6751,17 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="M39" s="2"/>
       <c r="N39" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6795,7 +6810,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6813,10 +6828,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6827,7 +6842,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6850,19 +6865,19 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6911,7 +6926,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6929,10 +6944,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6943,7 +6958,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6966,19 +6981,19 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -6991,7 +7006,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7027,7 +7042,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7045,10 +7060,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7057,9 +7072,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7067,13 +7082,13 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7082,18 +7097,20 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
       </c>
@@ -7105,7 +7122,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7141,7 +7158,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7159,10 +7176,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7171,9 +7188,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7181,13 +7198,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7196,15 +7213,17 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>310</v>
+        <v>204</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="M43" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
         <v>78</v>
@@ -7217,7 +7236,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7253,7 +7272,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7271,10 +7290,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7285,7 +7304,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7308,17 +7327,15 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7367,7 +7384,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7385,10 +7402,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7399,7 +7416,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7410,7 +7427,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7422,16 +7439,16 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
@@ -7487,7 +7504,7 @@
         <v>76</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>78</v>
@@ -7496,13 +7513,13 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7513,7 +7530,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7536,16 +7553,16 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>99</v>
+        <v>328</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7595,7 +7612,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7610,13 +7627,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7627,11 +7644,11 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
-        <v>338</v>
+        <v>78</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7650,15 +7667,17 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>339</v>
+        <v>99</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M47" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
         <v>78</v>
@@ -7707,7 +7726,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7722,13 +7741,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7739,11 +7758,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7762,13 +7781,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7819,7 +7838,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7834,13 +7853,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7851,18 +7870,18 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>78</v>
@@ -7874,20 +7893,16 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>189</v>
+        <v>350</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7935,13 +7950,13 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>78</v>
@@ -7950,13 +7965,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7965,43 +7980,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>78</v>
+        <v>357</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8025,13 +8042,13 @@
         <v>78</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>366</v>
+        <v>78</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>367</v>
+        <v>78</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>78</v>
@@ -8049,10 +8066,10 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -8064,24 +8081,24 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>372</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -8107,13 +8124,13 @@
         <v>105</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
@@ -8139,13 +8156,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8163,7 +8180,7 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>85</v>
@@ -8178,24 +8195,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>128</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>78</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8203,7 +8220,7 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>85</v>
@@ -8212,26 +8229,24 @@
         <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
         <v>78</v>
       </c>
@@ -8255,13 +8270,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>387</v>
+        <v>219</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8279,13 +8294,13 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>78</v>
@@ -8294,24 +8309,24 @@
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>390</v>
+        <v>128</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8325,25 +8340,29 @@
         <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>203</v>
+        <v>386</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8367,13 +8386,11 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="X53" s="2"/>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -8391,31 +8408,31 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>205</v>
+        <v>385</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>206</v>
+        <v>392</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>384</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -8427,14 +8444,14 @@
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>78</v>
@@ -8446,17 +8463,15 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M54" s="2"/>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
         <v>78</v>
@@ -8493,31 +8508,31 @@
         <v>78</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AC54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD54" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
@@ -8526,7 +8541,7 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
@@ -8535,45 +8550,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>394</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>236</v>
+        <v>130</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8609,19 +8622,19 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD55" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8633,16 +8646,16 @@
         <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
@@ -8651,7 +8664,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>395</v>
       </c>
@@ -8661,31 +8674,35 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8733,28 +8750,28 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8769,14 +8786,14 @@
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>78</v>
@@ -8788,17 +8805,15 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
         <v>78</v>
@@ -8835,31 +8850,31 @@
         <v>78</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AC57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD57" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
@@ -8868,7 +8883,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8877,45 +8892,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>397</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8951,40 +8964,40 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD58" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8993,7 +9006,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>398</v>
       </c>
@@ -9009,7 +9022,7 @@
         <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -9018,18 +9031,20 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9077,7 +9092,7 @@
         <v>78</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -9095,10 +9110,10 @@
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9107,7 +9122,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>399</v>
       </c>
@@ -9117,13 +9132,13 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9132,18 +9147,18 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="M60" s="2"/>
-      <c r="N60" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9167,11 +9182,13 @@
         <v>78</v>
       </c>
       <c r="W60" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="X60" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y60" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="Z60" t="s" s="2">
         <v>78</v>
@@ -9189,7 +9206,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9207,10 +9224,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9221,7 +9238,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9229,7 +9246,7 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
@@ -9244,17 +9261,17 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="M61" s="2"/>
       <c r="N61" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>78</v>
@@ -9303,7 +9320,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9321,10 +9338,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9333,9 +9350,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9349,7 +9366,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9358,19 +9375,17 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>276</v>
+        <v>204</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="M62" s="2"/>
       <c r="N62" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9419,7 +9434,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9437,10 +9452,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9451,7 +9466,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9474,19 +9489,19 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9535,7 +9550,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9553,10 +9568,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9565,9 +9580,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9581,7 +9596,7 @@
         <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9590,22 +9605,24 @@
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>405</v>
+        <v>288</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O64" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P64" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="P64" s="2"/>
       <c r="Q64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9625,13 +9642,13 @@
         <v>78</v>
       </c>
       <c r="W64" t="s" s="2">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="Z64" t="s" s="2">
         <v>78</v>
@@ -9649,7 +9666,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>404</v>
+        <v>292</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9664,16 +9681,16 @@
         <v>97</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>411</v>
+        <v>293</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>412</v>
+        <v>294</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>413</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9681,7 +9698,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9698,31 +9715,27 @@
         <v>86</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>276</v>
+        <v>105</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>415</v>
+        <v>185</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="P65" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>78</v>
@@ -9743,13 +9756,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9767,7 +9780,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9782,24 +9795,24 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>410</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9813,29 +9826,35 @@
         <v>85</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O66" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="Q66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9879,7 +9898,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9891,16 +9910,16 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>78</v>
+        <v>420</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9911,7 +9930,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9922,7 +9941,7 @@
         <v>76</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>78</v>
@@ -9934,13 +9953,13 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>131</v>
+        <v>422</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>132</v>
+        <v>423</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -9979,29 +9998,31 @@
         <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB67" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -10019,13 +10040,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10034,10 +10053,10 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10046,13 +10065,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>427</v>
+        <v>130</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>405</v>
+        <v>131</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>405</v>
+        <v>132</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10091,19 +10110,17 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB68" s="2"/>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
@@ -10112,7 +10129,7 @@
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>136</v>
@@ -10133,11 +10150,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B69" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="C69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10149,7 +10168,7 @@
         <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10158,13 +10177,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>276</v>
+        <v>426</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10215,19 +10234,19 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>431</v>
+        <v>213</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>78</v>
@@ -10247,11 +10266,11 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -10267,20 +10286,18 @@
         <v>78</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>223</v>
+        <v>279</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
         <v>78</v>
@@ -10305,13 +10322,13 @@
         <v>78</v>
       </c>
       <c r="W70" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>78</v>
@@ -10329,53 +10346,53 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10384,16 +10401,16 @@
         <v>86</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
@@ -10419,13 +10436,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10443,39 +10460,39 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>451</v>
+        <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10495,21 +10512,19 @@
         <v>78</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>454</v>
+        <v>204</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>455</v>
+        <v>205</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>456</v>
+        <v>206</v>
       </c>
       <c r="M72" s="2"/>
-      <c r="N72" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10557,7 +10572,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>453</v>
+        <v>207</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
@@ -10569,16 +10584,16 @@
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>458</v>
+        <v>208</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10587,40 +10602,42 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>461</v>
+        <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M73" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>78</v>
@@ -10657,62 +10674,62 @@
         <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD73" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>459</v>
+        <v>213</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>464</v>
+        <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>465</v>
+        <v>208</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>466</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>78</v>
@@ -10724,16 +10741,20 @@
         <v>86</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>470</v>
+        <v>238</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>471</v>
+        <v>239</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10781,13 +10802,13 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>468</v>
+        <v>243</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>78</v>
@@ -10796,38 +10817,38 @@
         <v>97</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>473</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>474</v>
+        <v>244</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>475</v>
+        <v>245</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>476</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
-        <v>479</v>
+        <v>78</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10836,16 +10857,20 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>480</v>
+        <v>204</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>481</v>
+        <v>288</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10854,7 +10879,7 @@
         <v>78</v>
       </c>
       <c r="R75" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -10893,7 +10918,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>478</v>
+        <v>292</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10908,35 +10933,35 @@
         <v>97</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>484</v>
+        <v>293</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>485</v>
+        <v>294</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>487</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>78</v>
+        <v>451</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>78</v>
@@ -10948,15 +10973,17 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>489</v>
+        <v>225</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="M76" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
         <v>78</v>
@@ -10981,13 +11008,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11005,16 +11032,16 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>97</v>
@@ -11023,25 +11050,25 @@
         <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>78</v>
+        <v>458</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>494</v>
+        <v>442</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>495</v>
+        <v>444</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>497</v>
+        <v>78</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -11051,7 +11078,7 @@
         <v>85</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11060,16 +11087,18 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>498</v>
+        <v>460</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>499</v>
+        <v>461</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>500</v>
+        <v>462</v>
       </c>
       <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
+      <c r="N77" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11117,7 +11146,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -11132,32 +11161,32 @@
         <v>97</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>503</v>
+        <v>464</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>85</v>
@@ -11172,17 +11201,15 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>509</v>
+        <v>467</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
@@ -11231,10 +11258,10 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>85</v>
@@ -11246,28 +11273,28 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>512</v>
+        <v>469</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>515</v>
+        <v>472</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>516</v>
+        <v>473</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>517</v>
+        <v>474</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>518</v>
+        <v>475</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -11286,17 +11313,15 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>223</v>
+        <v>476</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>519</v>
+        <v>477</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
         <v>78</v>
@@ -11321,13 +11346,13 @@
         <v>78</v>
       </c>
       <c r="W79" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>522</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>523</v>
+        <v>78</v>
       </c>
       <c r="Z79" t="s" s="2">
         <v>78</v>
@@ -11345,7 +11370,7 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>517</v>
+        <v>474</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>76</v>
@@ -11360,35 +11385,35 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>524</v>
+        <v>479</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>525</v>
+        <v>480</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>526</v>
+        <v>481</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>529</v>
+        <v>485</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>78</v>
@@ -11400,17 +11425,15 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>530</v>
+        <v>486</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>531</v>
+        <v>487</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
         <v>78</v>
@@ -11459,13 +11482,13 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>78</v>
@@ -11474,24 +11497,24 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>534</v>
+        <v>489</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>535</v>
+        <v>490</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>536</v>
+        <v>491</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>527</v>
+        <v>492</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>537</v>
+        <v>494</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -11505,7 +11528,7 @@
         <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11514,13 +11537,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>223</v>
+        <v>495</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>538</v>
+        <v>496</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>539</v>
+        <v>497</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11547,13 +11570,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>540</v>
+        <v>498</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>541</v>
+        <v>499</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11571,13 +11594,13 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>537</v>
+        <v>494</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>78</v>
@@ -11592,22 +11615,22 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>542</v>
+        <v>500</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>527</v>
+        <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>78</v>
+        <v>501</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11617,22 +11640,22 @@
         <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>202</v>
+        <v>504</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>203</v>
+        <v>505</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>204</v>
+        <v>506</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11683,7 +11706,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>205</v>
+        <v>502</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11695,38 +11718,38 @@
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>78</v>
+        <v>507</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>78</v>
+        <v>508</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>206</v>
+        <v>509</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>510</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>78</v>
+        <v>511</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>181</v>
+        <v>513</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>78</v>
@@ -11735,19 +11758,19 @@
         <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>130</v>
+        <v>514</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>208</v>
+        <v>515</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>209</v>
+        <v>516</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>184</v>
+        <v>517</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
@@ -11785,65 +11808,65 @@
         <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AC83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD83" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>211</v>
+        <v>512</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>78</v>
+        <v>518</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>78</v>
+        <v>519</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>206</v>
+        <v>520</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11852,20 +11875,18 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>237</v>
+        <v>525</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>238</v>
+        <v>526</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11889,11 +11910,13 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="X84" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="Y84" t="s" s="2">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11911,13 +11934,13 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>241</v>
+        <v>523</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>78</v>
@@ -11926,28 +11949,28 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>78</v>
+        <v>530</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>242</v>
+        <v>531</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>243</v>
+        <v>532</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11957,24 +11980,26 @@
         <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>202</v>
+        <v>536</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>203</v>
+        <v>537</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="M85" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
         <v>78</v>
@@ -12023,72 +12048,70 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>205</v>
+        <v>534</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>206</v>
+        <v>542</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>208</v>
+        <v>544</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
@@ -12113,31 +12136,31 @@
         <v>78</v>
       </c>
       <c r="W86" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>78</v>
+        <v>546</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>78</v>
+        <v>547</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>210</v>
+        <v>78</v>
       </c>
       <c r="AC86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD86" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>211</v>
+        <v>543</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12149,7 +12172,7 @@
         <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>78</v>
@@ -12158,16 +12181,16 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>206</v>
+        <v>548</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>549</v>
       </c>
@@ -12177,35 +12200,31 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>247</v>
+        <v>205</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12253,7 +12272,7 @@
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
@@ -12265,16 +12284,16 @@
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12289,14 +12308,14 @@
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>78</v>
@@ -12305,19 +12324,19 @@
         <v>78</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>257</v>
+        <v>190</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
@@ -12355,40 +12374,40 @@
         <v>78</v>
       </c>
       <c r="AA88" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD88" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="AF88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12422,17 +12441,19 @@
         <v>86</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>105</v>
+        <v>238</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="M89" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="N89" t="s" s="2">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>78</v>
@@ -12457,13 +12478,11 @@
         <v>78</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="X89" s="2"/>
       <c r="Y89" t="s" s="2">
-        <v>78</v>
+        <v>552</v>
       </c>
       <c r="Z89" t="s" s="2">
         <v>78</v>
@@ -12481,13 +12500,13 @@
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>78</v>
@@ -12499,10 +12518,10 @@
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12511,9 +12530,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12527,27 +12546,25 @@
         <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>270</v>
+        <v>206</v>
       </c>
       <c r="M90" s="2"/>
-      <c r="N90" t="s" s="2">
-        <v>271</v>
-      </c>
+      <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12595,7 +12612,7 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>272</v>
+        <v>207</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
@@ -12607,16 +12624,16 @@
         <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>274</v>
+        <v>208</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12627,18 +12644,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>78</v>
@@ -12647,23 +12664,21 @@
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>277</v>
+        <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>278</v>
+        <v>211</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12699,40 +12714,40 @@
         <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="AC91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD91" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>281</v>
+        <v>213</v>
       </c>
       <c r="AF91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>283</v>
+        <v>208</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
@@ -12741,9 +12756,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12751,13 +12766,13 @@
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
@@ -12766,19 +12781,19 @@
         <v>86</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>78</v>
@@ -12827,7 +12842,7 @@
         <v>78</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
@@ -12845,10 +12860,10 @@
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12859,7 +12874,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12870,7 +12885,7 @@
         <v>76</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>78</v>
@@ -12882,15 +12897,17 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>556</v>
+        <v>204</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>538</v>
+        <v>257</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M93" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
         <v>78</v>
@@ -12939,13 +12956,13 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>555</v>
+        <v>260</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>78</v>
@@ -12957,13 +12974,13 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>558</v>
+        <v>262</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>527</v>
+        <v>78</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -12971,7 +12988,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -12979,7 +12996,7 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>85</v>
@@ -12994,18 +13011,18 @@
         <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>560</v>
+        <v>264</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="M94" s="2"/>
+      <c r="N94" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13029,13 +13046,13 @@
         <v>78</v>
       </c>
       <c r="W94" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>564</v>
+        <v>78</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>78</v>
@@ -13053,13 +13070,13 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>559</v>
+        <v>268</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>78</v>
@@ -13068,24 +13085,24 @@
         <v>97</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>565</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>566</v>
+        <v>269</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>567</v>
+        <v>270</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13096,10 +13113,10 @@
         <v>76</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13108,18 +13125,18 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>570</v>
+        <v>204</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>571</v>
+        <v>272</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="M95" s="2"/>
+      <c r="N95" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13167,13 +13184,13 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>569</v>
+        <v>275</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>78</v>
@@ -13182,16 +13199,16 @@
         <v>97</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>574</v>
+        <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>575</v>
+        <v>276</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>576</v>
+        <v>277</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13199,7 +13216,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13210,7 +13227,7 @@
         <v>76</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>78</v>
@@ -13219,19 +13236,23 @@
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>578</v>
+        <v>279</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>579</v>
+        <v>280</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13279,13 +13300,13 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>577</v>
+        <v>284</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>78</v>
@@ -13294,13 +13315,13 @@
         <v>97</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>582</v>
+        <v>285</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>583</v>
+        <v>286</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13311,41 +13332,43 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I97" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J97" t="s" s="2">
-        <v>586</v>
+        <v>204</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>587</v>
+        <v>288</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>588</v>
+        <v>289</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="O97" t="s" s="2">
         <v>78</v>
       </c>
@@ -13381,25 +13404,25 @@
         <v>78</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>590</v>
+        <v>78</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>591</v>
+        <v>78</v>
       </c>
       <c r="AC97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD97" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>584</v>
+        <v>292</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>78</v>
@@ -13408,13 +13431,13 @@
         <v>97</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>593</v>
+        <v>293</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>594</v>
+        <v>294</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13423,44 +13446,40 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I98" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J98" t="s" s="2">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>587</v>
+        <v>544</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
         <v>78</v>
@@ -13509,7 +13528,7 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
@@ -13524,16 +13543,16 @@
         <v>97</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>593</v>
+        <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>594</v>
+        <v>564</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13541,13 +13560,11 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -13563,19 +13580,19 @@
         <v>78</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>586</v>
+        <v>225</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>588</v>
+        <v>567</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
@@ -13601,13 +13618,13 @@
         <v>78</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>78</v>
+        <v>569</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>78</v>
+        <v>570</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>78</v>
@@ -13625,7 +13642,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13640,58 +13657,56 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I100" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="H100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J100" t="s" s="2">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13741,7 +13756,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13756,40 +13771,38 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13798,17 +13811,15 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
         <v>78</v>
@@ -13857,7 +13868,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13872,13 +13883,13 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -13887,22 +13898,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>86</v>
@@ -13914,16 +13923,16 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
@@ -13961,19 +13970,19 @@
         <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>78</v>
+        <v>597</v>
       </c>
       <c r="AC102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -13988,13 +13997,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14005,13 +14014,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14030,16 +14039,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14089,7 +14098,7 @@
         <v>78</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14104,13 +14113,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14121,13 +14130,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14146,16 +14155,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14205,7 +14214,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14220,13 +14229,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14235,41 +14244,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="B105" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>604</v>
+      </c>
       <c r="C105" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14319,7 +14330,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14334,13 +14345,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14349,45 +14360,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="B106" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="C106" t="s" s="2">
-        <v>615</v>
+        <v>591</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>223</v>
+        <v>607</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>616</v>
+        <v>593</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14411,13 +14422,13 @@
         <v>78</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>620</v>
+        <v>78</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>621</v>
+        <v>78</v>
       </c>
       <c r="Z106" t="s" s="2">
         <v>78</v>
@@ -14435,7 +14446,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14450,38 +14461,40 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>623</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="B107" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="C107" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14490,15 +14503,17 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>47</v>
+        <v>593</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="M107" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
         <v>78</v>
@@ -14547,7 +14562,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>624</v>
+        <v>590</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14562,28 +14577,30 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>627</v>
+        <v>598</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>452</v>
+        <v>599</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>628</v>
+        <v>600</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>629</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B108" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="C108" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14593,24 +14610,26 @@
         <v>85</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>202</v>
+        <v>610</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>631</v>
+        <v>593</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M108" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
         <v>78</v>
@@ -14659,13 +14678,13 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>78</v>
@@ -14674,13 +14693,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>452</v>
+        <v>599</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>633</v>
+        <v>600</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14689,23 +14708,25 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B109" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="C109" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14714,16 +14735,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>636</v>
+        <v>593</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>637</v>
+        <v>594</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>638</v>
+        <v>595</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14773,7 +14794,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>634</v>
+        <v>590</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14788,23 +14809,591 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B110" s="2"/>
+      <c r="C110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P110" s="2"/>
+      <c r="Q110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B111" s="2"/>
+      <c r="C111" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="D111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B112" s="2"/>
+      <c r="C112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="M112" s="2"/>
+      <c r="N112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P112" s="2"/>
+      <c r="Q112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B113" s="2"/>
+      <c r="C113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AL113" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AK109" t="s" s="2">
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B114" s="2"/>
+      <c r="C114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AK114" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AL109" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN109" t="s" s="2">
+      <c r="AL114" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN109">
+  <autoFilter ref="A1:AN114">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14814,7 +15403,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI108">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$115</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4178" uniqueCount="651">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -593,6 +593,19 @@
   </si>
   <si>
     <t>Destino Atención Codigo</t>
+  </si>
+  <si>
+    <t>PrevisionCodigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/PrevisionCodigoLE}
+</t>
+  </si>
+  <si>
+    <t>Previsión determinada  de aseguramiento de salud del paciente.</t>
+  </si>
+  <si>
+    <t>La previsión es la  variable determinada el sistema de aseguramiento de salud del paciente.</t>
   </si>
   <si>
     <t>PertinenciaInterconsulta</t>
@@ -2345,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN114"/>
+  <dimension ref="A1:AN115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.078125" customWidth="true" bestFit="true"/>
@@ -5045,7 +5058,7 @@
         <v>185</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -5126,45 +5139,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="B25" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="C25" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5212,7 +5223,7 @@
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>76</v>
@@ -5221,7 +5232,7 @@
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>136</v>
@@ -5233,7 +5244,7 @@
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -5244,11 +5255,11 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -5261,24 +5272,26 @@
         <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="K26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="L26" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5326,7 +5339,7 @@
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>76</v>
@@ -5338,27 +5351,27 @@
         <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>202</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -5369,7 +5382,7 @@
         <v>76</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>78</v>
@@ -5378,18 +5391,20 @@
         <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M27" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
         <v>78</v>
@@ -5438,13 +5453,13 @@
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>78</v>
@@ -5453,35 +5468,35 @@
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>78</v>
+        <v>205</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>78</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>78</v>
@@ -5493,17 +5508,15 @@
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
         <v>78</v>
@@ -5540,40 +5553,40 @@
         <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5584,43 +5597,41 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5644,52 +5655,52 @@
         <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>221</v>
+        <v>78</v>
       </c>
       <c r="Z29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5698,9 +5709,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5708,34 +5719,34 @@
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H30" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>78</v>
@@ -5760,13 +5771,13 @@
         <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>78</v>
@@ -5784,7 +5795,7 @@
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>76</v>
@@ -5802,10 +5813,10 @@
         <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5814,9 +5825,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5824,31 +5835,35 @@
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5872,13 +5887,13 @@
         <v>78</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>78</v>
+        <v>235</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>78</v>
+        <v>236</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>78</v>
@@ -5896,7 +5911,7 @@
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>76</v>
@@ -5908,16 +5923,16 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>78</v>
+        <v>238</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>78</v>
@@ -5928,18 +5943,18 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>78</v>
@@ -5951,17 +5966,15 @@
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
         <v>78</v>
@@ -5998,41 +6011,41 @@
         <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AC32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AM32" t="s" s="2">
         <v>78</v>
       </c>
@@ -6040,45 +6053,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6114,19 +6125,19 @@
         <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>76</v>
@@ -6138,16 +6149,16 @@
         <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>78</v>
@@ -6156,9 +6167,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -6166,31 +6177,35 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O34" t="s" s="2">
         <v>78</v>
       </c>
@@ -6238,28 +6253,28 @@
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6270,18 +6285,18 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>78</v>
@@ -6293,17 +6308,15 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
         <v>78</v>
@@ -6340,41 +6353,41 @@
         <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AC35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6382,45 +6395,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
         <v>78</v>
       </c>
@@ -6456,40 +6467,40 @@
         <v>78</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6498,9 +6509,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6508,13 +6519,13 @@
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6523,18 +6534,20 @@
         <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6582,7 +6595,7 @@
         <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>76</v>
@@ -6600,10 +6613,10 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6612,9 +6625,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6622,13 +6635,13 @@
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
@@ -6637,18 +6650,18 @@
         <v>86</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M38" s="2"/>
-      <c r="N38" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6657,7 +6670,7 @@
         <v>78</v>
       </c>
       <c r="R38" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>78</v>
@@ -6696,7 +6709,7 @@
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>76</v>
@@ -6714,10 +6727,10 @@
         <v>78</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
@@ -6728,7 +6741,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6736,7 +6749,7 @@
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>85</v>
@@ -6751,17 +6764,17 @@
         <v>86</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O39" t="s" s="2">
         <v>78</v>
@@ -6771,7 +6784,7 @@
         <v>78</v>
       </c>
       <c r="R39" t="s" s="2">
-        <v>78</v>
+        <v>271</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>78</v>
@@ -6810,7 +6823,7 @@
         <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6828,10 +6841,10 @@
         <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6840,9 +6853,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6856,7 +6869,7 @@
         <v>85</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -6865,19 +6878,17 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="M40" s="2"/>
       <c r="N40" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>78</v>
@@ -6926,7 +6937,7 @@
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>76</v>
@@ -6944,10 +6955,10 @@
         <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -6958,7 +6969,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6981,19 +6992,19 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="O41" t="s" s="2">
         <v>78</v>
@@ -7042,7 +7053,7 @@
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -7060,10 +7071,10 @@
         <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7074,7 +7085,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -7097,19 +7108,19 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="O42" t="s" s="2">
         <v>78</v>
@@ -7122,7 +7133,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7158,7 +7169,7 @@
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -7176,10 +7187,10 @@
         <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>78</v>
@@ -7188,9 +7199,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -7198,13 +7209,13 @@
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7213,18 +7224,20 @@
         <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="O43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7236,7 +7249,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7272,7 +7285,7 @@
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -7290,10 +7303,10 @@
         <v>78</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7302,9 +7315,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -7312,13 +7325,13 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7327,15 +7340,17 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>313</v>
+        <v>208</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M44" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
         <v>78</v>
@@ -7348,7 +7363,7 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>78</v>
@@ -7384,7 +7399,7 @@
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -7402,10 +7417,10 @@
         <v>78</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7416,7 +7431,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -7439,17 +7454,15 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
         <v>78</v>
@@ -7498,7 +7511,7 @@
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
@@ -7516,10 +7529,10 @@
         <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7530,7 +7543,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7541,7 +7554,7 @@
         <v>76</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>78</v>
@@ -7553,16 +7566,16 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
@@ -7612,13 +7625,13 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>78</v>
@@ -7627,13 +7640,13 @@
         <v>97</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7644,7 +7657,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7667,16 +7680,16 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>99</v>
+        <v>332</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
@@ -7726,7 +7739,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7741,13 +7754,13 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7758,11 +7771,11 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
-        <v>341</v>
+        <v>78</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7781,15 +7794,17 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="K48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>78</v>
@@ -7838,7 +7853,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7853,13 +7868,13 @@
         <v>97</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7870,11 +7885,11 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7893,13 +7908,13 @@
         <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
@@ -7950,7 +7965,7 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
@@ -7965,13 +7980,13 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -7982,18 +7997,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>78</v>
@@ -8005,20 +8020,16 @@
         <v>86</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>194</v>
+        <v>354</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8066,13 +8077,13 @@
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>78</v>
@@ -8081,13 +8092,13 @@
         <v>97</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
@@ -8096,43 +8107,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="O51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8156,13 +8169,13 @@
         <v>78</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>78</v>
@@ -8180,10 +8193,10 @@
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>85</v>
@@ -8195,24 +8208,24 @@
         <v>97</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -8238,13 +8251,13 @@
         <v>105</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
@@ -8270,13 +8283,13 @@
         <v>78</v>
       </c>
       <c r="W52" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="Z52" t="s" s="2">
         <v>78</v>
@@ -8294,7 +8307,7 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>85</v>
@@ -8309,24 +8322,24 @@
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>128</v>
+        <v>376</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -8334,7 +8347,7 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>85</v>
@@ -8343,26 +8356,24 @@
         <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8386,11 +8397,13 @@
         <v>78</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X53" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="Y53" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>78</v>
@@ -8408,13 +8421,13 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>78</v>
@@ -8423,24 +8436,24 @@
         <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>391</v>
+        <v>128</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8454,25 +8467,29 @@
         <v>85</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>205</v>
+        <v>390</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="O54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8496,13 +8513,11 @@
         <v>78</v>
       </c>
       <c r="W54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="X54" s="2"/>
       <c r="Y54" t="s" s="2">
-        <v>78</v>
+        <v>394</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>78</v>
@@ -8520,31 +8535,31 @@
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>207</v>
+        <v>389</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>78</v>
+        <v>395</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>208</v>
+        <v>396</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8552,18 +8567,18 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>78</v>
@@ -8575,17 +8590,15 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
         <v>78</v>
@@ -8622,41 +8635,41 @@
         <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
       </c>
@@ -8664,45 +8677,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
         <v>78</v>
       </c>
@@ -8738,19 +8749,19 @@
         <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD56" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
@@ -8762,16 +8773,16 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8780,9 +8791,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8790,31 +8801,35 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O57" t="s" s="2">
         <v>78</v>
       </c>
@@ -8862,28 +8877,28 @@
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8894,18 +8909,18 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>78</v>
@@ -8917,17 +8932,15 @@
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L58" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
         <v>78</v>
@@ -8964,41 +8977,41 @@
         <v>78</v>
       </c>
       <c r="AA58" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
       </c>
@@ -9006,45 +9019,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9080,40 +9091,40 @@
         <v>78</v>
       </c>
       <c r="AA59" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD59" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9122,9 +9133,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -9138,7 +9149,7 @@
         <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9147,18 +9158,20 @@
         <v>86</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9206,7 +9219,7 @@
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -9224,10 +9237,10 @@
         <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9236,9 +9249,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -9246,13 +9259,13 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -9261,18 +9274,18 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M61" s="2"/>
-      <c r="N61" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9320,7 +9333,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>76</v>
@@ -9338,10 +9351,10 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9352,7 +9365,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9360,7 +9373,7 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>85</v>
@@ -9375,17 +9388,17 @@
         <v>86</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>78</v>
@@ -9434,7 +9447,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9452,10 +9465,10 @@
         <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9464,9 +9477,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9480,7 +9493,7 @@
         <v>85</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9489,19 +9502,17 @@
         <v>86</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="M63" s="2"/>
       <c r="N63" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="O63" t="s" s="2">
         <v>78</v>
@@ -9550,7 +9561,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9568,10 +9579,10 @@
         <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9582,7 +9593,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9605,19 +9616,19 @@
         <v>86</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="O64" t="s" s="2">
         <v>78</v>
@@ -9666,7 +9677,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9684,10 +9695,10 @@
         <v>78</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9696,9 +9707,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9712,7 +9723,7 @@
         <v>85</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9721,22 +9732,24 @@
         <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>185</v>
+        <v>292</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O65" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="P65" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="P65" s="2"/>
       <c r="Q65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9756,13 +9769,13 @@
         <v>78</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>407</v>
+        <v>78</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>408</v>
+        <v>78</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>78</v>
@@ -9780,7 +9793,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>404</v>
+        <v>296</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9795,16 +9808,16 @@
         <v>97</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>410</v>
+        <v>297</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>411</v>
+        <v>298</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>412</v>
+        <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9812,7 +9825,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9829,31 +9842,27 @@
         <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>86</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>279</v>
+        <v>105</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>414</v>
+        <v>189</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="P66" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="Q66" t="s" s="2">
         <v>78</v>
@@ -9874,13 +9883,13 @@
         <v>78</v>
       </c>
       <c r="W66" t="s" s="2">
-        <v>78</v>
+        <v>223</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="Z66" t="s" s="2">
         <v>78</v>
@@ -9898,7 +9907,7 @@
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>76</v>
@@ -9913,24 +9922,24 @@
         <v>97</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9944,94 +9953,100 @@
         <v>85</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P67" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="Q67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="P67" s="2"/>
-      <c r="Q67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="R67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>78</v>
+        <v>424</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -10042,7 +10057,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -10053,7 +10068,7 @@
         <v>76</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>78</v>
@@ -10065,13 +10080,13 @@
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>131</v>
+        <v>426</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>132</v>
+        <v>427</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -10110,29 +10125,31 @@
         <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AB68" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AC68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>78</v>
@@ -10150,13 +10167,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10165,10 +10180,10 @@
         <v>76</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10177,13 +10192,13 @@
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>426</v>
+        <v>130</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>427</v>
+        <v>131</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>427</v>
+        <v>132</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -10222,19 +10237,17 @@
         <v>78</v>
       </c>
       <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AB69" s="2"/>
       <c r="AC69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD69" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
@@ -10243,7 +10256,7 @@
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>136</v>
@@ -10264,11 +10277,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="B70" s="2"/>
+      <c r="B70" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="C70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10280,7 +10295,7 @@
         <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10289,13 +10304,13 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>279</v>
+        <v>430</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -10346,19 +10361,19 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>431</v>
+        <v>217</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>78</v>
@@ -10376,13 +10391,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>432</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -10392,26 +10407,24 @@
         <v>85</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>225</v>
+        <v>283</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L71" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>436</v>
-      </c>
+      <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
         <v>78</v>
@@ -10436,13 +10449,13 @@
         <v>78</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>439</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10460,7 +10473,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10472,31 +10485,31 @@
         <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>443</v>
+        <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10506,24 +10519,26 @@
         <v>85</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>205</v>
+        <v>438</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M72" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>78</v>
@@ -10548,13 +10563,13 @@
         <v>78</v>
       </c>
       <c r="W72" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
+        <v>442</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>78</v>
@@ -10572,7 +10587,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>207</v>
+        <v>436</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
@@ -10584,38 +10599,38 @@
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>78</v>
+        <v>444</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>445</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>208</v>
+        <v>446</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>78</v>
@@ -10627,17 +10642,15 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L73" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>78</v>
@@ -10674,40 +10687,40 @@
         <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10718,11 +10731,11 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10738,23 +10751,21 @@
         <v>78</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10790,19 +10801,19 @@
         <v>78</v>
       </c>
       <c r="AA74" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD74" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
@@ -10814,16 +10825,16 @@
         <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10832,9 +10843,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
@@ -10842,13 +10853,13 @@
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10857,19 +10868,19 @@
         <v>86</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>289</v>
+        <v>244</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>291</v>
+        <v>246</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>78</v>
@@ -10879,7 +10890,7 @@
         <v>78</v>
       </c>
       <c r="R75" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -10918,13 +10929,13 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>292</v>
+        <v>247</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>78</v>
@@ -10936,10 +10947,10 @@
         <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>293</v>
+        <v>248</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
@@ -10948,23 +10959,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
-        <v>451</v>
+        <v>78</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -10973,18 +10984,20 @@
         <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>452</v>
+        <v>292</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>453</v>
+        <v>293</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10993,7 +11006,7 @@
         <v>78</v>
       </c>
       <c r="R76" t="s" s="2">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>78</v>
@@ -11008,13 +11021,13 @@
         <v>78</v>
       </c>
       <c r="W76" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>455</v>
+        <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>78</v>
@@ -11032,16 +11045,16 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>450</v>
+        <v>296</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>97</v>
@@ -11050,32 +11063,32 @@
         <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>458</v>
+        <v>297</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>442</v>
+        <v>298</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>78</v>
@@ -11087,18 +11100,18 @@
         <v>86</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>460</v>
+        <v>229</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M77" s="2"/>
-      <c r="N77" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11122,13 +11135,13 @@
         <v>78</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>78</v>
+        <v>459</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>78</v>
@@ -11146,16 +11159,16 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>97</v>
@@ -11164,21 +11177,21 @@
         <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -11186,13 +11199,13 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11201,16 +11214,18 @@
         <v>86</v>
       </c>
       <c r="J78" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="K78" t="s" s="2">
+      <c r="M78" s="2"/>
+      <c r="N78" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L78" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>78</v>
       </c>
@@ -11258,10 +11273,10 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>85</v>
@@ -11273,38 +11288,38 @@
         <v>97</v>
       </c>
       <c r="AJ78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11313,13 +11328,13 @@
         <v>86</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -11370,10 +11385,10 @@
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>85</v>
@@ -11385,28 +11400,28 @@
         <v>97</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -11425,13 +11440,13 @@
         <v>86</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -11482,7 +11497,7 @@
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="AF80" t="s" s="2">
         <v>76</v>
@@ -11497,28 +11512,28 @@
         <v>97</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
-        <v>78</v>
+        <v>489</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11537,13 +11552,13 @@
         <v>86</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -11570,13 +11585,13 @@
         <v>78</v>
       </c>
       <c r="W81" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>498</v>
+        <v>78</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="Z81" t="s" s="2">
         <v>78</v>
@@ -11594,7 +11609,7 @@
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>76</v>
@@ -11609,28 +11624,28 @@
         <v>97</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>496</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
-        <v>503</v>
+        <v>78</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11640,7 +11655,7 @@
         <v>85</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
@@ -11649,13 +11664,13 @@
         <v>86</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11682,13 +11697,13 @@
         <v>78</v>
       </c>
       <c r="W82" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>78</v>
+        <v>502</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>78</v>
@@ -11706,7 +11721,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>76</v>
@@ -11721,28 +11736,28 @@
         <v>97</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>510</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>511</v>
+        <v>505</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -11752,7 +11767,7 @@
         <v>85</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11761,17 +11776,15 @@
         <v>86</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
         <v>78</v>
@@ -11820,7 +11833,7 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
@@ -11835,28 +11848,28 @@
         <v>97</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -11875,16 +11888,16 @@
         <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>225</v>
+        <v>518</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
@@ -11910,13 +11923,13 @@
         <v>78</v>
       </c>
       <c r="W84" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>528</v>
+        <v>78</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11934,7 +11947,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -11949,28 +11962,28 @@
         <v>97</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
@@ -11980,7 +11993,7 @@
         <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -11989,16 +12002,16 @@
         <v>86</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>536</v>
+        <v>229</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
@@ -12024,13 +12037,13 @@
         <v>78</v>
       </c>
       <c r="W85" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>78</v>
+        <v>532</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="Z85" t="s" s="2">
         <v>78</v>
@@ -12048,13 +12061,13 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>78</v>
@@ -12063,16 +12076,16 @@
         <v>97</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12080,11 +12093,11 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -12103,15 +12116,17 @@
         <v>86</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>225</v>
+        <v>540</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M86" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
         <v>78</v>
@@ -12136,13 +12151,13 @@
         <v>78</v>
       </c>
       <c r="W86" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>547</v>
+        <v>78</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>78</v>
@@ -12160,7 +12175,7 @@
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -12175,24 +12190,24 @@
         <v>97</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
@@ -12206,22 +12221,22 @@
         <v>85</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>205</v>
+        <v>548</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>206</v>
+        <v>549</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -12248,13 +12263,13 @@
         <v>78</v>
       </c>
       <c r="W87" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>78</v>
+        <v>550</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="Z87" t="s" s="2">
         <v>78</v>
@@ -12272,19 +12287,19 @@
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>207</v>
+        <v>547</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>78</v>
@@ -12293,10 +12308,10 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>208</v>
+        <v>552</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12304,18 +12319,18 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>78</v>
@@ -12327,17 +12342,15 @@
         <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L88" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
         <v>78</v>
@@ -12374,41 +12387,41 @@
         <v>78</v>
       </c>
       <c r="AA88" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL88" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AC88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12416,45 +12429,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12478,29 +12489,31 @@
         <v>78</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="X89" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y89" t="s" s="2">
-        <v>552</v>
+        <v>78</v>
       </c>
       <c r="Z89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AA89" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD89" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>76</v>
@@ -12512,16 +12525,16 @@
         <v>78</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
@@ -12530,9 +12543,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12540,31 +12553,35 @@
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="O90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12588,13 +12605,11 @@
         <v>78</v>
       </c>
       <c r="W90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="X90" s="2"/>
       <c r="Y90" t="s" s="2">
-        <v>78</v>
+        <v>556</v>
       </c>
       <c r="Z90" t="s" s="2">
         <v>78</v>
@@ -12612,28 +12627,28 @@
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>78</v>
+        <v>248</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12644,18 +12659,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>78</v>
@@ -12667,17 +12682,15 @@
         <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L91" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>190</v>
-      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
         <v>78</v>
@@ -12714,41 +12727,41 @@
         <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="AB91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL91" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AC91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12756,45 +12769,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
         <v>78</v>
       </c>
@@ -12830,40 +12841,40 @@
         <v>78</v>
       </c>
       <c r="AA92" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AC92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD92" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="AF92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -12872,9 +12883,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -12882,13 +12893,13 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12897,18 +12908,20 @@
         <v>86</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>204</v>
+        <v>99</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="O93" t="s" s="2">
         <v>78</v>
       </c>
@@ -12956,7 +12969,7 @@
         <v>78</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>76</v>
@@ -12974,10 +12987,10 @@
         <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -12986,9 +12999,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -12996,13 +13009,13 @@
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13011,18 +13024,18 @@
         <v>86</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M94" s="2"/>
-      <c r="N94" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13070,7 +13083,7 @@
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>76</v>
@@ -13088,10 +13101,10 @@
         <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -13102,7 +13115,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13110,7 +13123,7 @@
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>85</v>
@@ -13125,17 +13138,17 @@
         <v>86</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>78</v>
@@ -13184,7 +13197,7 @@
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>76</v>
@@ -13202,10 +13215,10 @@
         <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -13214,9 +13227,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13230,7 +13243,7 @@
         <v>85</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
@@ -13239,19 +13252,17 @@
         <v>86</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>279</v>
+        <v>208</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="M96" s="2"/>
       <c r="N96" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>78</v>
@@ -13300,7 +13311,7 @@
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>76</v>
@@ -13318,10 +13329,10 @@
         <v>78</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
@@ -13332,7 +13343,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13355,19 +13366,19 @@
         <v>86</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="O97" t="s" s="2">
         <v>78</v>
@@ -13416,7 +13427,7 @@
         <v>78</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AF97" t="s" s="2">
         <v>76</v>
@@ -13434,10 +13445,10 @@
         <v>78</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13448,7 +13459,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13459,7 +13470,7 @@
         <v>76</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>78</v>
@@ -13471,16 +13482,20 @@
         <v>86</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>562</v>
+        <v>208</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>544</v>
+        <v>292</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M98" s="2"/>
-      <c r="N98" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13528,13 +13543,13 @@
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>561</v>
+        <v>296</v>
       </c>
       <c r="AF98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>78</v>
@@ -13546,19 +13561,19 @@
         <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>564</v>
+        <v>298</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
         <v>565</v>
       </c>
@@ -13571,10 +13586,10 @@
         <v>76</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13583,17 +13598,15 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>225</v>
+        <v>566</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M99" t="s" s="2">
-        <v>568</v>
-      </c>
+      <c r="M99" s="2"/>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
         <v>78</v>
@@ -13618,13 +13631,13 @@
         <v>78</v>
       </c>
       <c r="W99" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>569</v>
+        <v>78</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>570</v>
+        <v>78</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>78</v>
@@ -13657,24 +13670,24 @@
         <v>97</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>572</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>574</v>
+        <v>537</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13685,10 +13698,10 @@
         <v>76</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13697,16 +13710,16 @@
         <v>86</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>576</v>
+        <v>229</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13732,13 +13745,13 @@
         <v>78</v>
       </c>
       <c r="W100" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>78</v>
+        <v>573</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>78</v>
+        <v>574</v>
       </c>
       <c r="Z100" t="s" s="2">
         <v>78</v>
@@ -13756,7 +13769,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13771,16 +13784,16 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13788,7 +13801,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
@@ -13808,18 +13821,20 @@
         <v>78</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="M101" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
         <v>78</v>
@@ -13868,7 +13883,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13883,16 +13898,16 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>578</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13900,11 +13915,11 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
-        <v>591</v>
+        <v>78</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -13914,7 +13929,7 @@
         <v>77</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -13923,17 +13938,15 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
         <v>78</v>
@@ -13970,19 +13983,19 @@
         <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
-        <v>596</v>
+        <v>78</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>597</v>
+        <v>78</v>
       </c>
       <c r="AC102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -13997,13 +14010,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14012,22 +14025,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="B103" s="2"/>
       <c r="C103" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>86</v>
@@ -14039,16 +14050,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14086,19 +14097,19 @@
         <v>78</v>
       </c>
       <c r="AA103" t="s" s="2">
-        <v>78</v>
+        <v>600</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>78</v>
+        <v>601</v>
       </c>
       <c r="AC103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AD103" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14113,13 +14124,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14130,13 +14141,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14155,16 +14166,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14214,7 +14225,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14229,13 +14240,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14246,13 +14257,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14271,16 +14282,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14330,7 +14341,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14345,13 +14356,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14362,13 +14373,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14387,16 +14398,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14446,7 +14457,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14461,13 +14472,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14478,13 +14489,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>146</v>
+        <v>610</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14503,16 +14514,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14562,7 +14573,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14577,13 +14588,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14594,13 +14605,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>609</v>
+        <v>146</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14619,16 +14630,16 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14678,7 +14689,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14693,13 +14704,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14710,13 +14721,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14735,16 +14746,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14794,7 +14805,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14809,13 +14820,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14824,41 +14835,43 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="B110" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="C110" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
@@ -14908,7 +14921,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14923,13 +14936,13 @@
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>78</v>
+        <v>602</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14940,11 +14953,11 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
-        <v>621</v>
+        <v>78</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14963,20 +14976,18 @@
         <v>86</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>225</v>
+        <v>618</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>625</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15000,13 +15011,13 @@
         <v>78</v>
       </c>
       <c r="W111" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>626</v>
+        <v>78</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>627</v>
+        <v>78</v>
       </c>
       <c r="Z111" t="s" s="2">
         <v>78</v>
@@ -15024,7 +15035,7 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
@@ -15042,25 +15053,25 @@
         <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>629</v>
+        <v>78</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
-        <v>78</v>
+        <v>625</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15076,19 +15087,23 @@
         <v>78</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>631</v>
+        <v>229</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>47</v>
+        <v>626</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
+        <v>627</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="O112" t="s" s="2">
         <v>78</v>
       </c>
@@ -15112,13 +15127,13 @@
         <v>78</v>
       </c>
       <c r="W112" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>78</v>
+        <v>630</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>78</v>
+        <v>631</v>
       </c>
       <c r="Z112" t="s" s="2">
         <v>78</v>
@@ -15136,7 +15151,7 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
@@ -15151,24 +15166,24 @@
         <v>97</v>
       </c>
       <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>635</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
@@ -15179,7 +15194,7 @@
         <v>76</v>
       </c>
       <c r="F113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>78</v>
@@ -15188,16 +15203,16 @@
         <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>204</v>
+        <v>635</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>637</v>
+        <v>47</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -15248,13 +15263,13 @@
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>78</v>
@@ -15263,19 +15278,19 @@
         <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>78</v>
+        <v>637</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AL113" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="114" hidden="true">
@@ -15291,7 +15306,7 @@
         <v>76</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>78</v>
@@ -15300,20 +15315,18 @@
         <v>78</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J114" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="K114" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="K114" t="s" s="2">
+      <c r="L114" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="L114" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>644</v>
-      </c>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
         <v>78</v>
@@ -15368,7 +15381,7 @@
         <v>76</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>78</v>
@@ -15377,23 +15390,137 @@
         <v>97</v>
       </c>
       <c r="AJ114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B115" s="2"/>
+      <c r="C115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="AK114" t="s" s="2">
+      <c r="K115" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="P115" s="2"/>
+      <c r="Q115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AK115" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="AL114" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN114" t="s" s="2">
+      <c r="AL115" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN114">
+  <autoFilter ref="A1:AN115">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15403,7 +15530,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI113">
+  <conditionalFormatting sqref="A2:AI114">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4178" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4178" uniqueCount="649">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1731,10 +1731,7 @@
     <t>The preferred location(s) where the procedure should actually happen in coded or free text form. E.g. at home or nursing day care center.</t>
   </si>
   <si>
-    <t>A location type where services are delivered.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
+    <t>http://minsal.cl/listaespera/ValueSet/VSDestinoReferenciaCodigo</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[scoper.determinerCode=KIND].code</t>
@@ -1747,9 +1744,6 @@
   </si>
   <si>
     <t>ServiceRequest.locationCode.coding</t>
-  </si>
-  <si>
-    <t>http://minsal.cl/listaespera/ValueSet/VSDestinoReferenciaCodigo</t>
   </si>
   <si>
     <t>ServiceRequest.locationCode.coding.id</t>
@@ -2385,7 +2379,7 @@
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="67.80078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="61.21484375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -12263,13 +12257,11 @@
         <v>78</v>
       </c>
       <c r="W87" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="X87" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="X87" s="2"/>
+      <c r="Y87" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="Z87" t="s" s="2">
         <v>78</v>
@@ -12308,7 +12300,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>537</v>
@@ -12319,7 +12311,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" t="s" s="2">
@@ -12431,7 +12423,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" t="s" s="2">
@@ -12545,7 +12537,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" t="s" s="2">
@@ -12605,11 +12597,13 @@
         <v>78</v>
       </c>
       <c r="W90" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="X90" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Y90" t="s" s="2">
-        <v>556</v>
+        <v>78</v>
       </c>
       <c r="Z90" t="s" s="2">
         <v>78</v>
@@ -12659,7 +12653,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" t="s" s="2">
@@ -12771,7 +12765,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" t="s" s="2">
@@ -12885,7 +12879,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" t="s" s="2">
@@ -13001,7 +12995,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" t="s" s="2">
@@ -13115,7 +13109,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" t="s" s="2">
@@ -13229,7 +13223,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" t="s" s="2">
@@ -13343,7 +13337,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" t="s" s="2">
@@ -13459,7 +13453,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" t="s" s="2">
@@ -13575,7 +13569,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" t="s" s="2">
@@ -13598,13 +13592,13 @@
         <v>86</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="K99" t="s" s="2">
         <v>548</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
@@ -13655,7 +13649,7 @@
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>76</v>
@@ -13676,7 +13670,7 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>537</v>
@@ -13687,7 +13681,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" t="s" s="2">
@@ -13713,13 +13707,13 @@
         <v>229</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
@@ -13748,10 +13742,10 @@
         <v>441</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="Z100" t="s" s="2">
         <v>78</v>
@@ -13769,7 +13763,7 @@
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>76</v>
@@ -13784,16 +13778,16 @@
         <v>97</v>
       </c>
       <c r="AJ100" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AL100" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AK100" t="s" s="2">
+      <c r="AM100" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -13801,7 +13795,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" t="s" s="2">
@@ -13824,16 +13818,16 @@
         <v>86</v>
       </c>
       <c r="J101" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="K101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
@@ -13883,7 +13877,7 @@
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AF101" t="s" s="2">
         <v>76</v>
@@ -13898,16 +13892,16 @@
         <v>97</v>
       </c>
       <c r="AJ101" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AL101" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AK101" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>586</v>
-      </c>
       <c r="AM101" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13915,7 +13909,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" t="s" s="2">
@@ -13938,13 +13932,13 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -13995,7 +13989,7 @@
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>76</v>
@@ -14010,13 +14004,13 @@
         <v>97</v>
       </c>
       <c r="AJ102" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AL102" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14027,11 +14021,11 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -14050,16 +14044,16 @@
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="K103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
@@ -14097,10 +14091,10 @@
         <v>78</v>
       </c>
       <c r="AA103" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AC103" t="s" s="2">
         <v>78</v>
@@ -14109,7 +14103,7 @@
         <v>134</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF103" t="s" s="2">
         <v>76</v>
@@ -14124,13 +14118,13 @@
         <v>97</v>
       </c>
       <c r="AJ103" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14141,13 +14135,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -14166,16 +14160,16 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
@@ -14225,7 +14219,7 @@
         <v>78</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>76</v>
@@ -14240,13 +14234,13 @@
         <v>97</v>
       </c>
       <c r="AJ104" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL104" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14257,13 +14251,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -14282,16 +14276,16 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L105" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="K105" t="s" s="2">
+      <c r="M105" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
@@ -14341,7 +14335,7 @@
         <v>78</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>76</v>
@@ -14356,13 +14350,13 @@
         <v>97</v>
       </c>
       <c r="AJ105" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL105" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14373,13 +14367,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -14398,16 +14392,16 @@
         <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
@@ -14457,7 +14451,7 @@
         <v>78</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF106" t="s" s="2">
         <v>76</v>
@@ -14472,13 +14466,13 @@
         <v>97</v>
       </c>
       <c r="AJ106" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL106" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>78</v>
@@ -14489,13 +14483,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -14514,16 +14508,16 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
@@ -14573,7 +14567,7 @@
         <v>78</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>76</v>
@@ -14588,13 +14582,13 @@
         <v>97</v>
       </c>
       <c r="AJ107" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>78</v>
@@ -14605,13 +14599,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>146</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -14630,16 +14624,16 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
@@ -14689,7 +14683,7 @@
         <v>78</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF108" t="s" s="2">
         <v>76</v>
@@ -14704,13 +14698,13 @@
         <v>97</v>
       </c>
       <c r="AJ108" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>78</v>
@@ -14721,13 +14715,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -14746,16 +14740,16 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
@@ -14805,7 +14799,7 @@
         <v>78</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>76</v>
@@ -14820,13 +14814,13 @@
         <v>97</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL109" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>78</v>
@@ -14837,13 +14831,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14862,16 +14856,16 @@
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
@@ -14921,7 +14915,7 @@
         <v>78</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AF110" t="s" s="2">
         <v>76</v>
@@ -14936,13 +14930,13 @@
         <v>97</v>
       </c>
       <c r="AJ110" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL110" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -14953,7 +14947,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
@@ -14976,16 +14970,16 @@
         <v>86</v>
       </c>
       <c r="J111" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="K111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
@@ -15035,7 +15029,7 @@
         <v>78</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AF111" t="s" s="2">
         <v>76</v>
@@ -15053,10 +15047,10 @@
         <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -15067,11 +15061,11 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -15093,16 +15087,16 @@
         <v>229</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="O112" t="s" s="2">
         <v>78</v>
@@ -15130,10 +15124,10 @@
         <v>441</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="Z112" t="s" s="2">
         <v>78</v>
@@ -15151,7 +15145,7 @@
         <v>78</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AF112" t="s" s="2">
         <v>76</v>
@@ -15169,21 +15163,21 @@
         <v>78</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
@@ -15206,13 +15200,13 @@
         <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="K113" t="s" s="2">
         <v>47</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -15263,7 +15257,7 @@
         <v>78</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>76</v>
@@ -15278,24 +15272,24 @@
         <v>97</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>462</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" t="s" s="2">
@@ -15321,10 +15315,10 @@
         <v>208</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
@@ -15375,7 +15369,7 @@
         <v>78</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AF114" t="s" s="2">
         <v>76</v>
@@ -15396,7 +15390,7 @@
         <v>462</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -15407,7 +15401,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" t="s" s="2">
@@ -15430,16 +15424,16 @@
         <v>78</v>
       </c>
       <c r="J115" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="L115" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="K115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
@@ -15489,7 +15483,7 @@
         <v>78</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>76</v>
@@ -15504,13 +15498,13 @@
         <v>97</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>128</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ServiceRequestLE.xlsx
+++ b/StructureDefinition-ServiceRequestLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
